--- a/db/A7XLK-3201-RestaurantA7.xlsx
+++ b/db/A7XLK-3201-RestaurantA7.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10711"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10808"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wangtaichung/Documents/7_WebSite/7.11_CommunityWebSite/A7Xinlinkou2/db/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wangtaichung/Documents/7_WebSite/7.11_CommunityWebSite/A7Xinlinkou4/db/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{686DA497-07D2-5C4D-B3B8-0AC780C0A9F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80A8218C-D16F-C048-8985-3CC3605FD8FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1040" yWindow="8720" windowWidth="39920" windowHeight="22540" xr2:uid="{EC3C71DD-AB41-7249-985D-4787F3B89605}"/>
+    <workbookView xWindow="6160" yWindow="3680" windowWidth="39920" windowHeight="22540" xr2:uid="{EC3C71DD-AB41-7249-985D-4787F3B89605}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -863,12 +863,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>&lt;p&gt;
-   資訊: &lt;a style="button" class="btn btn-info"  href="https://almablog.com.tw/blog/post/172302?fbclid=IwAR1Pl7ShDJeMe7m5BngujgTMXJTa0GuJ-Lq8MORepEuNKUwcvMCORzjZGYk"&gt;推薦&lt;/a&gt; 
-&lt;/p&gt;</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>弈膳の便當</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -884,6 +878,12 @@
     <t>&lt;p&gt;
    資訊: &lt;a style="button" class="btn btn-info"  href="fig/XLK-321-RestaurantA7/AiCity-952-奕膳便當-701.jpg"&gt;菜單&lt;/a&gt; 
   &lt;br&gt;試營運優惠期間為期兩週（8/7-8/22）
+&lt;/p&gt;</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;p&gt;
+   資訊: &lt;a style="button" class="btn btn-info"  href="https://almablog.com.tw/blog/post/172302?fbclid=IwAR1Pl7ShDJeMe7m5BngujgTMXJTa0GuJ-Lq8MORepEuNKUwcvMCORzjZGYk"&gt;推薦&lt;/a&gt; &amp;nbsp;&amp;nbsp;
 &lt;/p&gt;</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -1573,7 +1573,7 @@
         <v>51</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>18</v>
@@ -1593,7 +1593,7 @@
         <v>69</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C8" s="5" t="s">
         <v>20</v>
@@ -1612,7 +1612,7 @@
         <v>93</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>52</v>
@@ -1621,7 +1621,7 @@
         <v>61</v>
       </c>
       <c r="L8" s="4" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="M8" s="2"/>
     </row>
@@ -2142,7 +2142,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="23" spans="1:13" ht="80">
+    <row r="23" spans="1:13" ht="96">
       <c r="A23">
         <v>515</v>
       </c>
@@ -2174,7 +2174,7 @@
         <v>91</v>
       </c>
       <c r="L23" s="8" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="M23" t="s">
         <v>196</v>

--- a/db/A7XLK-3201-RestaurantA7.xlsx
+++ b/db/A7XLK-3201-RestaurantA7.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wangtaichung/Documents/7_WebSite/7.11_CommunityWebSite/A7Xinlinkou4/db/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80A8218C-D16F-C048-8985-3CC3605FD8FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40ED89F1-087C-2B44-A5E8-304254D7ED68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6160" yWindow="3680" windowWidth="39920" windowHeight="22540" xr2:uid="{EC3C71DD-AB41-7249-985D-4787F3B89605}"/>
+    <workbookView xWindow="20" yWindow="500" windowWidth="39920" windowHeight="22540" xr2:uid="{EC3C71DD-AB41-7249-985D-4787F3B89605}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="255" uniqueCount="204">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="245" uniqueCount="198">
   <si>
     <t>no</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -176,22 +176,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>桃園市龜山區長慶三街40號1樓</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>0916-538-733</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>06:00 - 21:00, 週日公休</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>fig/XLK-321-RestaurantA7/A7XLK-3201-RestaurantA7-04.jpg</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>番茄村Brunch &amp; Café</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -292,9 +276,6 @@
   </si>
   <si>
     <t>103</t>
-  </si>
-  <si>
-    <t>104</t>
   </si>
   <si>
     <t>105</t>
@@ -799,13 +780,6 @@
     <t>&lt;p&gt;
    資訊: &lt;a style="button" class="btn btn-info"  href="https://tcwang.github.io/A7Xinlinkou/A7XLK-32-RestaurantA7-A1.html#Menu-B05"&gt;模擬點餐&lt;/a&gt; &amp;nbsp;  
 &lt;a style="button" class="btn btn-info"  href="https://tcwang.github.io/A7Xinlinkou/fig/XLK-321-RestaurantA7/AiCity-950-番茄村菜單.jpg"&gt;菜單&lt;/a&gt;
-&lt;/p&gt;</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>&lt;p&gt;
-   資訊: &lt;a style="button" class="btn btn-info"  href="https://tcwang.github.io/A7Xinlinkou/A7XLK-32-RestaurantA7-A1.html#Menu-B04"&gt;模擬點餐&lt;/a&gt; &amp;nbsp; 
-&lt;a style="button" class="btn btn-info"  href="https://tcwang.github.io/A7Xinlinkou/fig/XLK-321-RestaurantA7/AiCity-950-越南小吃菜單.jpg"&gt;菜單&lt;/a&gt; &amp;nbsp; 
 &lt;/p&gt;</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -1302,7 +1276,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D43F91F4-866F-584C-A1A3-A0D1F56F484D}">
-  <dimension ref="A1:M23"/>
+  <dimension ref="A1:M22"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col min="3" max="3" width="10.1640625" customWidth="1"/>
@@ -1348,7 +1322,7 @@
         <v>9</v>
       </c>
       <c r="K1" s="2" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="L1" s="2" t="s">
         <v>10</v>
@@ -1357,9 +1331,9 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:13" ht="192">
+    <row r="2" spans="1:13" ht="224">
       <c r="A2" s="1" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>12</v>
@@ -1381,24 +1355,24 @@
         <v>17</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>18</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="L2" s="4" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
     </row>
     <row r="3" spans="1:13" ht="128">
       <c r="A3" s="1" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>19</v>
@@ -1428,18 +1402,18 @@
         <v>18</v>
       </c>
       <c r="K3" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="L3" s="4" t="s">
+        <v>183</v>
+      </c>
+      <c r="M3" s="3" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" ht="112">
+      <c r="A4" s="1" t="s">
         <v>61</v>
-      </c>
-      <c r="L3" s="4" t="s">
-        <v>189</v>
-      </c>
-      <c r="M3" s="3" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="96">
-      <c r="A4" s="1" t="s">
-        <v>65</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>27</v>
@@ -1467,287 +1441,291 @@
         <v>18</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="L4" s="4" t="s">
-        <v>188</v>
+        <v>182</v>
       </c>
       <c r="M4" s="2"/>
     </row>
-    <row r="5" spans="1:13" ht="128">
+    <row r="5" spans="1:13" ht="144">
       <c r="A5" s="1" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>28</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="G5" s="2"/>
+        <v>39</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>40</v>
+      </c>
       <c r="H5" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
+      </c>
+      <c r="I5" s="3" t="s">
+        <v>42</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>18</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="L5" s="4" t="s">
-        <v>187</v>
-      </c>
-      <c r="M5" s="2"/>
+        <v>181</v>
+      </c>
+      <c r="M5" s="3" t="s">
+        <v>54</v>
+      </c>
     </row>
-    <row r="6" spans="1:13" ht="128">
+    <row r="6" spans="1:13" ht="129">
       <c r="A6" s="1" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>28</v>
+        <v>43</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>35</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="G6" s="3" t="s">
-        <v>44</v>
-      </c>
+        <v>45</v>
+      </c>
+      <c r="F6" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="G6" s="6"/>
       <c r="H6" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>46</v>
+        <v>194</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>18</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="L6" s="4" t="s">
-        <v>186</v>
+        <v>180</v>
       </c>
       <c r="M6" s="3" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" ht="80">
+      <c r="A7" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="F7" s="2" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="7" spans="1:13" ht="129">
-      <c r="A7" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="D7" s="2" t="s">
+      <c r="G7" s="2"/>
+      <c r="H7" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="I7" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="J7" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="E7" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="F7" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="G7" s="6"/>
-      <c r="H7" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="I7" s="3" t="s">
-        <v>200</v>
-      </c>
-      <c r="J7" s="2" t="s">
-        <v>18</v>
-      </c>
       <c r="K7" s="2" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="L7" s="4" t="s">
-        <v>185</v>
-      </c>
-      <c r="M7" s="3" t="s">
-        <v>59</v>
-      </c>
+        <v>196</v>
+      </c>
+      <c r="M7" s="2"/>
     </row>
     <row r="8" spans="1:13" ht="80">
-      <c r="A8" s="1" t="s">
+      <c r="A8">
+        <v>501</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="J8" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="K8" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="L8" s="8" t="s">
+        <v>179</v>
+      </c>
+      <c r="M8" s="3" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" ht="208">
+      <c r="A9">
+        <v>502</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="H9" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="B8" s="2" t="s">
-        <v>199</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="G8" s="2"/>
-      <c r="H8" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="I8" s="3" t="s">
-        <v>201</v>
-      </c>
-      <c r="J8" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="K8" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="L8" s="4" t="s">
-        <v>202</v>
-      </c>
-      <c r="M8" s="2"/>
+      <c r="I9" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="J9" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="K9" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="L9" s="8" t="s">
+        <v>178</v>
+      </c>
+      <c r="M9" s="3" t="s">
+        <v>90</v>
+      </c>
     </row>
-    <row r="9" spans="1:13" ht="80">
-      <c r="A9">
-        <v>501</v>
-      </c>
-      <c r="B9" s="2" t="s">
+    <row r="10" spans="1:13" ht="80">
+      <c r="A10">
+        <v>503</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="H10" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="C9" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="H9" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="I9" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="J9" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="K9" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="L9" s="8" t="s">
-        <v>184</v>
-      </c>
-      <c r="M9" s="3" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13" ht="208">
-      <c r="A10">
-        <v>502</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="C10" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="D10" s="2" t="s">
+      <c r="I10" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="J10" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="K10" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="L10" s="8" t="s">
+        <v>177</v>
+      </c>
+      <c r="M10" s="3" t="s">
         <v>96</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="H10" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="J10" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="K10" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="L10" s="8" t="s">
-        <v>183</v>
-      </c>
-      <c r="M10" s="3" t="s">
-        <v>95</v>
       </c>
     </row>
     <row r="11" spans="1:13" ht="80">
       <c r="A11">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>28</v>
+        <v>66</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>104</v>
+        <v>135</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="I11" s="3" t="s">
         <v>105</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="L11" s="8" t="s">
-        <v>182</v>
+        <v>176</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
-    <row r="12" spans="1:13" ht="80">
+    <row r="12" spans="1:13" ht="192">
       <c r="A12">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>106</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>71</v>
+        <v>28</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>108</v>
@@ -1756,22 +1734,22 @@
         <v>109</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>140</v>
+        <v>110</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="L12" s="8" t="s">
-        <v>181</v>
+        <v>168</v>
       </c>
       <c r="M12" s="3" t="s">
         <v>107</v>
@@ -1779,405 +1757,367 @@
     </row>
     <row r="13" spans="1:13" ht="192">
       <c r="A13">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C13" s="5" t="s">
         <v>28</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>114</v>
       </c>
       <c r="F13" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="I13" t="s">
         <v>115</v>
       </c>
-      <c r="H13" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="I13" s="3" t="s">
+      <c r="J13" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="K13" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="L13" s="8" t="s">
+        <v>169</v>
+      </c>
+      <c r="M13" s="3" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" ht="144">
+      <c r="A14">
+        <v>507</v>
+      </c>
+      <c r="B14" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="J13" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="K13" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="L13" s="8" t="s">
-        <v>173</v>
-      </c>
-      <c r="M13" s="3" t="s">
-        <v>112</v>
+      <c r="C14" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="J14" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="K14" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="L14" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="M14" t="s">
+        <v>118</v>
       </c>
     </row>
-    <row r="14" spans="1:13" ht="192">
-      <c r="A14">
-        <v>506</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="C14" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="H14" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="I14" t="s">
-        <v>120</v>
-      </c>
-      <c r="J14" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="K14" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="L14" s="8" t="s">
-        <v>174</v>
-      </c>
-      <c r="M14" s="3" t="s">
-        <v>118</v>
+    <row r="15" spans="1:13">
+      <c r="A15">
+        <v>508</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="I15" s="7" t="s">
+        <v>127</v>
+      </c>
+      <c r="J15" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="K15" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="M15" s="3" t="s">
+        <v>124</v>
       </c>
     </row>
-    <row r="15" spans="1:13" ht="144">
-      <c r="A15">
-        <v>507</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="C15" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="F15" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="H15" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="I15" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="J15" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="K15" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="L15" s="4" t="s">
-        <v>175</v>
-      </c>
-      <c r="M15" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="16" spans="1:13">
+    <row r="16" spans="1:13" ht="240">
       <c r="A16">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C16" s="5" t="s">
         <v>130</v>
       </c>
       <c r="D16" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="I16" t="s">
+        <v>137</v>
+      </c>
+      <c r="J16" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="K16" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="L16" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="M16" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="F16" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="H16" s="2" t="s">
+    </row>
+    <row r="17" spans="1:13" ht="176">
+      <c r="A17">
+        <v>510</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="C17" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="I17" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="J17" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="K17" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="L17" s="9" t="s">
+        <v>172</v>
+      </c>
+      <c r="M17" s="3" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" ht="144">
+      <c r="A18">
+        <v>511</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="C18" s="5" t="s">
+        <v>145</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="I18" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="J18" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="K18" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="L18" s="9" t="s">
+        <v>173</v>
+      </c>
+      <c r="M18" s="2" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" ht="304">
+      <c r="A19">
+        <v>512</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="C19" s="5" t="s">
+        <v>152</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="H19" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="I16" s="7" t="s">
-        <v>132</v>
-      </c>
-      <c r="J16" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="K16" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="M16" s="3" t="s">
-        <v>129</v>
+      <c r="I19" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="J19" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="K19" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="L19" s="9" t="s">
+        <v>174</v>
+      </c>
+      <c r="M19" s="3" t="s">
+        <v>153</v>
       </c>
     </row>
-    <row r="17" spans="1:13" ht="240">
-      <c r="A17">
-        <v>509</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="C17" s="5" t="s">
-        <v>135</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="F17" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="H17" s="2" t="s">
+    <row r="20" spans="1:13" ht="96">
+      <c r="A20">
+        <v>513</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="C20" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="H20" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="I17" t="s">
-        <v>142</v>
-      </c>
-      <c r="J17" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="K17" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="L17" s="4" t="s">
-        <v>176</v>
-      </c>
-      <c r="M17" s="3" t="s">
-        <v>136</v>
+      <c r="J20" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="K20" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="L20" s="9" t="s">
+        <v>175</v>
+      </c>
+      <c r="M20" t="s">
+        <v>158</v>
       </c>
     </row>
-    <row r="18" spans="1:13" ht="176">
-      <c r="A18">
-        <v>510</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="C18" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="F18" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="H18" s="2" t="s">
+    <row r="21" spans="1:13">
+      <c r="A21">
+        <v>514</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="C21" s="5" t="s">
+        <v>130</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="H21" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="I18" s="3" t="s">
-        <v>148</v>
-      </c>
-      <c r="J18" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="K18" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="L18" s="9" t="s">
-        <v>177</v>
-      </c>
-      <c r="M18" s="3" t="s">
-        <v>144</v>
+      <c r="I21" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="J21" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="K21" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="M21" s="3" t="s">
+        <v>163</v>
       </c>
     </row>
-    <row r="19" spans="1:13" ht="144">
-      <c r="A19">
-        <v>511</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>149</v>
-      </c>
-      <c r="C19" s="5" t="s">
-        <v>150</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="F19" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="H19" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="I19" s="3" t="s">
-        <v>155</v>
-      </c>
-      <c r="J19" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="K19" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="L19" s="9" t="s">
-        <v>178</v>
-      </c>
-      <c r="M19" s="2" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="20" spans="1:13" ht="304">
-      <c r="A20">
-        <v>512</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>156</v>
-      </c>
-      <c r="C20" s="5" t="s">
-        <v>157</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>159</v>
-      </c>
-      <c r="E20" s="2" t="s">
-        <v>160</v>
-      </c>
-      <c r="F20" s="2" t="s">
-        <v>161</v>
-      </c>
-      <c r="H20" s="2" t="s">
+    <row r="22" spans="1:13" ht="96">
+      <c r="A22">
+        <v>515</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="C22" s="5" t="s">
+        <v>185</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="I22" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="J22" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="I20" s="3" t="s">
-        <v>162</v>
-      </c>
-      <c r="J20" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="K20" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="L20" s="9" t="s">
-        <v>179</v>
-      </c>
-      <c r="M20" s="3" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="21" spans="1:13" ht="96">
-      <c r="A21">
-        <v>513</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>164</v>
-      </c>
-      <c r="C21" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>165</v>
-      </c>
-      <c r="E21" s="2" t="s">
-        <v>166</v>
-      </c>
-      <c r="H21" s="2" t="s">
+      <c r="K22" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="J21" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="K21" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="L21" s="9" t="s">
-        <v>180</v>
-      </c>
-      <c r="M21" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="22" spans="1:13">
-      <c r="A22">
-        <v>514</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="C22" s="5" t="s">
-        <v>135</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>169</v>
-      </c>
-      <c r="E22" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="F22" s="2" t="s">
-        <v>171</v>
-      </c>
-      <c r="H22" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="I22" s="3" t="s">
-        <v>172</v>
-      </c>
-      <c r="J22" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="K22" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="M22" s="3" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="23" spans="1:13" ht="96">
-      <c r="A23">
-        <v>515</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>192</v>
-      </c>
-      <c r="C23" s="5" t="s">
-        <v>191</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>193</v>
-      </c>
-      <c r="E23" s="2" t="s">
-        <v>198</v>
-      </c>
-      <c r="F23" s="2" t="s">
-        <v>194</v>
-      </c>
-      <c r="H23" s="2" t="s">
+      <c r="L22" s="8" t="s">
         <v>197</v>
       </c>
-      <c r="I23" s="7" t="s">
-        <v>195</v>
-      </c>
-      <c r="J23" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="K23" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="L23" s="8" t="s">
-        <v>203</v>
-      </c>
-      <c r="M23" t="s">
-        <v>196</v>
+      <c r="M22" t="s">
+        <v>190</v>
       </c>
     </row>
   </sheetData>
@@ -2185,37 +2125,37 @@
   <hyperlinks>
     <hyperlink ref="I3" r:id="rId1" xr:uid="{C4FC3919-D074-B04C-8404-BC6DE733F558}"/>
     <hyperlink ref="I4" r:id="rId2" xr:uid="{F003A365-8C23-084B-B31A-663E82D27E11}"/>
-    <hyperlink ref="G6" r:id="rId3" xr:uid="{7AEBC60D-47CB-2041-BB0C-5BB638DE9DEC}"/>
-    <hyperlink ref="I6" r:id="rId4" xr:uid="{E2777161-F973-9B42-BC21-88DA80C19FD3}"/>
-    <hyperlink ref="I8" r:id="rId5" xr:uid="{240368C4-8A23-D049-BE75-A45A65EB147A}"/>
+    <hyperlink ref="G5" r:id="rId3" xr:uid="{7AEBC60D-47CB-2041-BB0C-5BB638DE9DEC}"/>
+    <hyperlink ref="I5" r:id="rId4" xr:uid="{E2777161-F973-9B42-BC21-88DA80C19FD3}"/>
+    <hyperlink ref="I7" r:id="rId5" xr:uid="{240368C4-8A23-D049-BE75-A45A65EB147A}"/>
     <hyperlink ref="M2" r:id="rId6" xr:uid="{2E20CE02-8C51-1045-B84E-5304199A5CEC}"/>
     <hyperlink ref="M3" r:id="rId7" xr:uid="{21CC0B31-826D-6549-8434-94B01CACE62D}"/>
-    <hyperlink ref="M6" r:id="rId8" xr:uid="{24019989-F9BD-E143-A40C-50EE4DDF5BD1}"/>
-    <hyperlink ref="M7" r:id="rId9" display="https://www.google.com.tw/maps/place/%E5%8A%89%E5%A6%B9%E9%8D%8B%E7%87%92%E6%84%8F%E9%BA%B5-%E6%A1%83%E5%9C%92%E6%9E%97%E5%8F%A3%E5%BA%97/@25.0548468,121.3827894,19.1z/data=!4m5!3m4!1s0x3442a7b02079176f:0x78906ae51c7f6abc!8m2!3d25.0553573!4d121.3840157?hl=zh-TW&amp;authuser=0" xr:uid="{13C7C2D5-34CD-404D-BEE1-B9C104B3C41D}"/>
-    <hyperlink ref="I9" r:id="rId10" xr:uid="{D22B71CE-BEE8-4D4A-B73B-DF696843091A}"/>
-    <hyperlink ref="M9" r:id="rId11" display="https://www.google.com.tw/maps/place/%E8%83%96%E8%80%81%E7%88%B9%E7%BE%8E%E5%BC%8F%E7%82%B8%E9%9B%9EA7%E6%96%87%E9%9D%92%E5%BA%97/@25.0394257,121.3894157,19.83z/data=!4m5!3m4!1s0x3442a73165d8f2d3:0xce822b237485dc8c!8m2!3d25.0394354!4d121.3903716?hl=zh-TW&amp;authuser=0" xr:uid="{C64399C5-4BBF-C54B-AFFF-C515FF32551F}"/>
-    <hyperlink ref="M10" r:id="rId12" display="https://www.google.com.tw/maps/place/%E8%B6%A3%E5%95%83%E7%82%B8%E7%89%A9-%E6%96%87%E9%9D%92%E5%BA%97/@25.039422,121.389821,19z/data=!4m9!1m2!2m1!1z6Laj5ZWD54K454mpQTfmlofpnZLlupc!3m5!1s0x3442a79257c7d5e1:0x96b9a8c7ea325295!8m2!3d25.0394086!4d121.3903675!15sChfotqPllYPngrjnialBN-aWh-mdkuW6l1ogIh7otqMg5ZWDIOeCuCDniakgYTcg5paHIOmdkiDlupeSAQRkZWxp?hl=zh-TW&amp;authuser=0" xr:uid="{ECDBCB9E-1A0B-2440-BEDC-B3365ABCEB46}"/>
-    <hyperlink ref="I10" r:id="rId13" xr:uid="{C84B02C1-9D57-3449-BF10-8BF8B150E1B0}"/>
-    <hyperlink ref="M11" r:id="rId14" display="https://www.google.com.tw/maps/place/MQ%E5%85%83%E6%B0%A3house/@25.0396043,121.3889924,19z/data=!4m9!1m2!2m1!1z5YWD5rCj5pep5Y2I6aSQQTfmlofpnZLlupc!3m5!1s0x3442a73b0be03237:0xb76fc65b93d291de!8m2!3d25.0395543!4d121.389809!15sChrlhYPmsKPml6nljYjppJBBN-aWh-mdkuW6lyIDiAEBWh4iHOWFg-awoyDml6kg5Y2I6aSQIGE3IOaWhyDpnZKSARRicmVha2Zhc3RfcmVzdGF1cmFudJoBJENoZERTVWhOTUc5blMwVkpRMEZuU1VSTE1tSjJWbWRCUlJBQg?hl=zh-TW&amp;authuser=0" xr:uid="{A608DFF8-5556-A348-BCCF-DF8FED89A676}"/>
-    <hyperlink ref="I11" r:id="rId15" xr:uid="{2AC2704D-3B90-7143-8538-1BCF2601B133}"/>
-    <hyperlink ref="M12" r:id="rId16" xr:uid="{BCFDF63E-46D6-4C46-A895-F2BE3AF3A43C}"/>
-    <hyperlink ref="I12" r:id="rId17" xr:uid="{DA402F63-BBBF-314A-9282-201C2F50A8E9}"/>
-    <hyperlink ref="M13" r:id="rId18" xr:uid="{62B3945D-7D85-6F41-B0AE-685C751A1E0D}"/>
-    <hyperlink ref="I13" r:id="rId19" xr:uid="{CF45B8DE-914A-2B48-BCB7-14602F96BD36}"/>
-    <hyperlink ref="M14" r:id="rId20" display="https://www.google.com.tw/maps/place/W%E3%80%82D%E6%88%91%E7%9A%84%E6%97%A9%E9%A4%90/@25.039828,121.3881883,18z/data=!4m9!1m2!2m1!1zV0TmiJHnmoTml6nppJAgQTfmlofpnZLlupc!3m5!1s0x3442a771fa73353d:0x329428879337e9d8!8m2!3d25.0396834!4d121.38925!15sChpXROaIkeeahOaXqemkkCBBN-aWh-mdkuW6l1oeIhx3ZCDmiJEg55qEIOaXqemkkCBhNyDmlocg6Z2SkgEUYnJlYWtmYXN0X3Jlc3RhdXJhbnSaASNDaFpEU1VoTk1HOW5TMFZKUTBGblNVUk5iMlZYVDFoUkVBRQ?hl=zh-TW&amp;authuser=0" xr:uid="{1A766ADC-BF5A-F54B-8857-2EC343131663}"/>
-    <hyperlink ref="I15" r:id="rId21" xr:uid="{D29C3BC2-9385-1848-8CD3-329B3FEC96D0}"/>
-    <hyperlink ref="M16" r:id="rId22" display="https://www.google.com.tw/maps/place/%E9%BA%B5%E9%A4%93%E5%BF%83%E8%86%B3italiana%E7%BE%A9%E5%BC%8F%E6%96%99%E7%90%86/@25.0399443,121.3879522,18z/data=!3m1!4b1!4m5!3m4!1s0x3442a771fefa1693:0x3751e2ae6c6a4c1b!8m2!3d25.0399443!4d121.3890492?hl=zh-TW&amp;authuser=0" xr:uid="{CFA5CDA3-DFA0-A345-802E-4E27D0DD6388}"/>
-    <hyperlink ref="I16" r:id="rId23" xr:uid="{52227806-B293-3140-BA54-19D8D37B7072}"/>
-    <hyperlink ref="M17" r:id="rId24" display="https://www.google.com.tw/maps/place/%E9%BC%8E%E8%A8%98+%E5%B0%8F%E7%B1%A0%E5%8C%85/@25.0394911,121.3880801,18z/data=!4m9!1m2!2m1!1z6byO6KiY5bCP57Gg5YyFIEE35paH6Z2S5bqX!3m5!1s0x3442a771eb8a1057:0x50474f8ab9f0306d!8m2!3d25.0399461!4d121.3891357!15sChvpvI7oqJjlsI_nsaDljIUgQTfmlofpnZLlupdaJCIi6byOIOiomCDlsI8g57GgIOWMhSBhNyDmlocg6Z2SIOW6l5IBCnJlc3RhdXJhbnSaASRDaGREU1VoTk1HOW5TMFZKUTBGblNVUlZORjlEZFd4blJSQUI?hl=zh-TW&amp;authuser=0" xr:uid="{40D2FFA0-1BA7-7D40-9492-E31751F5971E}"/>
-    <hyperlink ref="M18" r:id="rId25" display="https://www.google.com.tw/maps/place/%E6%B2%88%E5%AE%B6%E8%B1%86%E6%BC%BF/@25.0400428,121.3880621,18z/data=!4m9!1m2!2m1!1z5rKI5a626LGG5ry_IEE35paH6Z2S5bqX!3m5!1s0x3442a7e71b4fdbef:0xa7327c25e217658c!8m2!3d25.0398612!4d121.3890308!15sChjmsojlrrbosYbmvL8gQTfmlofpnZLlupdaGyIZ5rKIIOWutiDosYbmvL8gYTcg5paHIOmdkpIBFGJyZWFrZmFzdF9yZXN0YXVyYW50mgEkQ2hkRFNVaE5NRzluUzBWSlEwRm5TVU5qYWpkRU1HbFJSUkFC?hl=zh-TW&amp;authuser=0" xr:uid="{5BED3BAC-7517-6C44-8DD0-2E9AAD01210B}"/>
-    <hyperlink ref="I18" r:id="rId26" xr:uid="{FA94FB62-C3B4-F440-B546-D5651C4C1EF0}"/>
-    <hyperlink ref="I19" r:id="rId27" xr:uid="{36593C4B-5784-D647-A021-407E9C5E9859}"/>
-    <hyperlink ref="M20" r:id="rId28" xr:uid="{C10E1D29-46CE-4843-8B5F-0C73F3E21715}"/>
-    <hyperlink ref="I20" r:id="rId29" xr:uid="{4108B3FA-F736-964B-AFA8-8EA10E9958B5}"/>
-    <hyperlink ref="M22" r:id="rId30" xr:uid="{98E56C55-CA1A-F648-87ED-05DD4AEF5C71}"/>
-    <hyperlink ref="I22" r:id="rId31" xr:uid="{32037A18-7380-4045-A4B0-FCA8B0774D4F}"/>
-    <hyperlink ref="I23" r:id="rId32" xr:uid="{6F802D23-EF8F-E748-A152-E7AB9EBBC40B}"/>
-    <hyperlink ref="I7" r:id="rId33" xr:uid="{7D690390-5CDC-774F-88F8-D0A10F74092B}"/>
+    <hyperlink ref="M5" r:id="rId8" xr:uid="{24019989-F9BD-E143-A40C-50EE4DDF5BD1}"/>
+    <hyperlink ref="M6" r:id="rId9" display="https://www.google.com.tw/maps/place/%E5%8A%89%E5%A6%B9%E9%8D%8B%E7%87%92%E6%84%8F%E9%BA%B5-%E6%A1%83%E5%9C%92%E6%9E%97%E5%8F%A3%E5%BA%97/@25.0548468,121.3827894,19.1z/data=!4m5!3m4!1s0x3442a7b02079176f:0x78906ae51c7f6abc!8m2!3d25.0553573!4d121.3840157?hl=zh-TW&amp;authuser=0" xr:uid="{13C7C2D5-34CD-404D-BEE1-B9C104B3C41D}"/>
+    <hyperlink ref="I8" r:id="rId10" xr:uid="{D22B71CE-BEE8-4D4A-B73B-DF696843091A}"/>
+    <hyperlink ref="M8" r:id="rId11" display="https://www.google.com.tw/maps/place/%E8%83%96%E8%80%81%E7%88%B9%E7%BE%8E%E5%BC%8F%E7%82%B8%E9%9B%9EA7%E6%96%87%E9%9D%92%E5%BA%97/@25.0394257,121.3894157,19.83z/data=!4m5!3m4!1s0x3442a73165d8f2d3:0xce822b237485dc8c!8m2!3d25.0394354!4d121.3903716?hl=zh-TW&amp;authuser=0" xr:uid="{C64399C5-4BBF-C54B-AFFF-C515FF32551F}"/>
+    <hyperlink ref="M9" r:id="rId12" display="https://www.google.com.tw/maps/place/%E8%B6%A3%E5%95%83%E7%82%B8%E7%89%A9-%E6%96%87%E9%9D%92%E5%BA%97/@25.039422,121.389821,19z/data=!4m9!1m2!2m1!1z6Laj5ZWD54K454mpQTfmlofpnZLlupc!3m5!1s0x3442a79257c7d5e1:0x96b9a8c7ea325295!8m2!3d25.0394086!4d121.3903675!15sChfotqPllYPngrjnialBN-aWh-mdkuW6l1ogIh7otqMg5ZWDIOeCuCDniakgYTcg5paHIOmdkiDlupeSAQRkZWxp?hl=zh-TW&amp;authuser=0" xr:uid="{ECDBCB9E-1A0B-2440-BEDC-B3365ABCEB46}"/>
+    <hyperlink ref="I9" r:id="rId13" xr:uid="{C84B02C1-9D57-3449-BF10-8BF8B150E1B0}"/>
+    <hyperlink ref="M10" r:id="rId14" display="https://www.google.com.tw/maps/place/MQ%E5%85%83%E6%B0%A3house/@25.0396043,121.3889924,19z/data=!4m9!1m2!2m1!1z5YWD5rCj5pep5Y2I6aSQQTfmlofpnZLlupc!3m5!1s0x3442a73b0be03237:0xb76fc65b93d291de!8m2!3d25.0395543!4d121.389809!15sChrlhYPmsKPml6nljYjppJBBN-aWh-mdkuW6lyIDiAEBWh4iHOWFg-awoyDml6kg5Y2I6aSQIGE3IOaWhyDpnZKSARRicmVha2Zhc3RfcmVzdGF1cmFudJoBJENoZERTVWhOTUc5blMwVkpRMEZuU1VSTE1tSjJWbWRCUlJBQg?hl=zh-TW&amp;authuser=0" xr:uid="{A608DFF8-5556-A348-BCCF-DF8FED89A676}"/>
+    <hyperlink ref="I10" r:id="rId15" xr:uid="{2AC2704D-3B90-7143-8538-1BCF2601B133}"/>
+    <hyperlink ref="M11" r:id="rId16" xr:uid="{BCFDF63E-46D6-4C46-A895-F2BE3AF3A43C}"/>
+    <hyperlink ref="I11" r:id="rId17" xr:uid="{DA402F63-BBBF-314A-9282-201C2F50A8E9}"/>
+    <hyperlink ref="M12" r:id="rId18" xr:uid="{62B3945D-7D85-6F41-B0AE-685C751A1E0D}"/>
+    <hyperlink ref="I12" r:id="rId19" xr:uid="{CF45B8DE-914A-2B48-BCB7-14602F96BD36}"/>
+    <hyperlink ref="M13" r:id="rId20" display="https://www.google.com.tw/maps/place/W%E3%80%82D%E6%88%91%E7%9A%84%E6%97%A9%E9%A4%90/@25.039828,121.3881883,18z/data=!4m9!1m2!2m1!1zV0TmiJHnmoTml6nppJAgQTfmlofpnZLlupc!3m5!1s0x3442a771fa73353d:0x329428879337e9d8!8m2!3d25.0396834!4d121.38925!15sChpXROaIkeeahOaXqemkkCBBN-aWh-mdkuW6l1oeIhx3ZCDmiJEg55qEIOaXqemkkCBhNyDmlocg6Z2SkgEUYnJlYWtmYXN0X3Jlc3RhdXJhbnSaASNDaFpEU1VoTk1HOW5TMFZKUTBGblNVUk5iMlZYVDFoUkVBRQ?hl=zh-TW&amp;authuser=0" xr:uid="{1A766ADC-BF5A-F54B-8857-2EC343131663}"/>
+    <hyperlink ref="I14" r:id="rId21" xr:uid="{D29C3BC2-9385-1848-8CD3-329B3FEC96D0}"/>
+    <hyperlink ref="M15" r:id="rId22" display="https://www.google.com.tw/maps/place/%E9%BA%B5%E9%A4%93%E5%BF%83%E8%86%B3italiana%E7%BE%A9%E5%BC%8F%E6%96%99%E7%90%86/@25.0399443,121.3879522,18z/data=!3m1!4b1!4m5!3m4!1s0x3442a771fefa1693:0x3751e2ae6c6a4c1b!8m2!3d25.0399443!4d121.3890492?hl=zh-TW&amp;authuser=0" xr:uid="{CFA5CDA3-DFA0-A345-802E-4E27D0DD6388}"/>
+    <hyperlink ref="I15" r:id="rId23" xr:uid="{52227806-B293-3140-BA54-19D8D37B7072}"/>
+    <hyperlink ref="M16" r:id="rId24" display="https://www.google.com.tw/maps/place/%E9%BC%8E%E8%A8%98+%E5%B0%8F%E7%B1%A0%E5%8C%85/@25.0394911,121.3880801,18z/data=!4m9!1m2!2m1!1z6byO6KiY5bCP57Gg5YyFIEE35paH6Z2S5bqX!3m5!1s0x3442a771eb8a1057:0x50474f8ab9f0306d!8m2!3d25.0399461!4d121.3891357!15sChvpvI7oqJjlsI_nsaDljIUgQTfmlofpnZLlupdaJCIi6byOIOiomCDlsI8g57GgIOWMhSBhNyDmlocg6Z2SIOW6l5IBCnJlc3RhdXJhbnSaASRDaGREU1VoTk1HOW5TMFZKUTBGblNVUlZORjlEZFd4blJSQUI?hl=zh-TW&amp;authuser=0" xr:uid="{40D2FFA0-1BA7-7D40-9492-E31751F5971E}"/>
+    <hyperlink ref="M17" r:id="rId25" display="https://www.google.com.tw/maps/place/%E6%B2%88%E5%AE%B6%E8%B1%86%E6%BC%BF/@25.0400428,121.3880621,18z/data=!4m9!1m2!2m1!1z5rKI5a626LGG5ry_IEE35paH6Z2S5bqX!3m5!1s0x3442a7e71b4fdbef:0xa7327c25e217658c!8m2!3d25.0398612!4d121.3890308!15sChjmsojlrrbosYbmvL8gQTfmlofpnZLlupdaGyIZ5rKIIOWutiDosYbmvL8gYTcg5paHIOmdkpIBFGJyZWFrZmFzdF9yZXN0YXVyYW50mgEkQ2hkRFNVaE5NRzluUzBWSlEwRm5TVU5qYWpkRU1HbFJSUkFC?hl=zh-TW&amp;authuser=0" xr:uid="{5BED3BAC-7517-6C44-8DD0-2E9AAD01210B}"/>
+    <hyperlink ref="I17" r:id="rId26" xr:uid="{FA94FB62-C3B4-F440-B546-D5651C4C1EF0}"/>
+    <hyperlink ref="I18" r:id="rId27" xr:uid="{36593C4B-5784-D647-A021-407E9C5E9859}"/>
+    <hyperlink ref="M19" r:id="rId28" xr:uid="{C10E1D29-46CE-4843-8B5F-0C73F3E21715}"/>
+    <hyperlink ref="I19" r:id="rId29" xr:uid="{4108B3FA-F736-964B-AFA8-8EA10E9958B5}"/>
+    <hyperlink ref="M21" r:id="rId30" xr:uid="{98E56C55-CA1A-F648-87ED-05DD4AEF5C71}"/>
+    <hyperlink ref="I21" r:id="rId31" xr:uid="{32037A18-7380-4045-A4B0-FCA8B0774D4F}"/>
+    <hyperlink ref="I22" r:id="rId32" xr:uid="{6F802D23-EF8F-E748-A152-E7AB9EBBC40B}"/>
+    <hyperlink ref="I6" r:id="rId33" xr:uid="{7D690390-5CDC-774F-88F8-D0A10F74092B}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/db/A7XLK-3201-RestaurantA7.xlsx
+++ b/db/A7XLK-3201-RestaurantA7.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10808"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10912"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wangtaichung/Documents/7_WebSite/7.11_CommunityWebSite/A7Xinlinkou4/db/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40ED89F1-087C-2B44-A5E8-304254D7ED68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1EBC1F95-2906-304E-AC1F-311BB42EBEA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20" yWindow="500" windowWidth="39920" windowHeight="22540" xr2:uid="{EC3C71DD-AB41-7249-985D-4787F3B89605}"/>
+    <workbookView xWindow="-780" yWindow="2500" windowWidth="39920" windowHeight="22540" xr2:uid="{EC3C71DD-AB41-7249-985D-4787F3B89605}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="245" uniqueCount="198">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="255" uniqueCount="208">
   <si>
     <t>no</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -833,10 +833,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>8月2日至15日试营运</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>弈膳の便當</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -858,6 +854,52 @@
   <si>
     <t>&lt;p&gt;
    資訊: &lt;a style="button" class="btn btn-info"  href="https://almablog.com.tw/blog/post/172302?fbclid=IwAR1Pl7ShDJeMe7m5BngujgTMXJTa0GuJ-Lq8MORepEuNKUwcvMCORzjZGYk"&gt;推薦&lt;/a&gt; &amp;nbsp;&amp;nbsp;
+&lt;/p&gt;</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>4.中心商業區</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>海海人生餐酒館</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>酒館</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>桃園市龜山區桃園市龜山區樂善一路500之1號</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>0989-020-867</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>週3~5: 17:00 - 23:00, 週6～日：12:00 - 23:00</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.facebook.com/happyhihai/</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>樂善一路</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>fig/XLK-321-RestaurantA7/A7XLK-3206-海海人生-01.jpg</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.google.com.tw/maps/place/%E6%B5%B7%E6%B5%B7%E4%BA%BA%E7%94%9F%E9%A4%90%E9%85%92%E9%A4%A8-%E9%BE%9C%E5%B1%B1%E7%89%B9%E8%89%B2%E5%92%96%E5%95%A1%E5%BB%B3%7C%E8%81%9A%E9%A4%90%E6%8E%A8%E8%96%A6%7C%E6%85%B6%E7%94%9F%E9%A4%90%E5%BB%B3%7C%E7%86%B1%E9%96%80%E9%A4%90%E9%85%92%E9%A4%A8%7C%E6%8E%A8%E8%96%A6%E7%BE%8E%E5%BC%8F%E9%A4%90%E5%BB%B3%7C%E7%B4%84%E6%9C%83%E9%A4%90%E5%BB%B3/@25.0473364,121.3840045,17z/data=!4m5!3m4!1s0x3442a78eb45ea4ff:0x4474aec40a10127e!8m2!3d25.0471227!4d121.3875512?hl=zh-TW&amp;authuser=0</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;p&gt;
+   資訊: &lt;a style="button" class="btn btn-info"  href="https://www.facebook.com/happyhihai/photos/p.118458333557627/118458333557627"&gt;菜單&lt;/a&gt; &amp;nbsp; 
 &lt;/p&gt;</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -938,7 +980,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -960,6 +1002,9 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1276,17 +1321,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D43F91F4-866F-584C-A1A3-A0D1F56F484D}">
-  <dimension ref="A1:M22"/>
+  <dimension ref="A1:M23"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col min="3" max="3" width="10.1640625" customWidth="1"/>
     <col min="4" max="4" width="24.83203125" customWidth="1"/>
-    <col min="5" max="5" width="14" customWidth="1"/>
+    <col min="5" max="5" width="14" style="10" customWidth="1"/>
     <col min="6" max="6" width="26.5" customWidth="1"/>
     <col min="8" max="8" width="48" customWidth="1"/>
     <col min="9" max="9" width="25.6640625" customWidth="1"/>
     <col min="10" max="10" width="7.33203125" customWidth="1"/>
-    <col min="11" max="11" width="5.6640625" customWidth="1"/>
+    <col min="11" max="11" width="24.5" customWidth="1"/>
     <col min="12" max="12" width="69.5" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1303,7 +1348,7 @@
       <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F1" s="2" t="s">
@@ -1331,7 +1376,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:13" ht="224">
+    <row r="2" spans="1:13" ht="192">
       <c r="A2" s="1" t="s">
         <v>59</v>
       </c>
@@ -1344,7 +1389,7 @@
       <c r="D2" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" s="1" t="s">
         <v>15</v>
       </c>
       <c r="F2" s="2" t="s">
@@ -1383,7 +1428,7 @@
       <c r="D3" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="E3" s="1" t="s">
         <v>22</v>
       </c>
       <c r="F3" s="2" t="s">
@@ -1411,7 +1456,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="4" spans="1:13" ht="112">
+    <row r="4" spans="1:13" ht="96">
       <c r="A4" s="1" t="s">
         <v>61</v>
       </c>
@@ -1424,7 +1469,7 @@
       <c r="D4" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="E4" s="1" t="s">
         <v>30</v>
       </c>
       <c r="F4" s="2" t="s">
@@ -1448,7 +1493,7 @@
       </c>
       <c r="M4" s="2"/>
     </row>
-    <row r="5" spans="1:13" ht="144">
+    <row r="5" spans="1:13" ht="128">
       <c r="A5" s="1" t="s">
         <v>62</v>
       </c>
@@ -1461,7 +1506,7 @@
       <c r="D5" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="E5" s="2" t="s">
+      <c r="E5" s="1" t="s">
         <v>38</v>
       </c>
       <c r="F5" s="2" t="s">
@@ -1502,7 +1547,7 @@
       <c r="D6" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="E6" s="2" t="s">
+      <c r="E6" s="1" t="s">
         <v>45</v>
       </c>
       <c r="F6" s="6" t="s">
@@ -1513,7 +1558,7 @@
         <v>47</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>18</v>
@@ -1533,7 +1578,7 @@
         <v>64</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C7" s="5" t="s">
         <v>20</v>
@@ -1541,7 +1586,7 @@
       <c r="D7" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="E7" s="2" t="s">
+      <c r="E7" s="1" t="s">
         <v>50</v>
       </c>
       <c r="F7" s="2" t="s">
@@ -1552,7 +1597,7 @@
         <v>88</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>48</v>
@@ -1561,7 +1606,7 @@
         <v>57</v>
       </c>
       <c r="L7" s="4" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="M7" s="2"/>
     </row>
@@ -1578,7 +1623,7 @@
       <c r="D8" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="E8" s="2" t="s">
+      <c r="E8" s="1" t="s">
         <v>83</v>
       </c>
       <c r="F8" s="2" t="s">
@@ -1616,7 +1661,7 @@
       <c r="D9" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="E9" s="2" t="s">
+      <c r="E9" s="1" t="s">
         <v>92</v>
       </c>
       <c r="F9" s="2" t="s">
@@ -1654,7 +1699,7 @@
       <c r="D10" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="E10" s="2" t="s">
+      <c r="E10" s="1" t="s">
         <v>98</v>
       </c>
       <c r="F10" s="2" t="s">
@@ -1692,7 +1737,7 @@
       <c r="D11" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="E11" s="2" t="s">
+      <c r="E11" s="1" t="s">
         <v>104</v>
       </c>
       <c r="F11" s="2" t="s">
@@ -1730,7 +1775,7 @@
       <c r="D12" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="E12" s="2" t="s">
+      <c r="E12" s="1" t="s">
         <v>109</v>
       </c>
       <c r="F12" s="2" t="s">
@@ -1768,7 +1813,7 @@
       <c r="D13" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="E13" s="2" t="s">
+      <c r="E13" s="1" t="s">
         <v>114</v>
       </c>
       <c r="F13" s="2" t="s">
@@ -1806,7 +1851,7 @@
       <c r="D14" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="E14" s="2" t="s">
+      <c r="E14" s="1" t="s">
         <v>120</v>
       </c>
       <c r="F14" s="2" t="s">
@@ -1876,7 +1921,7 @@
       <c r="D16" s="2" t="s">
         <v>132</v>
       </c>
-      <c r="E16" s="2" t="s">
+      <c r="E16" s="1" t="s">
         <v>133</v>
       </c>
       <c r="F16" s="2" t="s">
@@ -1914,7 +1959,7 @@
       <c r="D17" s="2" t="s">
         <v>140</v>
       </c>
-      <c r="E17" s="2" t="s">
+      <c r="E17" s="1" t="s">
         <v>141</v>
       </c>
       <c r="F17" s="2" t="s">
@@ -1952,7 +1997,7 @@
       <c r="D18" s="2" t="s">
         <v>147</v>
       </c>
-      <c r="E18" s="2" t="s">
+      <c r="E18" s="1" t="s">
         <v>148</v>
       </c>
       <c r="F18" s="2" t="s">
@@ -1990,7 +2035,7 @@
       <c r="D19" s="2" t="s">
         <v>154</v>
       </c>
-      <c r="E19" s="2" t="s">
+      <c r="E19" s="1" t="s">
         <v>155</v>
       </c>
       <c r="F19" s="2" t="s">
@@ -2028,7 +2073,7 @@
       <c r="D20" s="2" t="s">
         <v>160</v>
       </c>
-      <c r="E20" s="2" t="s">
+      <c r="E20" s="1" t="s">
         <v>161</v>
       </c>
       <c r="H20" s="2" t="s">
@@ -2060,7 +2105,7 @@
       <c r="D21" s="2" t="s">
         <v>164</v>
       </c>
-      <c r="E21" s="2" t="s">
+      <c r="E21" s="1" t="s">
         <v>165</v>
       </c>
       <c r="F21" s="2" t="s">
@@ -2095,9 +2140,7 @@
       <c r="D22" s="2" t="s">
         <v>187</v>
       </c>
-      <c r="E22" s="2" t="s">
-        <v>192</v>
-      </c>
+      <c r="E22" s="1"/>
       <c r="F22" s="2" t="s">
         <v>188</v>
       </c>
@@ -2114,10 +2157,48 @@
         <v>86</v>
       </c>
       <c r="L22" s="8" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="M22" t="s">
         <v>190</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" ht="96">
+      <c r="A23">
+        <v>401</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="C23" s="5" t="s">
+        <v>199</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="E23" s="10" t="s">
+        <v>201</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="I23" s="7" t="s">
+        <v>203</v>
+      </c>
+      <c r="J23" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="K23" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="L23" s="9" t="s">
+        <v>207</v>
+      </c>
+      <c r="M23" s="2" t="s">
+        <v>206</v>
       </c>
     </row>
   </sheetData>
@@ -2156,6 +2237,7 @@
     <hyperlink ref="I21" r:id="rId31" xr:uid="{32037A18-7380-4045-A4B0-FCA8B0774D4F}"/>
     <hyperlink ref="I22" r:id="rId32" xr:uid="{6F802D23-EF8F-E748-A152-E7AB9EBBC40B}"/>
     <hyperlink ref="I6" r:id="rId33" xr:uid="{7D690390-5CDC-774F-88F8-D0A10F74092B}"/>
+    <hyperlink ref="I23" r:id="rId34" xr:uid="{3487482B-705B-934F-B345-27830D949CFF}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/db/A7XLK-3201-RestaurantA7.xlsx
+++ b/db/A7XLK-3201-RestaurantA7.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10912"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11010"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wangtaichung/Documents/7_WebSite/7.11_CommunityWebSite/A7Xinlinkou4/db/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1EBC1F95-2906-304E-AC1F-311BB42EBEA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E2A10EE-580E-A048-B3DB-81323053257F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-780" yWindow="2500" windowWidth="39920" windowHeight="22540" xr2:uid="{EC3C71DD-AB41-7249-985D-4787F3B89605}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="39920" windowHeight="22540" xr2:uid="{EC3C71DD-AB41-7249-985D-4787F3B89605}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -900,6 +900,7 @@
   <si>
     <t>&lt;p&gt;
    資訊: &lt;a style="button" class="btn btn-info"  href="https://www.facebook.com/happyhihai/photos/p.118458333557627/118458333557627"&gt;菜單&lt;/a&gt; &amp;nbsp; 
+&lt;a style="button" class="btn btn-info"  href="https://himydream.me/2021/10/13/bistro/"&gt;推薦&lt;/a&gt;
 &lt;/p&gt;</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -2163,7 +2164,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="23" spans="1:13" ht="96">
+    <row r="23" spans="1:13" ht="128">
       <c r="A23">
         <v>401</v>
       </c>

--- a/db/A7XLK-3201-RestaurantA7.xlsx
+++ b/db/A7XLK-3201-RestaurantA7.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11010"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11114"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wangtaichung/Documents/7_WebSite/7.11_CommunityWebSite/A7Xinlinkou4/db/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E2A10EE-580E-A048-B3DB-81323053257F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F90AD7B9-C8AA-8D46-95EB-4689DDE6A399}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="39920" windowHeight="22540" xr2:uid="{EC3C71DD-AB41-7249-985D-4787F3B89605}"/>
+    <workbookView xWindow="6580" yWindow="4540" windowWidth="39920" windowHeight="22540" xr2:uid="{EC3C71DD-AB41-7249-985D-4787F3B89605}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="255" uniqueCount="208">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="265" uniqueCount="215">
   <si>
     <t>no</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -901,6 +901,37 @@
     <t>&lt;p&gt;
    資訊: &lt;a style="button" class="btn btn-info"  href="https://www.facebook.com/happyhihai/photos/p.118458333557627/118458333557627"&gt;菜單&lt;/a&gt; &amp;nbsp; 
 &lt;a style="button" class="btn btn-info"  href="https://himydream.me/2021/10/13/bistro/"&gt;推薦&lt;/a&gt;
+&lt;/p&gt;</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>108</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>我是早餐</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>桃園市龜山區長慶三街42號</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>03-327-3593</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>週二～週五: 06:00 - 12:00, 週六，日: 06:00 - 13:00, 週一公休</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>fig/XLK-321-RestaurantA7/A7XLK-3201-RestaurantA7-08.jpg</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;p&gt;
+   資訊: 
+&lt;a style="button" class="btn btn-info"  href="https://tcwang.github.io/A7Xinlinkou/fig/XLK-321-RestaurantA7/AiCity-950-我是早餐菜單.jpg"&gt;菜單&lt;/a&gt;
 &lt;/p&gt;</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -1322,7 +1353,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D43F91F4-866F-584C-A1A3-A0D1F56F484D}">
-  <dimension ref="A1:M23"/>
+  <dimension ref="A1:M24"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col min="3" max="3" width="10.1640625" customWidth="1"/>
@@ -1377,32 +1408,30 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:13" ht="192">
+    <row r="2" spans="1:13" ht="96">
       <c r="A2" s="1" t="s">
-        <v>59</v>
+        <v>208</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>12</v>
+        <v>209</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>14</v>
+        <v>210</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>15</v>
+        <v>211</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>16</v>
+        <v>212</v>
       </c>
       <c r="G2" s="2"/>
       <c r="H2" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="I2" s="3" t="s">
-        <v>51</v>
-      </c>
+        <v>213</v>
+      </c>
+      <c r="I2" s="2"/>
       <c r="J2" s="2" t="s">
         <v>18</v>
       </c>
@@ -1410,39 +1439,35 @@
         <v>57</v>
       </c>
       <c r="L2" s="4" t="s">
-        <v>184</v>
-      </c>
-      <c r="M2" s="3" t="s">
-        <v>52</v>
-      </c>
+        <v>214</v>
+      </c>
+      <c r="M2" s="2"/>
     </row>
-    <row r="3" spans="1:13" ht="128">
+    <row r="3" spans="1:13" ht="192">
       <c r="A3" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>24</v>
-      </c>
+        <v>16</v>
+      </c>
+      <c r="G3" s="2"/>
       <c r="H3" s="2" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>26</v>
+        <v>51</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>18</v>
@@ -1451,37 +1476,39 @@
         <v>57</v>
       </c>
       <c r="L3" s="4" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
-    <row r="4" spans="1:13" ht="96">
+    <row r="4" spans="1:13" ht="128">
       <c r="A4" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="G4" s="2"/>
+        <v>23</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>24</v>
+      </c>
       <c r="H4" s="2" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>18</v>
@@ -1490,37 +1517,37 @@
         <v>57</v>
       </c>
       <c r="L4" s="4" t="s">
-        <v>182</v>
-      </c>
-      <c r="M4" s="2"/>
+        <v>183</v>
+      </c>
+      <c r="M4" s="3" t="s">
+        <v>53</v>
+      </c>
     </row>
-    <row r="5" spans="1:13" ht="128">
+    <row r="5" spans="1:13" ht="96">
       <c r="A5" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>40</v>
-      </c>
+        <v>31</v>
+      </c>
+      <c r="G5" s="2"/>
       <c r="H5" s="2" t="s">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>18</v>
@@ -1529,37 +1556,37 @@
         <v>57</v>
       </c>
       <c r="L5" s="4" t="s">
-        <v>181</v>
-      </c>
-      <c r="M5" s="3" t="s">
-        <v>54</v>
-      </c>
+        <v>182</v>
+      </c>
+      <c r="M5" s="2"/>
     </row>
-    <row r="6" spans="1:13" ht="129">
+    <row r="6" spans="1:13" ht="128">
       <c r="A6" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>28</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="F6" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="G6" s="6"/>
+        <v>38</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>40</v>
+      </c>
       <c r="H6" s="2" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>193</v>
+        <v>42</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>18</v>
@@ -1568,111 +1595,112 @@
         <v>57</v>
       </c>
       <c r="L6" s="4" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
-    <row r="7" spans="1:13" ht="80">
+    <row r="7" spans="1:13" ht="129">
       <c r="A7" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>192</v>
+        <v>43</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="G7" s="2"/>
+        <v>45</v>
+      </c>
+      <c r="F7" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="G7" s="6"/>
       <c r="H7" s="2" t="s">
-        <v>88</v>
+        <v>47</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>48</v>
+        <v>18</v>
       </c>
       <c r="K7" s="2" t="s">
         <v>57</v>
       </c>
       <c r="L7" s="4" t="s">
-        <v>195</v>
-      </c>
-      <c r="M7" s="2"/>
+        <v>180</v>
+      </c>
+      <c r="M7" s="3" t="s">
+        <v>55</v>
+      </c>
     </row>
     <row r="8" spans="1:13" ht="80">
-      <c r="A8">
+      <c r="A8" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="G8" s="2"/>
+      <c r="H8" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="J8" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="K8" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="L8" s="4" t="s">
+        <v>195</v>
+      </c>
+      <c r="M8" s="2"/>
+    </row>
+    <row r="9" spans="1:13" ht="80">
+      <c r="A9">
         <v>501</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="B9" s="2" t="s">
         <v>65</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="H8" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="I8" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="J8" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="K8" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="L8" s="8" t="s">
-        <v>179</v>
-      </c>
-      <c r="M8" s="3" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13" ht="208">
-      <c r="A9">
-        <v>502</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>89</v>
       </c>
       <c r="C9" s="5" t="s">
         <v>66</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>91</v>
+        <v>67</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>93</v>
+        <v>68</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>85</v>
@@ -1681,36 +1709,36 @@
         <v>86</v>
       </c>
       <c r="L9" s="8" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
     </row>
-    <row r="10" spans="1:13" ht="80">
+    <row r="10" spans="1:13" ht="208">
       <c r="A10">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>28</v>
+        <v>66</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>85</v>
@@ -1719,36 +1747,36 @@
         <v>86</v>
       </c>
       <c r="L10" s="8" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
     </row>
     <row r="11" spans="1:13" ht="80">
       <c r="A11">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>66</v>
+        <v>28</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>135</v>
+        <v>99</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>85</v>
@@ -1757,36 +1785,36 @@
         <v>86</v>
       </c>
       <c r="L11" s="8" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
     </row>
-    <row r="12" spans="1:13" ht="192">
+    <row r="12" spans="1:13" ht="80">
       <c r="A12">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>28</v>
+        <v>66</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>110</v>
+        <v>135</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>85</v>
@@ -1795,36 +1823,36 @@
         <v>86</v>
       </c>
       <c r="L12" s="8" t="s">
-        <v>168</v>
+        <v>176</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
     </row>
     <row r="13" spans="1:13" ht="192">
       <c r="A13">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="C13" s="5" t="s">
         <v>28</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>134</v>
+        <v>110</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="I13" t="s">
-        <v>115</v>
+        <v>72</v>
+      </c>
+      <c r="I13" s="3" t="s">
+        <v>111</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>85</v>
@@ -1833,36 +1861,36 @@
         <v>86</v>
       </c>
       <c r="L13" s="8" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="M13" s="3" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
     </row>
-    <row r="14" spans="1:13" ht="144">
+    <row r="14" spans="1:13" ht="192">
       <c r="A14">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>66</v>
+        <v>28</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>121</v>
+        <v>134</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>122</v>
+        <v>73</v>
+      </c>
+      <c r="I14" t="s">
+        <v>115</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>85</v>
@@ -1870,34 +1898,37 @@
       <c r="K14" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="L14" s="4" t="s">
-        <v>170</v>
-      </c>
-      <c r="M14" t="s">
-        <v>118</v>
+      <c r="L14" s="8" t="s">
+        <v>169</v>
+      </c>
+      <c r="M14" s="3" t="s">
+        <v>113</v>
       </c>
     </row>
-    <row r="15" spans="1:13">
+    <row r="15" spans="1:13" ht="144">
       <c r="A15">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>123</v>
+        <v>116</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>125</v>
+        <v>66</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>126</v>
+        <v>119</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>120</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="I15" s="7" t="s">
-        <v>127</v>
+        <v>74</v>
+      </c>
+      <c r="I15" s="3" t="s">
+        <v>122</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>85</v>
@@ -1905,34 +1936,34 @@
       <c r="K15" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="M15" s="3" t="s">
-        <v>124</v>
+      <c r="L15" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="M15" t="s">
+        <v>118</v>
       </c>
     </row>
-    <row r="16" spans="1:13" ht="240">
+    <row r="16" spans="1:13">
       <c r="A16">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="E16" s="1" t="s">
-        <v>133</v>
+        <v>126</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>136</v>
+        <v>128</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="I16" t="s">
-        <v>137</v>
+        <v>75</v>
+      </c>
+      <c r="I16" s="7" t="s">
+        <v>127</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>85</v>
@@ -1940,37 +1971,34 @@
       <c r="K16" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="L16" s="4" t="s">
-        <v>171</v>
-      </c>
       <c r="M16" s="3" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
     </row>
-    <row r="17" spans="1:13" ht="176">
+    <row r="17" spans="1:13" ht="240">
       <c r="A17">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>138</v>
+        <v>129</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>28</v>
+        <v>130</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>140</v>
+        <v>132</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>141</v>
+        <v>133</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>142</v>
+        <v>136</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="I17" s="3" t="s">
-        <v>143</v>
+        <v>76</v>
+      </c>
+      <c r="I17" t="s">
+        <v>137</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>85</v>
@@ -1978,37 +2006,37 @@
       <c r="K17" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="L17" s="9" t="s">
-        <v>172</v>
+      <c r="L17" s="4" t="s">
+        <v>171</v>
       </c>
       <c r="M17" s="3" t="s">
-        <v>139</v>
+        <v>131</v>
       </c>
     </row>
-    <row r="18" spans="1:13" ht="144">
+    <row r="18" spans="1:13" ht="176">
       <c r="A18">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>145</v>
+        <v>28</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>148</v>
+        <v>141</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>149</v>
+        <v>142</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>150</v>
+        <v>143</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>85</v>
@@ -2017,36 +2045,36 @@
         <v>86</v>
       </c>
       <c r="L18" s="9" t="s">
-        <v>173</v>
-      </c>
-      <c r="M18" s="2" t="s">
-        <v>146</v>
+        <v>172</v>
+      </c>
+      <c r="M18" s="3" t="s">
+        <v>139</v>
       </c>
     </row>
-    <row r="19" spans="1:13" ht="304">
+    <row r="19" spans="1:13" ht="144">
       <c r="A19">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>154</v>
+        <v>147</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>155</v>
+        <v>148</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>156</v>
+        <v>149</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>157</v>
+        <v>150</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>85</v>
@@ -2055,30 +2083,36 @@
         <v>86</v>
       </c>
       <c r="L19" s="9" t="s">
-        <v>174</v>
-      </c>
-      <c r="M19" s="3" t="s">
-        <v>153</v>
+        <v>173</v>
+      </c>
+      <c r="M19" s="2" t="s">
+        <v>146</v>
       </c>
     </row>
-    <row r="20" spans="1:13" ht="96">
+    <row r="20" spans="1:13" ht="304">
       <c r="A20">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>159</v>
+        <v>151</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>34</v>
+        <v>152</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>161</v>
+        <v>155</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>156</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>157</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>85</v>
@@ -2087,36 +2121,30 @@
         <v>86</v>
       </c>
       <c r="L20" s="9" t="s">
-        <v>175</v>
-      </c>
-      <c r="M20" t="s">
-        <v>158</v>
+        <v>174</v>
+      </c>
+      <c r="M20" s="3" t="s">
+        <v>153</v>
       </c>
     </row>
-    <row r="21" spans="1:13">
+    <row r="21" spans="1:13" ht="96">
       <c r="A21">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>130</v>
+        <v>34</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>165</v>
-      </c>
-      <c r="F21" s="2" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="I21" s="3" t="s">
-        <v>167</v>
+        <v>81</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>85</v>
@@ -2124,32 +2152,37 @@
       <c r="K21" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="M21" s="3" t="s">
-        <v>163</v>
+      <c r="L21" s="9" t="s">
+        <v>175</v>
+      </c>
+      <c r="M21" t="s">
+        <v>158</v>
       </c>
     </row>
-    <row r="22" spans="1:13" ht="96">
+    <row r="22" spans="1:13">
       <c r="A22">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>186</v>
+        <v>162</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>185</v>
+        <v>130</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>187</v>
-      </c>
-      <c r="E22" s="1"/>
+        <v>164</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>165</v>
+      </c>
       <c r="F22" s="2" t="s">
-        <v>188</v>
+        <v>166</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>191</v>
-      </c>
-      <c r="I22" s="7" t="s">
-        <v>189</v>
+        <v>82</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>167</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>85</v>
@@ -2157,88 +2190,121 @@
       <c r="K22" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="L22" s="8" t="s">
+      <c r="M22" s="3" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" ht="96">
+      <c r="A23">
+        <v>515</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="C23" s="5" t="s">
+        <v>185</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="E23" s="1"/>
+      <c r="F23" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="I23" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="J23" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="K23" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="L23" s="8" t="s">
         <v>196</v>
       </c>
-      <c r="M22" t="s">
+      <c r="M23" t="s">
         <v>190</v>
       </c>
     </row>
-    <row r="23" spans="1:13" ht="128">
-      <c r="A23">
+    <row r="24" spans="1:13" ht="128">
+      <c r="A24">
         <v>401</v>
       </c>
-      <c r="B23" s="2" t="s">
+      <c r="B24" s="2" t="s">
         <v>198</v>
       </c>
-      <c r="C23" s="5" t="s">
+      <c r="C24" s="5" t="s">
         <v>199</v>
       </c>
-      <c r="D23" s="2" t="s">
+      <c r="D24" s="2" t="s">
         <v>200</v>
       </c>
-      <c r="E23" s="10" t="s">
+      <c r="E24" s="10" t="s">
         <v>201</v>
       </c>
-      <c r="F23" s="2" t="s">
+      <c r="F24" s="2" t="s">
         <v>202</v>
       </c>
-      <c r="H23" s="2" t="s">
+      <c r="H24" s="2" t="s">
         <v>205</v>
       </c>
-      <c r="I23" s="7" t="s">
+      <c r="I24" s="7" t="s">
         <v>203</v>
       </c>
-      <c r="J23" s="2" t="s">
+      <c r="J24" s="2" t="s">
         <v>204</v>
       </c>
-      <c r="K23" s="2" t="s">
+      <c r="K24" s="2" t="s">
         <v>197</v>
       </c>
-      <c r="L23" s="9" t="s">
+      <c r="L24" s="9" t="s">
         <v>207</v>
       </c>
-      <c r="M23" s="2" t="s">
+      <c r="M24" s="2" t="s">
         <v>206</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="I3" r:id="rId1" xr:uid="{C4FC3919-D074-B04C-8404-BC6DE733F558}"/>
-    <hyperlink ref="I4" r:id="rId2" xr:uid="{F003A365-8C23-084B-B31A-663E82D27E11}"/>
-    <hyperlink ref="G5" r:id="rId3" xr:uid="{7AEBC60D-47CB-2041-BB0C-5BB638DE9DEC}"/>
-    <hyperlink ref="I5" r:id="rId4" xr:uid="{E2777161-F973-9B42-BC21-88DA80C19FD3}"/>
-    <hyperlink ref="I7" r:id="rId5" xr:uid="{240368C4-8A23-D049-BE75-A45A65EB147A}"/>
-    <hyperlink ref="M2" r:id="rId6" xr:uid="{2E20CE02-8C51-1045-B84E-5304199A5CEC}"/>
-    <hyperlink ref="M3" r:id="rId7" xr:uid="{21CC0B31-826D-6549-8434-94B01CACE62D}"/>
-    <hyperlink ref="M5" r:id="rId8" xr:uid="{24019989-F9BD-E143-A40C-50EE4DDF5BD1}"/>
-    <hyperlink ref="M6" r:id="rId9" display="https://www.google.com.tw/maps/place/%E5%8A%89%E5%A6%B9%E9%8D%8B%E7%87%92%E6%84%8F%E9%BA%B5-%E6%A1%83%E5%9C%92%E6%9E%97%E5%8F%A3%E5%BA%97/@25.0548468,121.3827894,19.1z/data=!4m5!3m4!1s0x3442a7b02079176f:0x78906ae51c7f6abc!8m2!3d25.0553573!4d121.3840157?hl=zh-TW&amp;authuser=0" xr:uid="{13C7C2D5-34CD-404D-BEE1-B9C104B3C41D}"/>
-    <hyperlink ref="I8" r:id="rId10" xr:uid="{D22B71CE-BEE8-4D4A-B73B-DF696843091A}"/>
-    <hyperlink ref="M8" r:id="rId11" display="https://www.google.com.tw/maps/place/%E8%83%96%E8%80%81%E7%88%B9%E7%BE%8E%E5%BC%8F%E7%82%B8%E9%9B%9EA7%E6%96%87%E9%9D%92%E5%BA%97/@25.0394257,121.3894157,19.83z/data=!4m5!3m4!1s0x3442a73165d8f2d3:0xce822b237485dc8c!8m2!3d25.0394354!4d121.3903716?hl=zh-TW&amp;authuser=0" xr:uid="{C64399C5-4BBF-C54B-AFFF-C515FF32551F}"/>
-    <hyperlink ref="M9" r:id="rId12" display="https://www.google.com.tw/maps/place/%E8%B6%A3%E5%95%83%E7%82%B8%E7%89%A9-%E6%96%87%E9%9D%92%E5%BA%97/@25.039422,121.389821,19z/data=!4m9!1m2!2m1!1z6Laj5ZWD54K454mpQTfmlofpnZLlupc!3m5!1s0x3442a79257c7d5e1:0x96b9a8c7ea325295!8m2!3d25.0394086!4d121.3903675!15sChfotqPllYPngrjnialBN-aWh-mdkuW6l1ogIh7otqMg5ZWDIOeCuCDniakgYTcg5paHIOmdkiDlupeSAQRkZWxp?hl=zh-TW&amp;authuser=0" xr:uid="{ECDBCB9E-1A0B-2440-BEDC-B3365ABCEB46}"/>
-    <hyperlink ref="I9" r:id="rId13" xr:uid="{C84B02C1-9D57-3449-BF10-8BF8B150E1B0}"/>
-    <hyperlink ref="M10" r:id="rId14" display="https://www.google.com.tw/maps/place/MQ%E5%85%83%E6%B0%A3house/@25.0396043,121.3889924,19z/data=!4m9!1m2!2m1!1z5YWD5rCj5pep5Y2I6aSQQTfmlofpnZLlupc!3m5!1s0x3442a73b0be03237:0xb76fc65b93d291de!8m2!3d25.0395543!4d121.389809!15sChrlhYPmsKPml6nljYjppJBBN-aWh-mdkuW6lyIDiAEBWh4iHOWFg-awoyDml6kg5Y2I6aSQIGE3IOaWhyDpnZKSARRicmVha2Zhc3RfcmVzdGF1cmFudJoBJENoZERTVWhOTUc5blMwVkpRMEZuU1VSTE1tSjJWbWRCUlJBQg?hl=zh-TW&amp;authuser=0" xr:uid="{A608DFF8-5556-A348-BCCF-DF8FED89A676}"/>
-    <hyperlink ref="I10" r:id="rId15" xr:uid="{2AC2704D-3B90-7143-8538-1BCF2601B133}"/>
-    <hyperlink ref="M11" r:id="rId16" xr:uid="{BCFDF63E-46D6-4C46-A895-F2BE3AF3A43C}"/>
-    <hyperlink ref="I11" r:id="rId17" xr:uid="{DA402F63-BBBF-314A-9282-201C2F50A8E9}"/>
-    <hyperlink ref="M12" r:id="rId18" xr:uid="{62B3945D-7D85-6F41-B0AE-685C751A1E0D}"/>
-    <hyperlink ref="I12" r:id="rId19" xr:uid="{CF45B8DE-914A-2B48-BCB7-14602F96BD36}"/>
-    <hyperlink ref="M13" r:id="rId20" display="https://www.google.com.tw/maps/place/W%E3%80%82D%E6%88%91%E7%9A%84%E6%97%A9%E9%A4%90/@25.039828,121.3881883,18z/data=!4m9!1m2!2m1!1zV0TmiJHnmoTml6nppJAgQTfmlofpnZLlupc!3m5!1s0x3442a771fa73353d:0x329428879337e9d8!8m2!3d25.0396834!4d121.38925!15sChpXROaIkeeahOaXqemkkCBBN-aWh-mdkuW6l1oeIhx3ZCDmiJEg55qEIOaXqemkkCBhNyDmlocg6Z2SkgEUYnJlYWtmYXN0X3Jlc3RhdXJhbnSaASNDaFpEU1VoTk1HOW5TMFZKUTBGblNVUk5iMlZYVDFoUkVBRQ?hl=zh-TW&amp;authuser=0" xr:uid="{1A766ADC-BF5A-F54B-8857-2EC343131663}"/>
-    <hyperlink ref="I14" r:id="rId21" xr:uid="{D29C3BC2-9385-1848-8CD3-329B3FEC96D0}"/>
-    <hyperlink ref="M15" r:id="rId22" display="https://www.google.com.tw/maps/place/%E9%BA%B5%E9%A4%93%E5%BF%83%E8%86%B3italiana%E7%BE%A9%E5%BC%8F%E6%96%99%E7%90%86/@25.0399443,121.3879522,18z/data=!3m1!4b1!4m5!3m4!1s0x3442a771fefa1693:0x3751e2ae6c6a4c1b!8m2!3d25.0399443!4d121.3890492?hl=zh-TW&amp;authuser=0" xr:uid="{CFA5CDA3-DFA0-A345-802E-4E27D0DD6388}"/>
-    <hyperlink ref="I15" r:id="rId23" xr:uid="{52227806-B293-3140-BA54-19D8D37B7072}"/>
-    <hyperlink ref="M16" r:id="rId24" display="https://www.google.com.tw/maps/place/%E9%BC%8E%E8%A8%98+%E5%B0%8F%E7%B1%A0%E5%8C%85/@25.0394911,121.3880801,18z/data=!4m9!1m2!2m1!1z6byO6KiY5bCP57Gg5YyFIEE35paH6Z2S5bqX!3m5!1s0x3442a771eb8a1057:0x50474f8ab9f0306d!8m2!3d25.0399461!4d121.3891357!15sChvpvI7oqJjlsI_nsaDljIUgQTfmlofpnZLlupdaJCIi6byOIOiomCDlsI8g57GgIOWMhSBhNyDmlocg6Z2SIOW6l5IBCnJlc3RhdXJhbnSaASRDaGREU1VoTk1HOW5TMFZKUTBGblNVUlZORjlEZFd4blJSQUI?hl=zh-TW&amp;authuser=0" xr:uid="{40D2FFA0-1BA7-7D40-9492-E31751F5971E}"/>
-    <hyperlink ref="M17" r:id="rId25" display="https://www.google.com.tw/maps/place/%E6%B2%88%E5%AE%B6%E8%B1%86%E6%BC%BF/@25.0400428,121.3880621,18z/data=!4m9!1m2!2m1!1z5rKI5a626LGG5ry_IEE35paH6Z2S5bqX!3m5!1s0x3442a7e71b4fdbef:0xa7327c25e217658c!8m2!3d25.0398612!4d121.3890308!15sChjmsojlrrbosYbmvL8gQTfmlofpnZLlupdaGyIZ5rKIIOWutiDosYbmvL8gYTcg5paHIOmdkpIBFGJyZWFrZmFzdF9yZXN0YXVyYW50mgEkQ2hkRFNVaE5NRzluUzBWSlEwRm5TVU5qYWpkRU1HbFJSUkFC?hl=zh-TW&amp;authuser=0" xr:uid="{5BED3BAC-7517-6C44-8DD0-2E9AAD01210B}"/>
-    <hyperlink ref="I17" r:id="rId26" xr:uid="{FA94FB62-C3B4-F440-B546-D5651C4C1EF0}"/>
-    <hyperlink ref="I18" r:id="rId27" xr:uid="{36593C4B-5784-D647-A021-407E9C5E9859}"/>
-    <hyperlink ref="M19" r:id="rId28" xr:uid="{C10E1D29-46CE-4843-8B5F-0C73F3E21715}"/>
-    <hyperlink ref="I19" r:id="rId29" xr:uid="{4108B3FA-F736-964B-AFA8-8EA10E9958B5}"/>
-    <hyperlink ref="M21" r:id="rId30" xr:uid="{98E56C55-CA1A-F648-87ED-05DD4AEF5C71}"/>
-    <hyperlink ref="I21" r:id="rId31" xr:uid="{32037A18-7380-4045-A4B0-FCA8B0774D4F}"/>
-    <hyperlink ref="I22" r:id="rId32" xr:uid="{6F802D23-EF8F-E748-A152-E7AB9EBBC40B}"/>
-    <hyperlink ref="I6" r:id="rId33" xr:uid="{7D690390-5CDC-774F-88F8-D0A10F74092B}"/>
-    <hyperlink ref="I23" r:id="rId34" xr:uid="{3487482B-705B-934F-B345-27830D949CFF}"/>
+    <hyperlink ref="I4" r:id="rId1" xr:uid="{C4FC3919-D074-B04C-8404-BC6DE733F558}"/>
+    <hyperlink ref="I5" r:id="rId2" xr:uid="{F003A365-8C23-084B-B31A-663E82D27E11}"/>
+    <hyperlink ref="G6" r:id="rId3" xr:uid="{7AEBC60D-47CB-2041-BB0C-5BB638DE9DEC}"/>
+    <hyperlink ref="I6" r:id="rId4" xr:uid="{E2777161-F973-9B42-BC21-88DA80C19FD3}"/>
+    <hyperlink ref="I8" r:id="rId5" xr:uid="{240368C4-8A23-D049-BE75-A45A65EB147A}"/>
+    <hyperlink ref="M3" r:id="rId6" xr:uid="{2E20CE02-8C51-1045-B84E-5304199A5CEC}"/>
+    <hyperlink ref="M4" r:id="rId7" xr:uid="{21CC0B31-826D-6549-8434-94B01CACE62D}"/>
+    <hyperlink ref="M6" r:id="rId8" xr:uid="{24019989-F9BD-E143-A40C-50EE4DDF5BD1}"/>
+    <hyperlink ref="M7" r:id="rId9" display="https://www.google.com.tw/maps/place/%E5%8A%89%E5%A6%B9%E9%8D%8B%E7%87%92%E6%84%8F%E9%BA%B5-%E6%A1%83%E5%9C%92%E6%9E%97%E5%8F%A3%E5%BA%97/@25.0548468,121.3827894,19.1z/data=!4m5!3m4!1s0x3442a7b02079176f:0x78906ae51c7f6abc!8m2!3d25.0553573!4d121.3840157?hl=zh-TW&amp;authuser=0" xr:uid="{13C7C2D5-34CD-404D-BEE1-B9C104B3C41D}"/>
+    <hyperlink ref="I9" r:id="rId10" xr:uid="{D22B71CE-BEE8-4D4A-B73B-DF696843091A}"/>
+    <hyperlink ref="M9" r:id="rId11" display="https://www.google.com.tw/maps/place/%E8%83%96%E8%80%81%E7%88%B9%E7%BE%8E%E5%BC%8F%E7%82%B8%E9%9B%9EA7%E6%96%87%E9%9D%92%E5%BA%97/@25.0394257,121.3894157,19.83z/data=!4m5!3m4!1s0x3442a73165d8f2d3:0xce822b237485dc8c!8m2!3d25.0394354!4d121.3903716?hl=zh-TW&amp;authuser=0" xr:uid="{C64399C5-4BBF-C54B-AFFF-C515FF32551F}"/>
+    <hyperlink ref="M10" r:id="rId12" display="https://www.google.com.tw/maps/place/%E8%B6%A3%E5%95%83%E7%82%B8%E7%89%A9-%E6%96%87%E9%9D%92%E5%BA%97/@25.039422,121.389821,19z/data=!4m9!1m2!2m1!1z6Laj5ZWD54K454mpQTfmlofpnZLlupc!3m5!1s0x3442a79257c7d5e1:0x96b9a8c7ea325295!8m2!3d25.0394086!4d121.3903675!15sChfotqPllYPngrjnialBN-aWh-mdkuW6l1ogIh7otqMg5ZWDIOeCuCDniakgYTcg5paHIOmdkiDlupeSAQRkZWxp?hl=zh-TW&amp;authuser=0" xr:uid="{ECDBCB9E-1A0B-2440-BEDC-B3365ABCEB46}"/>
+    <hyperlink ref="I10" r:id="rId13" xr:uid="{C84B02C1-9D57-3449-BF10-8BF8B150E1B0}"/>
+    <hyperlink ref="M11" r:id="rId14" display="https://www.google.com.tw/maps/place/MQ%E5%85%83%E6%B0%A3house/@25.0396043,121.3889924,19z/data=!4m9!1m2!2m1!1z5YWD5rCj5pep5Y2I6aSQQTfmlofpnZLlupc!3m5!1s0x3442a73b0be03237:0xb76fc65b93d291de!8m2!3d25.0395543!4d121.389809!15sChrlhYPmsKPml6nljYjppJBBN-aWh-mdkuW6lyIDiAEBWh4iHOWFg-awoyDml6kg5Y2I6aSQIGE3IOaWhyDpnZKSARRicmVha2Zhc3RfcmVzdGF1cmFudJoBJENoZERTVWhOTUc5blMwVkpRMEZuU1VSTE1tSjJWbWRCUlJBQg?hl=zh-TW&amp;authuser=0" xr:uid="{A608DFF8-5556-A348-BCCF-DF8FED89A676}"/>
+    <hyperlink ref="I11" r:id="rId15" xr:uid="{2AC2704D-3B90-7143-8538-1BCF2601B133}"/>
+    <hyperlink ref="M12" r:id="rId16" xr:uid="{BCFDF63E-46D6-4C46-A895-F2BE3AF3A43C}"/>
+    <hyperlink ref="I12" r:id="rId17" xr:uid="{DA402F63-BBBF-314A-9282-201C2F50A8E9}"/>
+    <hyperlink ref="M13" r:id="rId18" xr:uid="{62B3945D-7D85-6F41-B0AE-685C751A1E0D}"/>
+    <hyperlink ref="I13" r:id="rId19" xr:uid="{CF45B8DE-914A-2B48-BCB7-14602F96BD36}"/>
+    <hyperlink ref="M14" r:id="rId20" display="https://www.google.com.tw/maps/place/W%E3%80%82D%E6%88%91%E7%9A%84%E6%97%A9%E9%A4%90/@25.039828,121.3881883,18z/data=!4m9!1m2!2m1!1zV0TmiJHnmoTml6nppJAgQTfmlofpnZLlupc!3m5!1s0x3442a771fa73353d:0x329428879337e9d8!8m2!3d25.0396834!4d121.38925!15sChpXROaIkeeahOaXqemkkCBBN-aWh-mdkuW6l1oeIhx3ZCDmiJEg55qEIOaXqemkkCBhNyDmlocg6Z2SkgEUYnJlYWtmYXN0X3Jlc3RhdXJhbnSaASNDaFpEU1VoTk1HOW5TMFZKUTBGblNVUk5iMlZYVDFoUkVBRQ?hl=zh-TW&amp;authuser=0" xr:uid="{1A766ADC-BF5A-F54B-8857-2EC343131663}"/>
+    <hyperlink ref="I15" r:id="rId21" xr:uid="{D29C3BC2-9385-1848-8CD3-329B3FEC96D0}"/>
+    <hyperlink ref="M16" r:id="rId22" display="https://www.google.com.tw/maps/place/%E9%BA%B5%E9%A4%93%E5%BF%83%E8%86%B3italiana%E7%BE%A9%E5%BC%8F%E6%96%99%E7%90%86/@25.0399443,121.3879522,18z/data=!3m1!4b1!4m5!3m4!1s0x3442a771fefa1693:0x3751e2ae6c6a4c1b!8m2!3d25.0399443!4d121.3890492?hl=zh-TW&amp;authuser=0" xr:uid="{CFA5CDA3-DFA0-A345-802E-4E27D0DD6388}"/>
+    <hyperlink ref="I16" r:id="rId23" xr:uid="{52227806-B293-3140-BA54-19D8D37B7072}"/>
+    <hyperlink ref="M17" r:id="rId24" display="https://www.google.com.tw/maps/place/%E9%BC%8E%E8%A8%98+%E5%B0%8F%E7%B1%A0%E5%8C%85/@25.0394911,121.3880801,18z/data=!4m9!1m2!2m1!1z6byO6KiY5bCP57Gg5YyFIEE35paH6Z2S5bqX!3m5!1s0x3442a771eb8a1057:0x50474f8ab9f0306d!8m2!3d25.0399461!4d121.3891357!15sChvpvI7oqJjlsI_nsaDljIUgQTfmlofpnZLlupdaJCIi6byOIOiomCDlsI8g57GgIOWMhSBhNyDmlocg6Z2SIOW6l5IBCnJlc3RhdXJhbnSaASRDaGREU1VoTk1HOW5TMFZKUTBGblNVUlZORjlEZFd4blJSQUI?hl=zh-TW&amp;authuser=0" xr:uid="{40D2FFA0-1BA7-7D40-9492-E31751F5971E}"/>
+    <hyperlink ref="M18" r:id="rId25" display="https://www.google.com.tw/maps/place/%E6%B2%88%E5%AE%B6%E8%B1%86%E6%BC%BF/@25.0400428,121.3880621,18z/data=!4m9!1m2!2m1!1z5rKI5a626LGG5ry_IEE35paH6Z2S5bqX!3m5!1s0x3442a7e71b4fdbef:0xa7327c25e217658c!8m2!3d25.0398612!4d121.3890308!15sChjmsojlrrbosYbmvL8gQTfmlofpnZLlupdaGyIZ5rKIIOWutiDosYbmvL8gYTcg5paHIOmdkpIBFGJyZWFrZmFzdF9yZXN0YXVyYW50mgEkQ2hkRFNVaE5NRzluUzBWSlEwRm5TVU5qYWpkRU1HbFJSUkFC?hl=zh-TW&amp;authuser=0" xr:uid="{5BED3BAC-7517-6C44-8DD0-2E9AAD01210B}"/>
+    <hyperlink ref="I18" r:id="rId26" xr:uid="{FA94FB62-C3B4-F440-B546-D5651C4C1EF0}"/>
+    <hyperlink ref="I19" r:id="rId27" xr:uid="{36593C4B-5784-D647-A021-407E9C5E9859}"/>
+    <hyperlink ref="M20" r:id="rId28" xr:uid="{C10E1D29-46CE-4843-8B5F-0C73F3E21715}"/>
+    <hyperlink ref="I20" r:id="rId29" xr:uid="{4108B3FA-F736-964B-AFA8-8EA10E9958B5}"/>
+    <hyperlink ref="M22" r:id="rId30" xr:uid="{98E56C55-CA1A-F648-87ED-05DD4AEF5C71}"/>
+    <hyperlink ref="I22" r:id="rId31" xr:uid="{32037A18-7380-4045-A4B0-FCA8B0774D4F}"/>
+    <hyperlink ref="I23" r:id="rId32" xr:uid="{6F802D23-EF8F-E748-A152-E7AB9EBBC40B}"/>
+    <hyperlink ref="I7" r:id="rId33" xr:uid="{7D690390-5CDC-774F-88F8-D0A10F74092B}"/>
+    <hyperlink ref="I24" r:id="rId34" xr:uid="{3487482B-705B-934F-B345-27830D949CFF}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/db/A7XLK-3201-RestaurantA7.xlsx
+++ b/db/A7XLK-3201-RestaurantA7.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11114"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10520"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wangtaichung/Documents/7_WebSite/7.11_CommunityWebSite/A7Xinlinkou4/db/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wangtaizhong/Documents/92_WebSite/A7Xinlinkou/db/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F90AD7B9-C8AA-8D46-95EB-4689DDE6A399}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1D62811-DD59-3849-A25C-7A7A68C31177}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6580" yWindow="4540" windowWidth="39920" windowHeight="22540" xr2:uid="{EC3C71DD-AB41-7249-985D-4787F3B89605}"/>
+    <workbookView xWindow="-1540" yWindow="2200" windowWidth="27940" windowHeight="17500" xr2:uid="{EC3C71DD-AB41-7249-985D-4787F3B89605}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="265" uniqueCount="215">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="223">
   <si>
     <t>no</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -228,14 +228,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>桃園市龜山區長庚里長慶二街69號1樓</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">0900-261-520 </t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>https://www.facebook.com/%E8%8A%AC%E4%BA%AB%E7%BE%8E%E5%91%B3%E9%A4%90%E9%A4%A8-107527327690284/?ref=page_internal</t>
   </si>
   <si>
@@ -259,14 +251,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>1.樂善國小生活圈</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>週一～週五: 10:00 - 14:00, 17:00 - 20:30, 週六: 10:00 - 14:00, 週日公休</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>101</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -364,10 +348,6 @@
   </si>
   <si>
     <t>https://www.google.com.tw/maps/place/%E8%83%96%E8%80%81%E7%88%B9%E7%BE%8E%E5%BC%8F%E7%82%B8%E9%9B%9EA7%E6%96%87%E9%9D%92%E5%BA%97/@25.0394257,121.3894157,19.83z/data=!4m5!3m4!1s0x3442a73165d8f2d3:0xce822b237485dc8c!8m2!3d25.0394354!4d121.3903716?hl=zh-TW&amp;authuser=0</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>fig/XLK-321-RestaurantA7/A7XLK-3201-RestaurantA7-07.jpg</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -833,74 +813,12 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>弈膳の便當</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>https://www.liu-mei.com.tw/taste.php</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://www.facebook.com/A0900261520/</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>&lt;p&gt;
-   資訊: &lt;a style="button" class="btn btn-info"  href="fig/XLK-321-RestaurantA7/AiCity-952-奕膳便當-701.jpg"&gt;菜單&lt;/a&gt; 
-  &lt;br&gt;試營運優惠期間為期兩週（8/7-8/22）
-&lt;/p&gt;</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>&lt;p&gt;
    資訊: &lt;a style="button" class="btn btn-info"  href="https://almablog.com.tw/blog/post/172302?fbclid=IwAR1Pl7ShDJeMe7m5BngujgTMXJTa0GuJ-Lq8MORepEuNKUwcvMCORzjZGYk"&gt;推薦&lt;/a&gt; &amp;nbsp;&amp;nbsp;
-&lt;/p&gt;</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>4.中心商業區</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>海海人生餐酒館</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>酒館</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>桃園市龜山區桃園市龜山區樂善一路500之1號</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>0989-020-867</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>週3~5: 17:00 - 23:00, 週6～日：12:00 - 23:00</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://www.facebook.com/happyhihai/</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>樂善一路</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>fig/XLK-321-RestaurantA7/A7XLK-3206-海海人生-01.jpg</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://www.google.com.tw/maps/place/%E6%B5%B7%E6%B5%B7%E4%BA%BA%E7%94%9F%E9%A4%90%E9%85%92%E9%A4%A8-%E9%BE%9C%E5%B1%B1%E7%89%B9%E8%89%B2%E5%92%96%E5%95%A1%E5%BB%B3%7C%E8%81%9A%E9%A4%90%E6%8E%A8%E8%96%A6%7C%E6%85%B6%E7%94%9F%E9%A4%90%E5%BB%B3%7C%E7%86%B1%E9%96%80%E9%A4%90%E9%85%92%E9%A4%A8%7C%E6%8E%A8%E8%96%A6%E7%BE%8E%E5%BC%8F%E9%A4%90%E5%BB%B3%7C%E7%B4%84%E6%9C%83%E9%A4%90%E5%BB%B3/@25.0473364,121.3840045,17z/data=!4m5!3m4!1s0x3442a78eb45ea4ff:0x4474aec40a10127e!8m2!3d25.0471227!4d121.3875512?hl=zh-TW&amp;authuser=0</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>&lt;p&gt;
-   資訊: &lt;a style="button" class="btn btn-info"  href="https://www.facebook.com/happyhihai/photos/p.118458333557627/118458333557627"&gt;菜單&lt;/a&gt; &amp;nbsp; 
-&lt;a style="button" class="btn btn-info"  href="https://himydream.me/2021/10/13/bistro/"&gt;推薦&lt;/a&gt;
 &lt;/p&gt;</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -934,6 +852,122 @@
 &lt;a style="button" class="btn btn-info"  href="https://tcwang.github.io/A7Xinlinkou/fig/XLK-321-RestaurantA7/AiCity-950-我是早餐菜單.jpg"&gt;菜單&lt;/a&gt;
 &lt;/p&gt;</t>
     <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.樂善國小區</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>馬祖奶茶</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>飲料店</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>桃園市龜山區樂善二路215號</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>03-327-1053</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>週一～五: 10:30 - 20:20, 週六: 10:30 - 21:00, 週日: 10:30 - 19:00</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.facebook.com/%E9%A6%AC%E7%A5%96%E5%A5%B6%E8%8C%B6-%E9%BE%9C%E5%B1%B1%E6%A8%82%E5%96%84%E9%87%91%E6%8D%B7%E5%BA%97-104799568807318/</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>樂善二路</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;p&gt;
+   資訊: &lt;a style="button" class="btn btn-info"  href="https://www.facebook.com/104799568807318/photos/p.104839538803321/104839538803321"&gt;菜單&lt;/a&gt; &amp;nbsp; 
+&lt;a style="button" class="btn btn-info"  href="https://www.google.com.tw/search?q=%E9%A6%AC%E7%A5%96%E5%A5%B6%E8%8C%B6-%E6%A8%82%E5%96%84%E9%87%91%E6%8D%B7%E5%BA%97&amp;sxsrf=ALiCzsb_gbTsVJNp7ujnOaC2bYmU1Jbt3Q:1653800340702&amp;tbm=isch&amp;source=iu&amp;ictx=1&amp;vet=1&amp;fir=cf_mAwmATRvSZM%252CnemNJ_W9jrZqxM%252C_%253BmMoG4kI9JCH5NM%252CB-s64GdoVWUOBM%252C_%253ByFZXoNufqOrtgM%252CB-s64GdoVWUOBM%252C_%253B-Bw_Lc7NKCQg2M%252CB-s64GdoVWUOBM%252C_%253BFWHod__zxTLG1M%252Cpj5AWC77DfnEZM%252C_%253BIO_rvIfe2KOVLM%252CbdB6K4xvkPEKZM%252C_%253B9kl79PyfOApIKM%252CvGGX15WT-k1FaM%252C_%253BCcjK3KJoWb45wM%252CSSy2w-x1hfCXaM%252C_%253Bav42WUkDU9dHcM%252CxgVIzyTS31d0TM%252C_%253BTmhiC6c5CbOD6M%252CctH6rIOXnLyWVM%252C_&amp;usg=AI4_-kQXFL6MXgVNe_VAmXhj2YWgiojaLA&amp;sa=X&amp;ved=2ahUKEwjP39iu9oP4AhWOA6YKHdojCoYQ9QF6BAgXEAE#imgrc=cf_mAwmATRvSZM"&gt;圖片&lt;/a&gt;
+&lt;/p&gt;</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://goo.gl/maps/aG7tAH28F1mjfzqu7</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>早早點炭火三明治</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.google.com.tw/maps/place/%E6%97%A9%E6%97%A9%E9%BB%9E%E7%82%AD%E7%81%AB%E4%B8%89%E6%98%8E%E6%B2%BB/@25.0465716,121.3821609,17z/data=!3m1!4b1!4m5!3m4!1s0x3442a710757d3045:0xd7e7f36d6f4ee8a3!8m2!3d25.0465716!4d121.3843496?hl=zh-TW</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>桃園市龜山區樂善二路201號</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>03-327-2772</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>週一～五: 06:00 - 14:00, 週六日: 06:00-15:00</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.facebook.com/groups/3102206776730468/?ref=share</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;p&gt;
+   資訊: &lt;a style="button" class="btn btn-info"  href="https://www.ubereats.com/tw/store/%E6%97%A9%E6%97%A9%E9%BB%9E%E7%82%AD%E7%81%AB%E4%B8%89%E6%98%8E%E6%B2%BB/2uoTMVvsWSO5glewU92HhQ?diningMode=DELIVERY&amp;pl=JTdCJTIyYWRkcmVzcyUyMiUzQSUyMkphZGUlMjBEeW5hc3R5JTIyJTJDJTIycmVmZXJlbmNlJTIyJTNBJTIyZjgyZTA1YTItODE2NS0xMGU4LWQ3M2QtNDMwYzIyOWY5MjA4JTIyJTJDJTIycmVmZXJlbmNlVHlwZSUyMiUzQSUyMnViZXJfcGxhY2VzJTIyJTJDJTIybGF0aXR1ZGUlMjIlM0E0OS4yODAzOSUyQyUyMmxvbmdpdHVkZSUyMiUzQS0xMjMuMTAxMjglN0Q%3D&amp;utm_campaign=place-action-link&amp;utm_medium=organic&amp;utm_source=google"&gt;外送&lt;/a&gt; &amp;nbsp;&amp;nbsp;
+ &lt;a style="button" class="btn btn-info"  href="https://goo.gl/maps/uUppg3sd5zo3sk4EA"&gt;菜單&lt;/a&gt; &amp;nbsp; 
+&lt;/p&gt;</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>fig/XLK-321-RestaurantA7/A7XLK-3203-A7Restaurant-01.jpeg</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>fig/XLK-321-RestaurantA7/A7XLK-3203-A7Restaurant-02.jpeg</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>便當製造所</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>桃園市龜山區長庚里長慶二街71號1樓</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.google.com.tw/maps/place/%E4%BE%BF%E7%95%B6%E8%A3%BD%E9%80%A0%E6%89%80/@25.0543673,121.3814909,17z/data=!3m1!4b1!4m5!3m4!1s0x3442a707df663089:0x67f11136d812d17d!8m2!3d25.0543625!4d121.3836796?hl=zh-TW&amp;authuser=0</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>0909-990-187</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>週一～週五: 09:00 - 19:00, 週日公休</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;p&gt;
+   資訊: &lt;a style="button" class="btn btn-info"  href="https://www.ubereats.com/tw/store/%E4%BE%BF%E7%95%B6%E8%A3%BD%E9%80%A0%E6%89%80/eCMjXbmdXEq5H5uSGMCn8A?diningMode=DELIVERY&amp;pl=JTdCJTIyYWRkcmVzcyUyMiUzQSUyMkphZGUlMjBEeW5hc3R5JTIyJTJDJTIycmVmZXJlbmNlJTIyJTNBJTIyZjgyZTA1YTItODE2NS0xMGU4LWQ3M2QtNDMwYzIyOWY5MjA4JTIyJTJDJTIycmVmZXJlbmNlVHlwZSUyMiUzQSUyMnViZXJfcGxhY2VzJTIyJTJDJTIybGF0aXR1ZGUlMjIlM0E0OS4yODAzOSUyQyUyMmxvbmdpdHVkZSUyMiUzQS0xMjMuMTAxMjglN0Q%3D&amp;utm_campaign=place-action-link&amp;utm_medium=organic&amp;utm_source=google"&gt;外送&lt;/a&gt; 
+&lt;/p&gt;</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>fig/XLK-321-RestaurantA7/A7XLK-3201-RestaurantA7-07.jpeg</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>3.中心商業區</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1353,14 +1387,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D43F91F4-866F-584C-A1A3-A0D1F56F484D}">
-  <dimension ref="A1:M24"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col min="3" max="3" width="10.1640625" customWidth="1"/>
     <col min="4" max="4" width="24.83203125" customWidth="1"/>
     <col min="5" max="5" width="14" style="10" customWidth="1"/>
     <col min="6" max="6" width="26.5" customWidth="1"/>
-    <col min="8" max="8" width="48" customWidth="1"/>
+    <col min="8" max="8" width="55.5" customWidth="1"/>
     <col min="9" max="9" width="25.6640625" customWidth="1"/>
     <col min="10" max="10" width="7.33203125" customWidth="1"/>
     <col min="11" max="11" width="24.5" customWidth="1"/>
@@ -1399,7 +1433,7 @@
         <v>9</v>
       </c>
       <c r="K1" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="L1" s="2" t="s">
         <v>10</v>
@@ -1410,42 +1444,42 @@
     </row>
     <row r="2" spans="1:13" ht="96">
       <c r="A2" s="1" t="s">
-        <v>208</v>
+        <v>189</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>209</v>
+        <v>190</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>210</v>
+        <v>191</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>211</v>
+        <v>192</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>212</v>
+        <v>193</v>
       </c>
       <c r="G2" s="2"/>
       <c r="H2" s="2" t="s">
-        <v>213</v>
+        <v>194</v>
       </c>
       <c r="I2" s="2"/>
       <c r="J2" s="2" t="s">
         <v>18</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>57</v>
+        <v>196</v>
       </c>
       <c r="L2" s="4" t="s">
-        <v>214</v>
+        <v>195</v>
       </c>
       <c r="M2" s="2"/>
     </row>
     <row r="3" spans="1:13" ht="192">
       <c r="A3" s="1" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>12</v>
@@ -1467,24 +1501,24 @@
         <v>17</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>18</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>57</v>
+        <v>196</v>
       </c>
       <c r="L3" s="4" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="4" spans="1:13" ht="128">
       <c r="A4" s="1" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>19</v>
@@ -1514,18 +1548,18 @@
         <v>18</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>57</v>
+        <v>196</v>
       </c>
       <c r="L4" s="4" t="s">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="5" spans="1:13" ht="96">
       <c r="A5" s="1" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>27</v>
@@ -1553,16 +1587,16 @@
         <v>18</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>57</v>
+        <v>196</v>
       </c>
       <c r="L5" s="4" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="M5" s="2"/>
     </row>
     <row r="6" spans="1:13" ht="128">
       <c r="A6" s="1" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>36</v>
@@ -1592,18 +1626,18 @@
         <v>18</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>57</v>
+        <v>196</v>
       </c>
       <c r="L6" s="4" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
     </row>
     <row r="7" spans="1:13" ht="129">
       <c r="A7" s="1" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>43</v>
@@ -1625,94 +1659,94 @@
         <v>47</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>18</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>57</v>
+        <v>196</v>
       </c>
       <c r="L7" s="4" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" ht="80">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" ht="192">
       <c r="A8" s="1" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>192</v>
+        <v>215</v>
       </c>
       <c r="C8" s="5" t="s">
         <v>20</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>49</v>
+        <v>216</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>50</v>
+        <v>218</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>58</v>
+        <v>219</v>
       </c>
       <c r="G8" s="2"/>
       <c r="H8" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="I8" s="3" t="s">
-        <v>194</v>
-      </c>
+        <v>221</v>
+      </c>
+      <c r="I8" s="3"/>
       <c r="J8" s="2" t="s">
         <v>48</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>57</v>
+        <v>196</v>
       </c>
       <c r="L8" s="4" t="s">
-        <v>195</v>
-      </c>
-      <c r="M8" s="2"/>
+        <v>220</v>
+      </c>
+      <c r="M8" s="3" t="s">
+        <v>217</v>
+      </c>
     </row>
     <row r="9" spans="1:13" ht="80">
       <c r="A9">
         <v>501</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="E9" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="I9" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="J9" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="K9" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="L9" s="8" t="s">
+        <v>174</v>
+      </c>
+      <c r="M9" s="3" t="s">
         <v>83</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="H9" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="I9" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="J9" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="K9" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="L9" s="8" t="s">
-        <v>179</v>
-      </c>
-      <c r="M9" s="3" t="s">
-        <v>87</v>
       </c>
     </row>
     <row r="10" spans="1:13" ht="208">
@@ -1720,37 +1754,37 @@
         <v>502</v>
       </c>
       <c r="B10" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="I10" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="C10" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="H10" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>94</v>
-      </c>
       <c r="J10" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="K10" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="L10" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="M10" s="3" t="s">
         <v>85</v>
-      </c>
-      <c r="K10" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="L10" s="8" t="s">
-        <v>178</v>
-      </c>
-      <c r="M10" s="3" t="s">
-        <v>90</v>
       </c>
     </row>
     <row r="11" spans="1:13" ht="80">
@@ -1758,37 +1792,37 @@
         <v>503</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="C11" s="5" t="s">
         <v>28</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="L11" s="8" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
     </row>
     <row r="12" spans="1:13" ht="80">
@@ -1796,37 +1830,37 @@
         <v>504</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="L12" s="8" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
     </row>
     <row r="13" spans="1:13" ht="192">
@@ -1834,37 +1868,37 @@
         <v>505</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="C13" s="5" t="s">
         <v>28</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="K13" s="2" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="L13" s="8" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="M13" s="3" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
     </row>
     <row r="14" spans="1:13" ht="192">
@@ -1872,37 +1906,37 @@
         <v>506</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="C14" s="5" t="s">
         <v>28</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="I14" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="K14" s="2" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="L14" s="8" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="M14" s="3" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
     </row>
     <row r="15" spans="1:13" ht="144">
@@ -1910,37 +1944,37 @@
         <v>507</v>
       </c>
       <c r="B15" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="F15" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="C15" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="E15" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="F15" s="2" t="s">
-        <v>121</v>
-      </c>
       <c r="H15" s="2" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="K15" s="2" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="L15" s="4" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="M15" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
     </row>
     <row r="16" spans="1:13">
@@ -1948,31 +1982,31 @@
         <v>508</v>
       </c>
       <c r="B16" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="F16" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="C16" s="5" t="s">
-        <v>125</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="F16" s="2" t="s">
-        <v>128</v>
-      </c>
       <c r="H16" s="2" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="I16" s="7" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="K16" s="2" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="M16" s="3" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
     </row>
     <row r="17" spans="1:13" ht="240">
@@ -1980,37 +2014,37 @@
         <v>509</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="D17" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="I17" t="s">
         <v>132</v>
       </c>
-      <c r="E17" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="F17" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="H17" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="I17" t="s">
-        <v>137</v>
-      </c>
       <c r="J17" s="2" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="K17" s="2" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="L17" s="4" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="M17" s="3" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
     </row>
     <row r="18" spans="1:13" ht="176">
@@ -2018,37 +2052,37 @@
         <v>510</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="C18" s="5" t="s">
         <v>28</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="K18" s="2" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="L18" s="9" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="M18" s="3" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
     </row>
     <row r="19" spans="1:13" ht="144">
@@ -2056,37 +2090,37 @@
         <v>511</v>
       </c>
       <c r="B19" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="C19" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="F19" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="C19" s="5" t="s">
+      <c r="H19" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="I19" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="D19" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="E19" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="F19" s="2" t="s">
-        <v>149</v>
-      </c>
-      <c r="H19" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="I19" s="3" t="s">
-        <v>150</v>
-      </c>
       <c r="J19" s="2" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="K19" s="2" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="L19" s="9" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="M19" s="2" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
     </row>
     <row r="20" spans="1:13" ht="304">
@@ -2094,37 +2128,37 @@
         <v>512</v>
       </c>
       <c r="B20" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="C20" s="5" t="s">
+        <v>147</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="F20" s="2" t="s">
         <v>151</v>
       </c>
-      <c r="C20" s="5" t="s">
+      <c r="H20" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="I20" s="3" t="s">
         <v>152</v>
       </c>
-      <c r="D20" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="E20" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="F20" s="2" t="s">
-        <v>156</v>
-      </c>
-      <c r="H20" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="I20" s="3" t="s">
-        <v>157</v>
-      </c>
       <c r="J20" s="2" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="K20" s="2" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="L20" s="9" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="M20" s="3" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
     </row>
     <row r="21" spans="1:13" ht="96">
@@ -2132,31 +2166,31 @@
         <v>513</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="C21" s="5" t="s">
         <v>34</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="H21" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="J21" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="J21" s="2" t="s">
-        <v>85</v>
-      </c>
       <c r="K21" s="2" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="L21" s="9" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="M21" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
     </row>
     <row r="22" spans="1:13">
@@ -2164,34 +2198,34 @@
         <v>514</v>
       </c>
       <c r="B22" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="C22" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="I22" s="3" t="s">
         <v>162</v>
       </c>
-      <c r="C22" s="5" t="s">
-        <v>130</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>164</v>
-      </c>
-      <c r="E22" s="1" t="s">
-        <v>165</v>
-      </c>
-      <c r="F22" s="2" t="s">
-        <v>166</v>
-      </c>
-      <c r="H22" s="2" t="s">
+      <c r="J22" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="K22" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="I22" s="3" t="s">
-        <v>167</v>
-      </c>
-      <c r="J22" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="K22" s="2" t="s">
-        <v>86</v>
-      </c>
       <c r="M22" s="3" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
     </row>
     <row r="23" spans="1:13" ht="96">
@@ -2199,73 +2233,111 @@
         <v>515</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="E23" s="1"/>
       <c r="F23" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="I23" s="7" t="s">
+        <v>184</v>
+      </c>
+      <c r="J23" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="K23" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="L23" s="8" t="s">
         <v>188</v>
       </c>
-      <c r="H23" s="2" t="s">
-        <v>191</v>
-      </c>
-      <c r="I23" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="J23" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="K23" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="L23" s="8" t="s">
-        <v>196</v>
-      </c>
       <c r="M23" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="24" spans="1:13" ht="128">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" ht="335">
       <c r="A24">
-        <v>401</v>
+        <v>301</v>
       </c>
       <c r="B24" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="C24" s="5" t="s">
         <v>198</v>
       </c>
-      <c r="C24" s="5" t="s">
+      <c r="D24" s="2" t="s">
         <v>199</v>
       </c>
-      <c r="D24" s="2" t="s">
+      <c r="E24" s="10" t="s">
         <v>200</v>
       </c>
-      <c r="E24" s="10" t="s">
+      <c r="F24" s="2" t="s">
         <v>201</v>
       </c>
-      <c r="F24" s="2" t="s">
+      <c r="H24" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="I24" s="7" t="s">
         <v>202</v>
       </c>
-      <c r="H24" s="2" t="s">
+      <c r="J24" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="K24" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="L24" s="9" t="s">
+        <v>204</v>
+      </c>
+      <c r="M24" s="3" t="s">
         <v>205</v>
       </c>
-      <c r="I24" s="7" t="s">
+    </row>
+    <row r="25" spans="1:13" ht="224">
+      <c r="A25">
+        <v>302</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="C25" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="E25" s="10" t="s">
+        <v>209</v>
+      </c>
+      <c r="F25" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="I25" s="7" t="s">
+        <v>211</v>
+      </c>
+      <c r="J25" s="2" t="s">
         <v>203</v>
       </c>
-      <c r="J24" s="2" t="s">
-        <v>204</v>
-      </c>
-      <c r="K24" s="2" t="s">
-        <v>197</v>
-      </c>
-      <c r="L24" s="9" t="s">
+      <c r="K25" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="L25" s="8" t="s">
+        <v>212</v>
+      </c>
+      <c r="M25" s="7" t="s">
         <v>207</v>
-      </c>
-      <c r="M24" s="2" t="s">
-        <v>206</v>
       </c>
     </row>
   </sheetData>
@@ -2275,36 +2347,39 @@
     <hyperlink ref="I5" r:id="rId2" xr:uid="{F003A365-8C23-084B-B31A-663E82D27E11}"/>
     <hyperlink ref="G6" r:id="rId3" xr:uid="{7AEBC60D-47CB-2041-BB0C-5BB638DE9DEC}"/>
     <hyperlink ref="I6" r:id="rId4" xr:uid="{E2777161-F973-9B42-BC21-88DA80C19FD3}"/>
-    <hyperlink ref="I8" r:id="rId5" xr:uid="{240368C4-8A23-D049-BE75-A45A65EB147A}"/>
-    <hyperlink ref="M3" r:id="rId6" xr:uid="{2E20CE02-8C51-1045-B84E-5304199A5CEC}"/>
-    <hyperlink ref="M4" r:id="rId7" xr:uid="{21CC0B31-826D-6549-8434-94B01CACE62D}"/>
-    <hyperlink ref="M6" r:id="rId8" xr:uid="{24019989-F9BD-E143-A40C-50EE4DDF5BD1}"/>
-    <hyperlink ref="M7" r:id="rId9" display="https://www.google.com.tw/maps/place/%E5%8A%89%E5%A6%B9%E9%8D%8B%E7%87%92%E6%84%8F%E9%BA%B5-%E6%A1%83%E5%9C%92%E6%9E%97%E5%8F%A3%E5%BA%97/@25.0548468,121.3827894,19.1z/data=!4m5!3m4!1s0x3442a7b02079176f:0x78906ae51c7f6abc!8m2!3d25.0553573!4d121.3840157?hl=zh-TW&amp;authuser=0" xr:uid="{13C7C2D5-34CD-404D-BEE1-B9C104B3C41D}"/>
-    <hyperlink ref="I9" r:id="rId10" xr:uid="{D22B71CE-BEE8-4D4A-B73B-DF696843091A}"/>
-    <hyperlink ref="M9" r:id="rId11" display="https://www.google.com.tw/maps/place/%E8%83%96%E8%80%81%E7%88%B9%E7%BE%8E%E5%BC%8F%E7%82%B8%E9%9B%9EA7%E6%96%87%E9%9D%92%E5%BA%97/@25.0394257,121.3894157,19.83z/data=!4m5!3m4!1s0x3442a73165d8f2d3:0xce822b237485dc8c!8m2!3d25.0394354!4d121.3903716?hl=zh-TW&amp;authuser=0" xr:uid="{C64399C5-4BBF-C54B-AFFF-C515FF32551F}"/>
-    <hyperlink ref="M10" r:id="rId12" display="https://www.google.com.tw/maps/place/%E8%B6%A3%E5%95%83%E7%82%B8%E7%89%A9-%E6%96%87%E9%9D%92%E5%BA%97/@25.039422,121.389821,19z/data=!4m9!1m2!2m1!1z6Laj5ZWD54K454mpQTfmlofpnZLlupc!3m5!1s0x3442a79257c7d5e1:0x96b9a8c7ea325295!8m2!3d25.0394086!4d121.3903675!15sChfotqPllYPngrjnialBN-aWh-mdkuW6l1ogIh7otqMg5ZWDIOeCuCDniakgYTcg5paHIOmdkiDlupeSAQRkZWxp?hl=zh-TW&amp;authuser=0" xr:uid="{ECDBCB9E-1A0B-2440-BEDC-B3365ABCEB46}"/>
-    <hyperlink ref="I10" r:id="rId13" xr:uid="{C84B02C1-9D57-3449-BF10-8BF8B150E1B0}"/>
-    <hyperlink ref="M11" r:id="rId14" display="https://www.google.com.tw/maps/place/MQ%E5%85%83%E6%B0%A3house/@25.0396043,121.3889924,19z/data=!4m9!1m2!2m1!1z5YWD5rCj5pep5Y2I6aSQQTfmlofpnZLlupc!3m5!1s0x3442a73b0be03237:0xb76fc65b93d291de!8m2!3d25.0395543!4d121.389809!15sChrlhYPmsKPml6nljYjppJBBN-aWh-mdkuW6lyIDiAEBWh4iHOWFg-awoyDml6kg5Y2I6aSQIGE3IOaWhyDpnZKSARRicmVha2Zhc3RfcmVzdGF1cmFudJoBJENoZERTVWhOTUc5blMwVkpRMEZuU1VSTE1tSjJWbWRCUlJBQg?hl=zh-TW&amp;authuser=0" xr:uid="{A608DFF8-5556-A348-BCCF-DF8FED89A676}"/>
-    <hyperlink ref="I11" r:id="rId15" xr:uid="{2AC2704D-3B90-7143-8538-1BCF2601B133}"/>
-    <hyperlink ref="M12" r:id="rId16" xr:uid="{BCFDF63E-46D6-4C46-A895-F2BE3AF3A43C}"/>
-    <hyperlink ref="I12" r:id="rId17" xr:uid="{DA402F63-BBBF-314A-9282-201C2F50A8E9}"/>
-    <hyperlink ref="M13" r:id="rId18" xr:uid="{62B3945D-7D85-6F41-B0AE-685C751A1E0D}"/>
-    <hyperlink ref="I13" r:id="rId19" xr:uid="{CF45B8DE-914A-2B48-BCB7-14602F96BD36}"/>
-    <hyperlink ref="M14" r:id="rId20" display="https://www.google.com.tw/maps/place/W%E3%80%82D%E6%88%91%E7%9A%84%E6%97%A9%E9%A4%90/@25.039828,121.3881883,18z/data=!4m9!1m2!2m1!1zV0TmiJHnmoTml6nppJAgQTfmlofpnZLlupc!3m5!1s0x3442a771fa73353d:0x329428879337e9d8!8m2!3d25.0396834!4d121.38925!15sChpXROaIkeeahOaXqemkkCBBN-aWh-mdkuW6l1oeIhx3ZCDmiJEg55qEIOaXqemkkCBhNyDmlocg6Z2SkgEUYnJlYWtmYXN0X3Jlc3RhdXJhbnSaASNDaFpEU1VoTk1HOW5TMFZKUTBGblNVUk5iMlZYVDFoUkVBRQ?hl=zh-TW&amp;authuser=0" xr:uid="{1A766ADC-BF5A-F54B-8857-2EC343131663}"/>
-    <hyperlink ref="I15" r:id="rId21" xr:uid="{D29C3BC2-9385-1848-8CD3-329B3FEC96D0}"/>
-    <hyperlink ref="M16" r:id="rId22" display="https://www.google.com.tw/maps/place/%E9%BA%B5%E9%A4%93%E5%BF%83%E8%86%B3italiana%E7%BE%A9%E5%BC%8F%E6%96%99%E7%90%86/@25.0399443,121.3879522,18z/data=!3m1!4b1!4m5!3m4!1s0x3442a771fefa1693:0x3751e2ae6c6a4c1b!8m2!3d25.0399443!4d121.3890492?hl=zh-TW&amp;authuser=0" xr:uid="{CFA5CDA3-DFA0-A345-802E-4E27D0DD6388}"/>
-    <hyperlink ref="I16" r:id="rId23" xr:uid="{52227806-B293-3140-BA54-19D8D37B7072}"/>
-    <hyperlink ref="M17" r:id="rId24" display="https://www.google.com.tw/maps/place/%E9%BC%8E%E8%A8%98+%E5%B0%8F%E7%B1%A0%E5%8C%85/@25.0394911,121.3880801,18z/data=!4m9!1m2!2m1!1z6byO6KiY5bCP57Gg5YyFIEE35paH6Z2S5bqX!3m5!1s0x3442a771eb8a1057:0x50474f8ab9f0306d!8m2!3d25.0399461!4d121.3891357!15sChvpvI7oqJjlsI_nsaDljIUgQTfmlofpnZLlupdaJCIi6byOIOiomCDlsI8g57GgIOWMhSBhNyDmlocg6Z2SIOW6l5IBCnJlc3RhdXJhbnSaASRDaGREU1VoTk1HOW5TMFZKUTBGblNVUlZORjlEZFd4blJSQUI?hl=zh-TW&amp;authuser=0" xr:uid="{40D2FFA0-1BA7-7D40-9492-E31751F5971E}"/>
-    <hyperlink ref="M18" r:id="rId25" display="https://www.google.com.tw/maps/place/%E6%B2%88%E5%AE%B6%E8%B1%86%E6%BC%BF/@25.0400428,121.3880621,18z/data=!4m9!1m2!2m1!1z5rKI5a626LGG5ry_IEE35paH6Z2S5bqX!3m5!1s0x3442a7e71b4fdbef:0xa7327c25e217658c!8m2!3d25.0398612!4d121.3890308!15sChjmsojlrrbosYbmvL8gQTfmlofpnZLlupdaGyIZ5rKIIOWutiDosYbmvL8gYTcg5paHIOmdkpIBFGJyZWFrZmFzdF9yZXN0YXVyYW50mgEkQ2hkRFNVaE5NRzluUzBWSlEwRm5TVU5qYWpkRU1HbFJSUkFC?hl=zh-TW&amp;authuser=0" xr:uid="{5BED3BAC-7517-6C44-8DD0-2E9AAD01210B}"/>
-    <hyperlink ref="I18" r:id="rId26" xr:uid="{FA94FB62-C3B4-F440-B546-D5651C4C1EF0}"/>
-    <hyperlink ref="I19" r:id="rId27" xr:uid="{36593C4B-5784-D647-A021-407E9C5E9859}"/>
-    <hyperlink ref="M20" r:id="rId28" xr:uid="{C10E1D29-46CE-4843-8B5F-0C73F3E21715}"/>
-    <hyperlink ref="I20" r:id="rId29" xr:uid="{4108B3FA-F736-964B-AFA8-8EA10E9958B5}"/>
-    <hyperlink ref="M22" r:id="rId30" xr:uid="{98E56C55-CA1A-F648-87ED-05DD4AEF5C71}"/>
-    <hyperlink ref="I22" r:id="rId31" xr:uid="{32037A18-7380-4045-A4B0-FCA8B0774D4F}"/>
-    <hyperlink ref="I23" r:id="rId32" xr:uid="{6F802D23-EF8F-E748-A152-E7AB9EBBC40B}"/>
-    <hyperlink ref="I7" r:id="rId33" xr:uid="{7D690390-5CDC-774F-88F8-D0A10F74092B}"/>
-    <hyperlink ref="I24" r:id="rId34" xr:uid="{3487482B-705B-934F-B345-27830D949CFF}"/>
+    <hyperlink ref="M3" r:id="rId5" xr:uid="{2E20CE02-8C51-1045-B84E-5304199A5CEC}"/>
+    <hyperlink ref="M4" r:id="rId6" xr:uid="{21CC0B31-826D-6549-8434-94B01CACE62D}"/>
+    <hyperlink ref="M6" r:id="rId7" xr:uid="{24019989-F9BD-E143-A40C-50EE4DDF5BD1}"/>
+    <hyperlink ref="M7" r:id="rId8" display="https://www.google.com.tw/maps/place/%E5%8A%89%E5%A6%B9%E9%8D%8B%E7%87%92%E6%84%8F%E9%BA%B5-%E6%A1%83%E5%9C%92%E6%9E%97%E5%8F%A3%E5%BA%97/@25.0548468,121.3827894,19.1z/data=!4m5!3m4!1s0x3442a7b02079176f:0x78906ae51c7f6abc!8m2!3d25.0553573!4d121.3840157?hl=zh-TW&amp;authuser=0" xr:uid="{13C7C2D5-34CD-404D-BEE1-B9C104B3C41D}"/>
+    <hyperlink ref="I9" r:id="rId9" xr:uid="{D22B71CE-BEE8-4D4A-B73B-DF696843091A}"/>
+    <hyperlink ref="M9" r:id="rId10" display="https://www.google.com.tw/maps/place/%E8%83%96%E8%80%81%E7%88%B9%E7%BE%8E%E5%BC%8F%E7%82%B8%E9%9B%9EA7%E6%96%87%E9%9D%92%E5%BA%97/@25.0394257,121.3894157,19.83z/data=!4m5!3m4!1s0x3442a73165d8f2d3:0xce822b237485dc8c!8m2!3d25.0394354!4d121.3903716?hl=zh-TW&amp;authuser=0" xr:uid="{C64399C5-4BBF-C54B-AFFF-C515FF32551F}"/>
+    <hyperlink ref="M10" r:id="rId11" display="https://www.google.com.tw/maps/place/%E8%B6%A3%E5%95%83%E7%82%B8%E7%89%A9-%E6%96%87%E9%9D%92%E5%BA%97/@25.039422,121.389821,19z/data=!4m9!1m2!2m1!1z6Laj5ZWD54K454mpQTfmlofpnZLlupc!3m5!1s0x3442a79257c7d5e1:0x96b9a8c7ea325295!8m2!3d25.0394086!4d121.3903675!15sChfotqPllYPngrjnialBN-aWh-mdkuW6l1ogIh7otqMg5ZWDIOeCuCDniakgYTcg5paHIOmdkiDlupeSAQRkZWxp?hl=zh-TW&amp;authuser=0" xr:uid="{ECDBCB9E-1A0B-2440-BEDC-B3365ABCEB46}"/>
+    <hyperlink ref="I10" r:id="rId12" xr:uid="{C84B02C1-9D57-3449-BF10-8BF8B150E1B0}"/>
+    <hyperlink ref="M11" r:id="rId13" display="https://www.google.com.tw/maps/place/MQ%E5%85%83%E6%B0%A3house/@25.0396043,121.3889924,19z/data=!4m9!1m2!2m1!1z5YWD5rCj5pep5Y2I6aSQQTfmlofpnZLlupc!3m5!1s0x3442a73b0be03237:0xb76fc65b93d291de!8m2!3d25.0395543!4d121.389809!15sChrlhYPmsKPml6nljYjppJBBN-aWh-mdkuW6lyIDiAEBWh4iHOWFg-awoyDml6kg5Y2I6aSQIGE3IOaWhyDpnZKSARRicmVha2Zhc3RfcmVzdGF1cmFudJoBJENoZERTVWhOTUc5blMwVkpRMEZuU1VSTE1tSjJWbWRCUlJBQg?hl=zh-TW&amp;authuser=0" xr:uid="{A608DFF8-5556-A348-BCCF-DF8FED89A676}"/>
+    <hyperlink ref="I11" r:id="rId14" xr:uid="{2AC2704D-3B90-7143-8538-1BCF2601B133}"/>
+    <hyperlink ref="M12" r:id="rId15" xr:uid="{BCFDF63E-46D6-4C46-A895-F2BE3AF3A43C}"/>
+    <hyperlink ref="I12" r:id="rId16" xr:uid="{DA402F63-BBBF-314A-9282-201C2F50A8E9}"/>
+    <hyperlink ref="M13" r:id="rId17" xr:uid="{62B3945D-7D85-6F41-B0AE-685C751A1E0D}"/>
+    <hyperlink ref="I13" r:id="rId18" xr:uid="{CF45B8DE-914A-2B48-BCB7-14602F96BD36}"/>
+    <hyperlink ref="M14" r:id="rId19" display="https://www.google.com.tw/maps/place/W%E3%80%82D%E6%88%91%E7%9A%84%E6%97%A9%E9%A4%90/@25.039828,121.3881883,18z/data=!4m9!1m2!2m1!1zV0TmiJHnmoTml6nppJAgQTfmlofpnZLlupc!3m5!1s0x3442a771fa73353d:0x329428879337e9d8!8m2!3d25.0396834!4d121.38925!15sChpXROaIkeeahOaXqemkkCBBN-aWh-mdkuW6l1oeIhx3ZCDmiJEg55qEIOaXqemkkCBhNyDmlocg6Z2SkgEUYnJlYWtmYXN0X3Jlc3RhdXJhbnSaASNDaFpEU1VoTk1HOW5TMFZKUTBGblNVUk5iMlZYVDFoUkVBRQ?hl=zh-TW&amp;authuser=0" xr:uid="{1A766ADC-BF5A-F54B-8857-2EC343131663}"/>
+    <hyperlink ref="I15" r:id="rId20" xr:uid="{D29C3BC2-9385-1848-8CD3-329B3FEC96D0}"/>
+    <hyperlink ref="M16" r:id="rId21" display="https://www.google.com.tw/maps/place/%E9%BA%B5%E9%A4%93%E5%BF%83%E8%86%B3italiana%E7%BE%A9%E5%BC%8F%E6%96%99%E7%90%86/@25.0399443,121.3879522,18z/data=!3m1!4b1!4m5!3m4!1s0x3442a771fefa1693:0x3751e2ae6c6a4c1b!8m2!3d25.0399443!4d121.3890492?hl=zh-TW&amp;authuser=0" xr:uid="{CFA5CDA3-DFA0-A345-802E-4E27D0DD6388}"/>
+    <hyperlink ref="I16" r:id="rId22" xr:uid="{52227806-B293-3140-BA54-19D8D37B7072}"/>
+    <hyperlink ref="M17" r:id="rId23" display="https://www.google.com.tw/maps/place/%E9%BC%8E%E8%A8%98+%E5%B0%8F%E7%B1%A0%E5%8C%85/@25.0394911,121.3880801,18z/data=!4m9!1m2!2m1!1z6byO6KiY5bCP57Gg5YyFIEE35paH6Z2S5bqX!3m5!1s0x3442a771eb8a1057:0x50474f8ab9f0306d!8m2!3d25.0399461!4d121.3891357!15sChvpvI7oqJjlsI_nsaDljIUgQTfmlofpnZLlupdaJCIi6byOIOiomCDlsI8g57GgIOWMhSBhNyDmlocg6Z2SIOW6l5IBCnJlc3RhdXJhbnSaASRDaGREU1VoTk1HOW5TMFZKUTBGblNVUlZORjlEZFd4blJSQUI?hl=zh-TW&amp;authuser=0" xr:uid="{40D2FFA0-1BA7-7D40-9492-E31751F5971E}"/>
+    <hyperlink ref="M18" r:id="rId24" display="https://www.google.com.tw/maps/place/%E6%B2%88%E5%AE%B6%E8%B1%86%E6%BC%BF/@25.0400428,121.3880621,18z/data=!4m9!1m2!2m1!1z5rKI5a626LGG5ry_IEE35paH6Z2S5bqX!3m5!1s0x3442a7e71b4fdbef:0xa7327c25e217658c!8m2!3d25.0398612!4d121.3890308!15sChjmsojlrrbosYbmvL8gQTfmlofpnZLlupdaGyIZ5rKIIOWutiDosYbmvL8gYTcg5paHIOmdkpIBFGJyZWFrZmFzdF9yZXN0YXVyYW50mgEkQ2hkRFNVaE5NRzluUzBWSlEwRm5TVU5qYWpkRU1HbFJSUkFC?hl=zh-TW&amp;authuser=0" xr:uid="{5BED3BAC-7517-6C44-8DD0-2E9AAD01210B}"/>
+    <hyperlink ref="I18" r:id="rId25" xr:uid="{FA94FB62-C3B4-F440-B546-D5651C4C1EF0}"/>
+    <hyperlink ref="I19" r:id="rId26" xr:uid="{36593C4B-5784-D647-A021-407E9C5E9859}"/>
+    <hyperlink ref="M20" r:id="rId27" xr:uid="{C10E1D29-46CE-4843-8B5F-0C73F3E21715}"/>
+    <hyperlink ref="I20" r:id="rId28" xr:uid="{4108B3FA-F736-964B-AFA8-8EA10E9958B5}"/>
+    <hyperlink ref="M22" r:id="rId29" xr:uid="{98E56C55-CA1A-F648-87ED-05DD4AEF5C71}"/>
+    <hyperlink ref="I22" r:id="rId30" xr:uid="{32037A18-7380-4045-A4B0-FCA8B0774D4F}"/>
+    <hyperlink ref="I23" r:id="rId31" xr:uid="{6F802D23-EF8F-E748-A152-E7AB9EBBC40B}"/>
+    <hyperlink ref="I7" r:id="rId32" xr:uid="{7D690390-5CDC-774F-88F8-D0A10F74092B}"/>
+    <hyperlink ref="I24" r:id="rId33" xr:uid="{3487482B-705B-934F-B345-27830D949CFF}"/>
+    <hyperlink ref="M24" r:id="rId34" xr:uid="{74F32270-5AC7-4741-9928-D33D18CF9FB3}"/>
+    <hyperlink ref="M25" r:id="rId35" xr:uid="{E246A458-07DD-CC4C-99FE-5782C2F2DFA4}"/>
+    <hyperlink ref="I25" r:id="rId36" xr:uid="{5E178450-E303-0D48-8BD2-F7009B785BA5}"/>
+    <hyperlink ref="M8" r:id="rId37" xr:uid="{14DEDDAA-9C5B-4748-8774-11268E961283}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/db/A7XLK-3201-RestaurantA7.xlsx
+++ b/db/A7XLK-3201-RestaurantA7.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wangtaizhong/Documents/92_WebSite/A7Xinlinkou/db/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1D62811-DD59-3849-A25C-7A7A68C31177}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C521544-5307-DE44-BCF1-A9013F57A315}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-1540" yWindow="2200" windowWidth="27940" windowHeight="17500" xr2:uid="{EC3C71DD-AB41-7249-985D-4787F3B89605}"/>
+    <workbookView xWindow="480" yWindow="500" windowWidth="27940" windowHeight="17500" xr2:uid="{EC3C71DD-AB41-7249-985D-4787F3B89605}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="223">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="320" uniqueCount="252">
   <si>
     <t>no</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -932,10 +932,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>fig/XLK-321-RestaurantA7/A7XLK-3203-A7Restaurant-02.jpeg</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>便當製造所</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -968,6 +964,133 @@
   <si>
     <t>3.中心商業區</t>
     <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Joyfull 台灣珍有福</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.google.com.tw/maps/place/Joyfull%E5%8F%B0%E7%81%A3%E7%8F%8D%E6%9C%89%E7%A6%8F+%E9%BE%9C%E5%B1%B1%E6%96%87%E9%9D%92%E5%BA%97/@25.0404003,121.3845642,17z/data=!3m1!4b1!4m5!3m4!1s0x3442a7699aa9553d:0xe952e516cf83c284!8m2!3d25.0404003!4d121.3867529?hl=zh-TW&amp;authuser=0</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>桃園市龜山區文青路137號1樓</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>03-397-9595</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>fig/XLK-321-RestaurantA7/A7XLK-3203-A7Restaurant-02.jpeg</t>
+  </si>
+  <si>
+    <t>fig/XLK-321-RestaurantA7/A7XLK-3203-A7Restaurant-03.jpeg</t>
+  </si>
+  <si>
+    <t>fig/XLK-321-RestaurantA7/A7XLK-3203-A7Restaurant-04.jpeg</t>
+  </si>
+  <si>
+    <t>fig/XLK-321-RestaurantA7/A7XLK-3203-A7Restaurant-05.jpeg</t>
+  </si>
+  <si>
+    <t>fig/XLK-321-RestaurantA7/A7XLK-3203-A7Restaurant-06.jpeg</t>
+  </si>
+  <si>
+    <t>http://www.joyfull.com.tw/index.php</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>日本連鎖店</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;p&gt;
+   資訊: &lt;a style="button" class="btn btn-info"  href="https://www.ubereats.com/tw/store/joyfull-%E9%BE%9C%E5%B1%B1%E6%96%87%E9%9D%92%E5%BA%97/KqxuraEhVbmGUWxJ59Q3eQ?diningMode=DELIVERY&amp;pl=JTdCJTIyYWRkcmVzcyUyMiUzQSUyMkphZGUlMjBEeW5hc3R5JTIyJTJDJTIycmVmZXJlbmNlJTIyJTNBJTIyZjgyZTA1YTItODE2NS0xMGU4LWQ3M2QtNDMwYzIyOWY5MjA4JTIyJTJDJTIycmVmZXJlbmNlVHlwZSUyMiUzQSUyMnViZXJfcGxhY2VzJTIyJTJDJTIybGF0aXR1ZGUlMjIlM0E0OS4yODAzOSUyQyUyMmxvbmdpdHVkZSUyMiUzQS0xMjMuMTAxMjglN0Q%3D"&gt;Uber Eats&lt;/a&gt; &amp;nbsp; 
+&lt;a style="button" class="btn btn-info"  href="http://www.joyfull.com.tw/product.php"&gt;菜單&lt;/a&gt; &amp;nbsp;
+&lt;/p&gt;</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.google.com.tw/maps/place/%E4%B8%89%E5%95%86%E5%B7%A7%E7%A6%8F/@25.0403772,121.3845361,18z/data=!4m5!3m4!1s0x3442a7b4c61abf19:0x9568ebc0d6bad9cf!8m2!3d25.0403772!4d121.386596?hl=zh-TW</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>三商巧福</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>桃園市龜山區文青路137號</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>03-327-9452</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.3375.com.tw/</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;p&gt;
+   資訊: &lt;a style="button" class="btn btn-info"  href="https://www.foodpanda.com.tw/en/restaurant/wves/san-shang-qiao-fu-jia-le-fu-tao-yuan-gui-shan-a7wen-qing-dian-42a5"&gt;Foodpanda&lt;/a&gt; &amp;nbsp; 
+&lt;a style="button" class="btn btn-info"  href="https://www.3375.com.tw/Menu/FoodMenu"&gt;菜單&lt;/a&gt; &amp;nbsp;
+&lt;/p&gt;</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.google.com.tw/maps/place/Yipin+Pasta+%E7%BE%A9%E5%93%81+%E5%AE%B6%E6%A8%82%E7%A6%8F%E9%BE%9C%E5%B1%B1A7%E6%96%87%E9%9D%92%E5%BA%97/@25.0405787,121.3855057,18z/data=!3m1!4b1!4m5!3m4!1s0x3442a765f994e34f:0x64cc431d298f3874!8m2!3d25.0405787!4d121.3866?hl=zh-TW</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Yipin Pasta 義品</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>03-328-2870</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://yipinpasta.com.tw/</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;p&gt;
+   資訊: &lt;a style="button" class="btn btn-info"  href="https://www.foodpanda.com.tw/en/restaurant/r4cx/yipin-pasta-yi-pin-jia-le-fu-tao-yuan-gui-shan-a7wen-qing-dian"&gt;Foodpanda&lt;/a&gt; &amp;nbsp; 
+&lt;a style="button" class="btn btn-info"  href="https://yipinpasta.com.tw/menus/"&gt;菜單&lt;/a&gt; &amp;nbsp;
+&lt;/p&gt;</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>荖子鍋</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.google.com.tw/maps/place/%E8%8D%96%E5%AD%90%E9%8D%8B+%E5%AE%B6%E6%A8%82%E7%A6%8F%E9%BE%9C%E5%B1%B1A7%E6%96%87%E9%9D%92%E5%BA%97/@25.0403589,121.3854987,18z/data=!3m1!4b1!4m5!3m4!1s0x3442a7eeffa65687:0xf193de6d03030a5a!8m2!3d25.0403589!4d121.386593?hl=zh-TW</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>火鍋店</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>03-327-1960</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://laozihotpot.ec52.com/</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>文青路</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;p&gt;
+   資訊: &lt;a style="button" class="btn btn-info"  href="https://www.foodpanda.com.tw/en/restaurant/qox9/lao-zi-guo-jia-le-fu-gui-shan-a7wen-qing-dian?utm_source=google&amp;utm_medium=organic&amp;utm_campaign=google_reserve_place_order_action"&gt;Foodpanda&lt;/a&gt; &amp;nbsp; 
+&lt;a style="button" class="btn btn-info"  href="https://laozihotpot.ec52.com/food"&gt;菜單&lt;/a&gt; &amp;nbsp;
+&lt;/p&gt;</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1387,7 +1510,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D43F91F4-866F-584C-A1A3-A0D1F56F484D}">
-  <dimension ref="A1:M25"/>
+  <dimension ref="A1:M29"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col min="3" max="3" width="10.1640625" customWidth="1"/>
@@ -1679,23 +1802,23 @@
         <v>60</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C8" s="5" t="s">
         <v>20</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="E8" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="F8" s="2" t="s">
         <v>218</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>219</v>
       </c>
       <c r="G8" s="2"/>
       <c r="H8" s="2" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="I8" s="3"/>
       <c r="J8" s="2" t="s">
@@ -1705,10 +1828,10 @@
         <v>196</v>
       </c>
       <c r="L8" s="4" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="9" spans="1:13" ht="80">
@@ -2293,7 +2416,7 @@
         <v>203</v>
       </c>
       <c r="K24" s="2" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="L24" s="9" t="s">
         <v>204</v>
@@ -2322,7 +2445,7 @@
         <v>210</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>214</v>
+        <v>226</v>
       </c>
       <c r="I25" s="7" t="s">
         <v>211</v>
@@ -2331,13 +2454,165 @@
         <v>203</v>
       </c>
       <c r="K25" s="2" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="L25" s="8" t="s">
         <v>212</v>
       </c>
       <c r="M25" s="7" t="s">
         <v>207</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" ht="208">
+      <c r="A26">
+        <v>303</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="E26" s="10" t="s">
+        <v>225</v>
+      </c>
+      <c r="F26" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="I26" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="J26" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="K26" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="L26" s="9" t="s">
+        <v>233</v>
+      </c>
+      <c r="M26" s="7" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" ht="112">
+      <c r="A27">
+        <v>304</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="C27" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="E27" s="10" t="s">
+        <v>237</v>
+      </c>
+      <c r="F27" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="I27" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="J27" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="K27" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="L27" s="9" t="s">
+        <v>239</v>
+      </c>
+      <c r="M27" s="3" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13" ht="112">
+      <c r="A28">
+        <v>305</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="C28" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="E28" s="10" t="s">
+        <v>242</v>
+      </c>
+      <c r="F28" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="I28" s="3" t="s">
+        <v>243</v>
+      </c>
+      <c r="J28" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="K28" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="L28" s="9" t="s">
+        <v>244</v>
+      </c>
+      <c r="M28" s="3" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13" ht="144">
+      <c r="A29">
+        <v>306</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="C29" s="5" t="s">
+        <v>247</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="E29" s="10" t="s">
+        <v>248</v>
+      </c>
+      <c r="F29" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="H29" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="I29" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="J29" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="K29" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="L29" s="9" t="s">
+        <v>251</v>
+      </c>
+      <c r="M29" s="3" t="s">
+        <v>246</v>
       </c>
     </row>
   </sheetData>
@@ -2380,6 +2655,14 @@
     <hyperlink ref="M25" r:id="rId35" xr:uid="{E246A458-07DD-CC4C-99FE-5782C2F2DFA4}"/>
     <hyperlink ref="I25" r:id="rId36" xr:uid="{5E178450-E303-0D48-8BD2-F7009B785BA5}"/>
     <hyperlink ref="M8" r:id="rId37" xr:uid="{14DEDDAA-9C5B-4748-8774-11268E961283}"/>
+    <hyperlink ref="M26" r:id="rId38" display="https://www.google.com.tw/maps/place/Joyfull%E5%8F%B0%E7%81%A3%E7%8F%8D%E6%9C%89%E7%A6%8F+%E9%BE%9C%E5%B1%B1%E6%96%87%E9%9D%92%E5%BA%97/@25.0404003,121.3845642,17z/data=!3m1!4b1!4m5!3m4!1s0x3442a7699aa9553d:0xe952e516cf83c284!8m2!3d25.0404003!4d121.3867529?hl=zh-TW&amp;authuser=0" xr:uid="{0F99912D-9206-1341-91D3-A8ABE82B9B7D}"/>
+    <hyperlink ref="I26" r:id="rId39" xr:uid="{B3553713-7114-F644-828F-381533D5B59C}"/>
+    <hyperlink ref="M27" r:id="rId40" xr:uid="{529979E4-4FEA-E947-96A5-E04032E634FE}"/>
+    <hyperlink ref="I27" r:id="rId41" xr:uid="{AE19FED5-B89B-B04A-AF86-C5822C140599}"/>
+    <hyperlink ref="M28" r:id="rId42" display="https://www.google.com.tw/maps/place/Yipin+Pasta+%E7%BE%A9%E5%93%81+%E5%AE%B6%E6%A8%82%E7%A6%8F%E9%BE%9C%E5%B1%B1A7%E6%96%87%E9%9D%92%E5%BA%97/@25.0405787,121.3855057,18z/data=!3m1!4b1!4m5!3m4!1s0x3442a765f994e34f:0x64cc431d298f3874!8m2!3d25.0405787!4d121.3866?hl=zh-TW" xr:uid="{665007E7-4AC9-1B4B-AF8D-A54552764742}"/>
+    <hyperlink ref="I28" r:id="rId43" xr:uid="{1FA1272F-F1EF-ED4B-8F52-3369F01BB595}"/>
+    <hyperlink ref="M29" r:id="rId44" display="https://www.google.com.tw/maps/place/%E8%8D%96%E5%AD%90%E9%8D%8B+%E5%AE%B6%E6%A8%82%E7%A6%8F%E9%BE%9C%E5%B1%B1A7%E6%96%87%E9%9D%92%E5%BA%97/@25.0403589,121.3854987,18z/data=!3m1!4b1!4m5!3m4!1s0x3442a7eeffa65687:0xf193de6d03030a5a!8m2!3d25.0403589!4d121.386593?hl=zh-TW" xr:uid="{493F2D01-2EF4-1544-9625-767871CC044A}"/>
+    <hyperlink ref="I29" r:id="rId45" xr:uid="{0F604AB3-BEFF-2046-B537-A1F987B3C006}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/db/A7XLK-3201-RestaurantA7.xlsx
+++ b/db/A7XLK-3201-RestaurantA7.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wangtaizhong/Documents/92_WebSite/A7Xinlinkou/db/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C521544-5307-DE44-BCF1-A9013F57A315}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DAA0B78A-5F92-7041-BD08-B9B3DAE20A08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="480" yWindow="500" windowWidth="27940" windowHeight="17500" xr2:uid="{EC3C71DD-AB41-7249-985D-4787F3B89605}"/>
+    <workbookView xWindow="0" yWindow="3160" windowWidth="27940" windowHeight="17500" xr2:uid="{EC3C71DD-AB41-7249-985D-4787F3B89605}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>

--- a/db/A7XLK-3201-RestaurantA7.xlsx
+++ b/db/A7XLK-3201-RestaurantA7.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10520"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10611"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wangtaizhong/Documents/92_WebSite/A7Xinlinkou/db/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DAA0B78A-5F92-7041-BD08-B9B3DAE20A08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4FE295DF-9903-574B-9C9A-AC8F89746CFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="3160" windowWidth="27940" windowHeight="17500" xr2:uid="{EC3C71DD-AB41-7249-985D-4787F3B89605}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="27940" windowHeight="17500" xr2:uid="{EC3C71DD-AB41-7249-985D-4787F3B89605}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="320" uniqueCount="252">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="330" uniqueCount="261">
   <si>
     <t>no</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -1090,6 +1090,44 @@
    資訊: &lt;a style="button" class="btn btn-info"  href="https://www.foodpanda.com.tw/en/restaurant/qox9/lao-zi-guo-jia-le-fu-gui-shan-a7wen-qing-dian?utm_source=google&amp;utm_medium=organic&amp;utm_campaign=google_reserve_place_order_action"&gt;Foodpanda&lt;/a&gt; &amp;nbsp; 
 &lt;a style="button" class="btn btn-info"  href="https://laozihotpot.ec52.com/food"&gt;菜單&lt;/a&gt; &amp;nbsp;
 &lt;/p&gt;</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>16號快餐</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>中餐廳</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>fig/XLK-321-RestaurantA7/A7XLK-3203-A7Restaurant-07.png</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.google.com.tw/maps/place/16%E8%99%9F%E5%BF%AB%E9%A4%90%E5%BA%97/@25.0490638,121.3793653,17z/data=!4m12!1m6!3m5!1s0x3442a708f4e389cf:0xaa1a565c408caa4f!2zMTbomZ_lv6vppJDlupc!8m2!3d25.0490638!4d121.3815389!3m4!1s0x3442a708f4e389cf:0xaa1a565c408caa4f!8m2!3d25.0490638!4d121.3815389?hl=zh-TW&amp;authuser=0</t>
+  </si>
+  <si>
+    <t>華亞三路</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>桃園市龜山區華亞三路39巷16號</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>03-397-0686</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;p&gt;
+   資訊: &lt;a style="button" class="btn btn-info"  href="https://www.facebook.com/groups/1951117865015671/permalink/4876627412464687/"&gt;推薦&lt;/a&gt; &amp;nbsp; 
+&lt;a style="button" class="btn btn-info"  href="https://www.google.com.tw/maps/place/16%E8%99%9F%E5%BF%AB%E9%A4%90%E5%BA%97/@25.0490638,121.3815389,3a,75y/data=!3m8!1e2!3m6!1sAF1QipOipP95f3Xai-H4HAbqUXnKlcPNnGHQiCee4JE!2e10!3e12!6shttps:%2F%2Flh5.googleusercontent.com%2Fp%2FAF1QipOipP95f3Xai-H4HAbqUXnKlcPNnGHQiCee4JE%3Dw203-h152-k-no!7i4032!8i3024!4m5!3m4!1s0x3442a708f4e389cf:0xaa1a565c408caa4f!8m2!3d25.0490638!4d121.3815389?hl=zh-TW&amp;authuser=0#"&gt;菜單&lt;/a&gt; &amp;nbsp;
+&lt;/p&gt;</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>10:30 - 20:00, 週六日公休</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -1510,7 +1548,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D43F91F4-866F-584C-A1A3-A0D1F56F484D}">
-  <dimension ref="A1:M29"/>
+  <dimension ref="A1:M30"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col min="3" max="3" width="10.1640625" customWidth="1"/>
@@ -2387,68 +2425,66 @@
         <v>185</v>
       </c>
     </row>
-    <row r="24" spans="1:13" ht="335">
+    <row r="24" spans="1:13" ht="224">
       <c r="A24">
-        <v>301</v>
+        <v>307</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>197</v>
+        <v>252</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>198</v>
+        <v>253</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>199</v>
-      </c>
-      <c r="E24" s="10" t="s">
-        <v>200</v>
+        <v>257</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>258</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>201</v>
+        <v>260</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>213</v>
-      </c>
-      <c r="I24" s="7" t="s">
-        <v>202</v>
-      </c>
+        <v>254</v>
+      </c>
+      <c r="I24" s="7"/>
       <c r="J24" s="2" t="s">
-        <v>203</v>
+        <v>256</v>
       </c>
       <c r="K24" s="2" t="s">
         <v>221</v>
       </c>
       <c r="L24" s="9" t="s">
-        <v>204</v>
-      </c>
-      <c r="M24" s="3" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="25" spans="1:13" ht="224">
+        <v>259</v>
+      </c>
+      <c r="M24" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" ht="335">
       <c r="A25">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>206</v>
+        <v>197</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>28</v>
+        <v>198</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>208</v>
+        <v>199</v>
       </c>
       <c r="E25" s="10" t="s">
-        <v>209</v>
+        <v>200</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>210</v>
+        <v>201</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>226</v>
+        <v>213</v>
       </c>
       <c r="I25" s="7" t="s">
-        <v>211</v>
+        <v>202</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>203</v>
@@ -2456,75 +2492,75 @@
       <c r="K25" s="2" t="s">
         <v>221</v>
       </c>
-      <c r="L25" s="8" t="s">
-        <v>212</v>
-      </c>
-      <c r="M25" s="7" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="26" spans="1:13" ht="208">
+      <c r="L25" s="9" t="s">
+        <v>204</v>
+      </c>
+      <c r="M25" s="3" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" ht="224">
       <c r="A26">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>222</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>232</v>
+        <v>206</v>
+      </c>
+      <c r="C26" s="5" t="s">
+        <v>28</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>224</v>
+        <v>208</v>
       </c>
       <c r="E26" s="10" t="s">
-        <v>225</v>
+        <v>209</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>151</v>
+        <v>210</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="I26" s="3" t="s">
-        <v>231</v>
+        <v>226</v>
+      </c>
+      <c r="I26" s="7" t="s">
+        <v>211</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>81</v>
+        <v>203</v>
       </c>
       <c r="K26" s="2" t="s">
         <v>221</v>
       </c>
-      <c r="L26" s="9" t="s">
-        <v>233</v>
+      <c r="L26" s="8" t="s">
+        <v>212</v>
       </c>
       <c r="M26" s="7" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="27" spans="1:13" ht="112">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" ht="208">
       <c r="A27">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>235</v>
-      </c>
-      <c r="C27" s="5" t="s">
-        <v>125</v>
+        <v>222</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>232</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>236</v>
+        <v>224</v>
       </c>
       <c r="E27" s="10" t="s">
-        <v>237</v>
+        <v>225</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>151</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="I27" s="3" t="s">
-        <v>238</v>
+        <v>231</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>81</v>
@@ -2533,18 +2569,18 @@
         <v>221</v>
       </c>
       <c r="L27" s="9" t="s">
-        <v>239</v>
-      </c>
-      <c r="M27" s="3" t="s">
-        <v>234</v>
+        <v>233</v>
+      </c>
+      <c r="M27" s="7" t="s">
+        <v>223</v>
       </c>
     </row>
     <row r="28" spans="1:13" ht="112">
       <c r="A28">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>241</v>
+        <v>235</v>
       </c>
       <c r="C28" s="5" t="s">
         <v>125</v>
@@ -2553,16 +2589,16 @@
         <v>236</v>
       </c>
       <c r="E28" s="10" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>151</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>243</v>
+        <v>238</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>81</v>
@@ -2571,47 +2607,85 @@
         <v>221</v>
       </c>
       <c r="L28" s="9" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
       <c r="M28" s="3" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="29" spans="1:13" ht="144">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13" ht="112">
       <c r="A29">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>247</v>
+        <v>125</v>
       </c>
       <c r="D29" s="2" t="s">
         <v>236</v>
       </c>
       <c r="E29" s="10" t="s">
-        <v>248</v>
+        <v>242</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>151</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>250</v>
+        <v>81</v>
       </c>
       <c r="K29" s="2" t="s">
         <v>221</v>
       </c>
       <c r="L29" s="9" t="s">
+        <v>244</v>
+      </c>
+      <c r="M29" s="3" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13" ht="144">
+      <c r="A30">
+        <v>306</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="C30" s="5" t="s">
+        <v>247</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="E30" s="10" t="s">
+        <v>248</v>
+      </c>
+      <c r="F30" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="H30" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="I30" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="J30" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="K30" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="L30" s="9" t="s">
         <v>251</v>
       </c>
-      <c r="M29" s="3" t="s">
+      <c r="M30" s="3" t="s">
         <v>246</v>
       </c>
     </row>
@@ -2650,19 +2724,19 @@
     <hyperlink ref="I22" r:id="rId30" xr:uid="{32037A18-7380-4045-A4B0-FCA8B0774D4F}"/>
     <hyperlink ref="I23" r:id="rId31" xr:uid="{6F802D23-EF8F-E748-A152-E7AB9EBBC40B}"/>
     <hyperlink ref="I7" r:id="rId32" xr:uid="{7D690390-5CDC-774F-88F8-D0A10F74092B}"/>
-    <hyperlink ref="I24" r:id="rId33" xr:uid="{3487482B-705B-934F-B345-27830D949CFF}"/>
-    <hyperlink ref="M24" r:id="rId34" xr:uid="{74F32270-5AC7-4741-9928-D33D18CF9FB3}"/>
-    <hyperlink ref="M25" r:id="rId35" xr:uid="{E246A458-07DD-CC4C-99FE-5782C2F2DFA4}"/>
-    <hyperlink ref="I25" r:id="rId36" xr:uid="{5E178450-E303-0D48-8BD2-F7009B785BA5}"/>
+    <hyperlink ref="I25" r:id="rId33" xr:uid="{3487482B-705B-934F-B345-27830D949CFF}"/>
+    <hyperlink ref="M25" r:id="rId34" xr:uid="{74F32270-5AC7-4741-9928-D33D18CF9FB3}"/>
+    <hyperlink ref="M26" r:id="rId35" xr:uid="{E246A458-07DD-CC4C-99FE-5782C2F2DFA4}"/>
+    <hyperlink ref="I26" r:id="rId36" xr:uid="{5E178450-E303-0D48-8BD2-F7009B785BA5}"/>
     <hyperlink ref="M8" r:id="rId37" xr:uid="{14DEDDAA-9C5B-4748-8774-11268E961283}"/>
-    <hyperlink ref="M26" r:id="rId38" display="https://www.google.com.tw/maps/place/Joyfull%E5%8F%B0%E7%81%A3%E7%8F%8D%E6%9C%89%E7%A6%8F+%E9%BE%9C%E5%B1%B1%E6%96%87%E9%9D%92%E5%BA%97/@25.0404003,121.3845642,17z/data=!3m1!4b1!4m5!3m4!1s0x3442a7699aa9553d:0xe952e516cf83c284!8m2!3d25.0404003!4d121.3867529?hl=zh-TW&amp;authuser=0" xr:uid="{0F99912D-9206-1341-91D3-A8ABE82B9B7D}"/>
-    <hyperlink ref="I26" r:id="rId39" xr:uid="{B3553713-7114-F644-828F-381533D5B59C}"/>
-    <hyperlink ref="M27" r:id="rId40" xr:uid="{529979E4-4FEA-E947-96A5-E04032E634FE}"/>
-    <hyperlink ref="I27" r:id="rId41" xr:uid="{AE19FED5-B89B-B04A-AF86-C5822C140599}"/>
-    <hyperlink ref="M28" r:id="rId42" display="https://www.google.com.tw/maps/place/Yipin+Pasta+%E7%BE%A9%E5%93%81+%E5%AE%B6%E6%A8%82%E7%A6%8F%E9%BE%9C%E5%B1%B1A7%E6%96%87%E9%9D%92%E5%BA%97/@25.0405787,121.3855057,18z/data=!3m1!4b1!4m5!3m4!1s0x3442a765f994e34f:0x64cc431d298f3874!8m2!3d25.0405787!4d121.3866?hl=zh-TW" xr:uid="{665007E7-4AC9-1B4B-AF8D-A54552764742}"/>
-    <hyperlink ref="I28" r:id="rId43" xr:uid="{1FA1272F-F1EF-ED4B-8F52-3369F01BB595}"/>
-    <hyperlink ref="M29" r:id="rId44" display="https://www.google.com.tw/maps/place/%E8%8D%96%E5%AD%90%E9%8D%8B+%E5%AE%B6%E6%A8%82%E7%A6%8F%E9%BE%9C%E5%B1%B1A7%E6%96%87%E9%9D%92%E5%BA%97/@25.0403589,121.3854987,18z/data=!3m1!4b1!4m5!3m4!1s0x3442a7eeffa65687:0xf193de6d03030a5a!8m2!3d25.0403589!4d121.386593?hl=zh-TW" xr:uid="{493F2D01-2EF4-1544-9625-767871CC044A}"/>
-    <hyperlink ref="I29" r:id="rId45" xr:uid="{0F604AB3-BEFF-2046-B537-A1F987B3C006}"/>
+    <hyperlink ref="M27" r:id="rId38" display="https://www.google.com.tw/maps/place/Joyfull%E5%8F%B0%E7%81%A3%E7%8F%8D%E6%9C%89%E7%A6%8F+%E9%BE%9C%E5%B1%B1%E6%96%87%E9%9D%92%E5%BA%97/@25.0404003,121.3845642,17z/data=!3m1!4b1!4m5!3m4!1s0x3442a7699aa9553d:0xe952e516cf83c284!8m2!3d25.0404003!4d121.3867529?hl=zh-TW&amp;authuser=0" xr:uid="{0F99912D-9206-1341-91D3-A8ABE82B9B7D}"/>
+    <hyperlink ref="I27" r:id="rId39" xr:uid="{B3553713-7114-F644-828F-381533D5B59C}"/>
+    <hyperlink ref="M28" r:id="rId40" xr:uid="{529979E4-4FEA-E947-96A5-E04032E634FE}"/>
+    <hyperlink ref="I28" r:id="rId41" xr:uid="{AE19FED5-B89B-B04A-AF86-C5822C140599}"/>
+    <hyperlink ref="M29" r:id="rId42" display="https://www.google.com.tw/maps/place/Yipin+Pasta+%E7%BE%A9%E5%93%81+%E5%AE%B6%E6%A8%82%E7%A6%8F%E9%BE%9C%E5%B1%B1A7%E6%96%87%E9%9D%92%E5%BA%97/@25.0405787,121.3855057,18z/data=!3m1!4b1!4m5!3m4!1s0x3442a765f994e34f:0x64cc431d298f3874!8m2!3d25.0405787!4d121.3866?hl=zh-TW" xr:uid="{665007E7-4AC9-1B4B-AF8D-A54552764742}"/>
+    <hyperlink ref="I29" r:id="rId43" xr:uid="{1FA1272F-F1EF-ED4B-8F52-3369F01BB595}"/>
+    <hyperlink ref="M30" r:id="rId44" display="https://www.google.com.tw/maps/place/%E8%8D%96%E5%AD%90%E9%8D%8B+%E5%AE%B6%E6%A8%82%E7%A6%8F%E9%BE%9C%E5%B1%B1A7%E6%96%87%E9%9D%92%E5%BA%97/@25.0403589,121.3854987,18z/data=!3m1!4b1!4m5!3m4!1s0x3442a7eeffa65687:0xf193de6d03030a5a!8m2!3d25.0403589!4d121.386593?hl=zh-TW" xr:uid="{493F2D01-2EF4-1544-9625-767871CC044A}"/>
+    <hyperlink ref="I30" r:id="rId45" xr:uid="{0F604AB3-BEFF-2046-B537-A1F987B3C006}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/db/A7XLK-3201-RestaurantA7.xlsx
+++ b/db/A7XLK-3201-RestaurantA7.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wangtaizhong/Documents/92_WebSite/A7Xinlinkou/db/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4FE295DF-9903-574B-9C9A-AC8F89746CFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2E17671-1370-D74D-83BC-EF77899D7F06}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="27940" windowHeight="17500" xr2:uid="{EC3C71DD-AB41-7249-985D-4787F3B89605}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="27780" windowHeight="17500" xr2:uid="{EC3C71DD-AB41-7249-985D-4787F3B89605}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="330" uniqueCount="261">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="365" uniqueCount="284">
   <si>
     <t>no</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -168,10 +168,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>越南小吃</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>麵食</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -306,9 +302,6 @@
     <t>fig/XLK-321-RestaurantA7/A7XLK-3205-RestaurantA7-07.jpg</t>
   </si>
   <si>
-    <t>fig/XLK-321-RestaurantA7/A7XLK-3205-RestaurantA7-08.jpg</t>
-  </si>
-  <si>
     <t>fig/XLK-321-RestaurantA7/A7XLK-3205-RestaurantA7-09.jpg</t>
   </si>
   <si>
@@ -325,9 +318,6 @@
     <t>fig/XLK-321-RestaurantA7/A7XLK-3205-RestaurantA7-12.jpg</t>
   </si>
   <si>
-    <t>fig/XLK-321-RestaurantA7/A7XLK-3205-RestaurantA7-13.jpg</t>
-  </si>
-  <si>
     <t>fig/XLK-321-RestaurantA7/A7XLK-3205-RestaurantA7-14.jpg</t>
   </si>
   <si>
@@ -485,30 +475,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>麵餓心膳</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://www.google.com.tw/maps/place/%E9%BA%B5%E9%A4%93%E5%BF%83%E8%86%B3italiana%E7%BE%A9%E5%BC%8F%E6%96%99%E7%90%86/@25.0399443,121.3879522,18z/data=!3m1!4b1!4m5!3m4!1s0x3442a771fefa1693:0x3751e2ae6c6a4c1b!8m2!3d25.0399443!4d121.3890492?hl=zh-TW&amp;authuser=0</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>義式料理</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>桃園市龜山區文青路230號桃園區</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://www.facebook.com/homerunpasta/</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>暫停營業</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>鼎記小籠包</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -621,21 +587,6 @@
   </si>
   <si>
     <t>https://www.tipga.com/e/5814a5e93286fe1fa000fb9e</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://www.google.com.tw/maps/place/%E6%B0%B8%E5%B7%9D%E9%91%AB%E5%8F%B0%E8%B6%8A%E5%B0%8F%E5%90%83/@25.0402635,121.3856894,17z/data=!4m8!1m2!2m1!1z5rC45bed6ZGrIEE35paH6Z2S5bqX!3m4!1s0x3442a76e174b7663:0x539707a537779d4e!8m2!3d25.0402964!4d121.3876816?hl=zh-TW&amp;authuser=0</t>
-  </si>
-  <si>
-    <t>永川鑫台越河粉</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>桃園市龜山區文青路161號</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>0928-223-959</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -718,12 +669,6 @@
   </si>
   <si>
     <t>&lt;p&gt;
-   資訊: &lt;a style="button" class="btn btn-info"  href="https://tcwang.github.io/A7Xinlinkou/fig/XLK-321-RestaurantA7/A7XLK-3205-RestaurantA7-13-菜單.jpg"&gt;菜單&lt;/a&gt; &amp;nbsp; 
-&lt;/p&gt;</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>&lt;p&gt;
    資訊: &lt;a style="button" class="btn btn-info"  href="https://www.hongya88.com.tw/TW/News/Event?guid=21050510425813&amp;category=al"&gt;官網&lt;/a&gt; &amp;nbsp; 
 &lt;/p&gt;</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -1128,6 +1073,165 @@
   </si>
   <si>
     <t>10:30 - 20:00, 週六日公休</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>109</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>110</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>fig/XLK-321-RestaurantA7/A7XLK-3201-RestaurantA7-09.jpeg</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>fig/XLK-321-RestaurantA7/A7XLK-3201-RestaurantA7-10.jpeg</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.google.com.tw/maps/place/%E5%92%95%E5%92%95%E9%9B%9E%E6%97%A9%E5%8D%88%E9%A4%90%E5%BA%97/@25.0543625,121.3814856,17z/data=!3m1!4b1!4m5!3m4!1s0x3442a71710785bb7:0xb8f25ff0936c61c0!8m2!3d25.0543625!4d121.3836796?hl=zh-TW&amp;authuser=0</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>咕咕雞早午餐店</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>桃園市龜山區長慶二街115號</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>03-327-9319</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>06:00 - 13:00</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;p&gt;
+   資訊: &lt;a style="button" class="btn btn-info"  href="https://www.google.com.tw/maps/place/%E5%92%95%E5%92%95%E9%9B%9E%E6%97%A9%E5%8D%88%E9%A4%90%E5%BA%97/@25.0543625,121.3836796,3a,75y,90t/data=!3m8!1e2!3m6!1sAF1QipNqN0k7OKTziTXsVTouQLKotUTmV6dwBWbV9_Zw!2e10!3e12!6shttps:%2F%2Flh5.googleusercontent.com%2Fp%2FAF1QipNqN0k7OKTziTXsVTouQLKotUTmV6dwBWbV9_Zw%3Dw224-h298-k-no!7i3024!8i4032!4m7!3m6!1s0x3442a71710785bb7:0xb8f25ff0936c61c0!8m2!3d25.0543625!4d121.3836796!14m1!1BCgIYIQ?hl=zh-TW&amp;authuser=0"&gt;菜單&lt;/a&gt; &amp;nbsp; 
+&lt;/p&gt;</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>新井茶</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.google.com.tw/maps/place/%E6%96%B0%E4%BA%95%E8%8C%B6-%E9%BE%9C%E5%B1%B1%E9%95%B7%E6%85%B6%E5%BA%97/@25.0551903,121.3817299,17z/data=!3m1!4b1!4m5!3m4!1s0x3442a7957e81ea8d:0xe8c57f8ae1daa721!8m2!3d25.0551903!4d121.3839239?hl=zh-TW&amp;authuser=0</t>
+  </si>
+  <si>
+    <t>桃園市龜山區長慶三街50號</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>0923-791-234</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>10:00 - 21:00</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.google.com.tw/maps/place/%E6%9D%BE%E6%82%85%E5%BB%9A%E6%88%BF%E3%83%BB%E6%97%A9%E5%8D%88%E9%A4%90%E3%83%BB%E7%BE%A9%E5%A4%A7%E5%88%A9%E9%BA%B5%E3%83%BB%E7%87%89%E9%A3%AF/@25.0486267,121.3801386,17z/data=!3m1!4b1!4m5!3m4!1s0x3442a79e5ab72d47:0x662579310e50e0fb!8m2!3d25.0486219!4d121.3823326?hl=zh-TW&amp;authuser=0</t>
+  </si>
+  <si>
+    <t>fig/XLK-321-RestaurantA7/A7XLK-3203-A7Restaurant-08.jpeg</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>松悅廚房</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>桃園市龜山區華亞三路39巷28號</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>0965-120-989</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>06:00 - 13:30, 17:00 - 21:00</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;p&gt;
+   資訊: &lt;a style="button" class="btn btn-info"  href="https://www.ubereats.com/tw/store/%E6%9D%BE%E6%82%85%E5%BB%9A%E6%88%BF-%E7%BE%A9%E5%A4%A7%E5%88%A9%E9%BA%B5/g0_Ct5jyWleitUjB-Hq5aw?diningMode=DELIVERY&amp;pl=JTdCJTIyYWRkcmVzcyUyMiUzQSUyMkphZGUlMjBEeW5hc3R5JTIyJTJDJTIycmVmZXJlbmNlJTIyJTNBJTIyZjgyZTA1YTItODE2NS0xMGU4LWQ3M2QtNDMwYzIyOWY5MjA4JTIyJTJDJTIycmVmZXJlbmNlVHlwZSUyMiUzQSUyMnViZXJfcGxhY2VzJTIyJTJDJTIybGF0aXR1ZGUlMjIlM0E0OS4yODAzOSUyQyUyMmxvbmdpdHVkZSUyMiUzQS0xMjMuMTAxMjglN0Q%3D"&gt;Uber Eats&lt;/a&gt; &amp;nbsp; 
+&lt;a style="button" class="btn btn-info"  href="https://www.google.com.tw/maps/place/%E6%9D%BE%E6%82%85%E5%BB%9A%E6%88%BF%E3%83%BB%E6%97%A9%E5%8D%88%E9%A4%90%E3%83%BB%E7%BE%A9%E5%A4%A7%E5%88%A9%E9%BA%B5%E3%83%BB%E7%87%89%E9%A3%AF/@25.0486219,121.3823326,3a,75y,90t/data=!3m8!1e2!3m6!1sAF1QipN7HDjrR0xJaTEW_pmIgqTfsKny5jlCuNwQHzFZ!2e10!3e12!6shttps:%2F%2Flh5.googleusercontent.com%2Fp%2FAF1QipN7HDjrR0xJaTEW_pmIgqTfsKny5jlCuNwQHzFZ%3Dw237-h298-k-no!7i1440!8i1807!4m16!1m8!3m7!1s0x3442a79e5ab72d47:0x662579310e50e0fb!2z5p2-5oKF5bua5oi_44O75pep5Y2I6aSQ44O7576p5aSn5Yip6bq144O754eJ6aOv!8m2!3d25.0486219!4d121.3823326!14m1!1BCgIYIQ!3m6!1s0x3442a79e5ab72d47:0x662579310e50e0fb!8m2!3d25.0486219!4d121.3823326!14m1!1BCgIYIQ?hl=zh-TW&amp;authuser=0"&gt;菜單&lt;/a&gt; &amp;nbsp;
+&lt;/p&gt;</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>愛呷甜甜</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.google.com.tw/maps/place/%E6%84%9B%E5%91%B7%E7%94%9C%E7%94%9C/@25.048889,121.3824569,19.22z/data=!4m5!3m4!1s0x3442a7ed1dea1c7f:0x18ec42ce9cb28129!8m2!3d25.0488842!4d121.3817747?hl=zh-TW&amp;authuser=0</t>
+  </si>
+  <si>
+    <t>fig/XLK-321-RestaurantA7/A7XLK-3203-A7Restaurant-09.jpeg</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>fig/XLK-321-RestaurantA7/A7XLK-3203-A7Restaurant-10.jpeg</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>桃園市龜山區華亞三路39巷26號</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>0971-667-360</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>11:00 - 20:00</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.facebook.com/%E6%84%9B%E5%91%B7%E7%94%9C%E7%94%9C-100272542698094/</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;p&gt;
+   資訊: 
+&lt;a style="button" class="btn btn-info"  href="https://www.facebook.com/%E6%84%9B%E5%91%B7%E7%94%9C%E7%94%9C-100272542698094/menu/"&gt;菜單&lt;/a&gt; &amp;nbsp;
+&lt;/p&gt;</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>金壹湯滷味</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.google.com.tw/maps/place/%E9%87%91%E5%A3%B9%E6%B9%AF%E6%BB%B7%E5%91%B3/@25.048914,121.3819749,19.22z/data=!4m5!3m4!1s0x3442a7c8b50d2039:0xec7fd2faf7dfe798!8m2!3d25.0490978!4d121.3813163?hl=zh-TW&amp;authuser=0</t>
+  </si>
+  <si>
+    <t>桃園市龜山區華亞三路39巷16號1樓</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>0908-886-885</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;p&gt;
+   資訊: 
+&lt;a style="button" class="btn btn-info"  href="https://www.ubereats.com/tw/store/%E9%87%91%E5%A3%B9%E6%B9%AF-%E9%8D%8B%E7%87%92%E9%BA%B5/Mer5Ln6WUWyxbu8_OFtm0Q?diningMode=DELIVERY&amp;pl=JTdCJTIyYWRkcmVzcyUyMiUzQSUyMkphZGUlMjBEeW5hc3R5JTIyJTJDJTIycmVmZXJlbmNlJTIyJTNBJTIyZjgyZTA1YTItODE2NS0xMGU4LWQ3M2QtNDMwYzIyOWY5MjA4JTIyJTJDJTIycmVmZXJlbmNlVHlwZSUyMiUzQSUyMnViZXJfcGxhY2VzJTIyJTJDJTIybGF0aXR1ZGUlMjIlM0E0OS4yODAzOSUyQyUyMmxvbmdpdHVkZSUyMiUzQS0xMjMuMTAxMjglN0Q%3D&amp;utm_campaign=place-action-link&amp;utm_medium=organic&amp;utm_source=google"&gt;Uber Eats&lt;/a&gt; &amp;nbsp;
+&lt;/p&gt;</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;p&gt;
+   資訊: 
+&lt;a style="button" class="btn btn-info"  href="fig/XLK-321-RestaurantA7/A7XLK-3201-RestaurantA7-10 新井茶.jpeg"&gt;菜單&lt;/a&gt;,
+&lt;a style="button" class="btn btn-info"  href="https://www.ubereats.com/tw/store/%E6%96%B0%E4%BA%95%E8%8C%B6-%E9%BE%9C%E5%B1%B1%E9%95%B7%E6%85%B6%E5%BA%97/r4RkIP-bX0yyYwC6zyUpfQ?diningMode=DELIVERY&amp;pl=JTdCJTIyYWRkcmVzcyUyMiUzQSUyMkphZGUlMjBEeW5hc3R5JTIyJTJDJTIycmVmZXJlbmNlJTIyJTNBJTIyZjgyZTA1YTItODE2NS0xMGU4LWQ3M2QtNDMwYzIyOWY5MjA4JTIyJTJDJTIycmVmZXJlbmNlVHlwZSUyMiUzQSUyMnViZXJfcGxhY2VzJTIyJTJDJTIybGF0aXR1ZGUlMjIlM0E0OS4yODAzOSUyQyUyMmxvbmdpdHVkZSUyMiUzQS0xMjMuMTAxMjglN0Q%3D&amp;utm_campaign=place-action-link&amp;utm_medium=organic&amp;utm_source=google"&gt;Uber Eats&lt;/a&gt;
+&lt;/p&gt;</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -1548,9 +1652,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D43F91F4-866F-584C-A1A3-A0D1F56F484D}">
-  <dimension ref="A1:M30"/>
+  <dimension ref="A1:M33"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
+    <col min="2" max="2" width="18.83203125" customWidth="1"/>
     <col min="3" max="3" width="10.1640625" customWidth="1"/>
     <col min="4" max="4" width="24.83203125" customWidth="1"/>
     <col min="5" max="5" width="14" style="10" customWidth="1"/>
@@ -1594,7 +1699,7 @@
         <v>9</v>
       </c>
       <c r="K1" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="L1" s="2" t="s">
         <v>10</v>
@@ -1603,755 +1708,765 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:13" ht="96">
+    <row r="2" spans="1:13" ht="240">
       <c r="A2" s="1" t="s">
-        <v>189</v>
+        <v>248</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>190</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>28</v>
+        <v>257</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>184</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>191</v>
+        <v>259</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>192</v>
+        <v>260</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>193</v>
+        <v>261</v>
       </c>
       <c r="G2" s="2"/>
       <c r="H2" s="2" t="s">
-        <v>194</v>
+        <v>250</v>
       </c>
       <c r="I2" s="2"/>
       <c r="J2" s="2" t="s">
         <v>18</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>196</v>
+        <v>182</v>
       </c>
       <c r="L2" s="4" t="s">
-        <v>195</v>
-      </c>
-      <c r="M2" s="2"/>
-    </row>
-    <row r="3" spans="1:13" ht="192">
+        <v>283</v>
+      </c>
+      <c r="M2" s="2" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" ht="96">
       <c r="A3" s="1" t="s">
-        <v>55</v>
+        <v>175</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>12</v>
+        <v>176</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>14</v>
+        <v>177</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>15</v>
+        <v>178</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>16</v>
+        <v>179</v>
       </c>
       <c r="G3" s="2"/>
       <c r="H3" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="I3" s="3" t="s">
-        <v>49</v>
-      </c>
+        <v>180</v>
+      </c>
+      <c r="I3" s="2"/>
       <c r="J3" s="2" t="s">
         <v>18</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>196</v>
+        <v>182</v>
       </c>
       <c r="L3" s="4" t="s">
-        <v>179</v>
-      </c>
-      <c r="M3" s="3" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="128">
+        <v>181</v>
+      </c>
+      <c r="M3" s="2"/>
+    </row>
+    <row r="4" spans="1:13" ht="192">
       <c r="A4" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>24</v>
-      </c>
+        <v>16</v>
+      </c>
+      <c r="G4" s="2"/>
       <c r="H4" s="2" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>26</v>
+        <v>48</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>18</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>196</v>
+        <v>182</v>
       </c>
       <c r="L4" s="4" t="s">
-        <v>178</v>
+        <v>165</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="96">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" ht="128">
       <c r="A5" s="1" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="G5" s="2"/>
+        <v>23</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>24</v>
+      </c>
       <c r="H5" s="2" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>18</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>196</v>
+        <v>182</v>
       </c>
       <c r="L5" s="4" t="s">
-        <v>177</v>
-      </c>
-      <c r="M5" s="2"/>
-    </row>
-    <row r="6" spans="1:13" ht="128">
+        <v>164</v>
+      </c>
+      <c r="M5" s="3" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" ht="96">
       <c r="A6" s="1" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="G6" s="3" t="s">
-        <v>40</v>
-      </c>
+        <v>31</v>
+      </c>
+      <c r="G6" s="2"/>
       <c r="H6" s="2" t="s">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>18</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>196</v>
+        <v>182</v>
       </c>
       <c r="L6" s="4" t="s">
-        <v>176</v>
-      </c>
-      <c r="M6" s="3" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" ht="129">
+        <v>163</v>
+      </c>
+      <c r="M6" s="2"/>
+    </row>
+    <row r="7" spans="1:13" ht="128">
       <c r="A7" s="1" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="C7" s="5" t="s">
         <v>35</v>
       </c>
+      <c r="C7" s="1" t="s">
+        <v>28</v>
+      </c>
       <c r="D7" s="2" t="s">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="F7" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="G7" s="6"/>
+        <v>37</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>39</v>
+      </c>
       <c r="H7" s="2" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>187</v>
+        <v>41</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>18</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>196</v>
+        <v>182</v>
       </c>
       <c r="L7" s="4" t="s">
-        <v>175</v>
+        <v>162</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" ht="192">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" ht="129">
       <c r="A8" s="1" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>214</v>
+        <v>42</v>
       </c>
       <c r="C8" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="F8" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="G8" s="6"/>
+      <c r="H8" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="J8" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="K8" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="L8" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="M8" s="3" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" ht="176">
+      <c r="A9" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="F9" s="6" t="s">
+        <v>255</v>
+      </c>
+      <c r="G9" s="6"/>
+      <c r="H9" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="I9" s="3"/>
+      <c r="J9" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="K9" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="L9" s="8" t="s">
+        <v>256</v>
+      </c>
+      <c r="M9" s="3" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" ht="192">
+      <c r="A10" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="C10" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="D8" s="2" t="s">
-        <v>215</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>217</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>218</v>
-      </c>
-      <c r="G8" s="2"/>
-      <c r="H8" s="2" t="s">
-        <v>220</v>
-      </c>
-      <c r="I8" s="3"/>
-      <c r="J8" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="K8" s="2" t="s">
-        <v>196</v>
-      </c>
-      <c r="L8" s="4" t="s">
-        <v>219</v>
-      </c>
-      <c r="M8" s="3" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13" ht="80">
-      <c r="A9">
-        <v>501</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="C9" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="H9" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="I9" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="J9" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="K9" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="L9" s="8" t="s">
-        <v>174</v>
-      </c>
-      <c r="M9" s="3" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13" ht="208">
-      <c r="A10">
-        <v>502</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="C10" s="5" t="s">
-        <v>62</v>
-      </c>
       <c r="D10" s="2" t="s">
-        <v>86</v>
+        <v>201</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>87</v>
+        <v>203</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>88</v>
-      </c>
+        <v>204</v>
+      </c>
+      <c r="G10" s="2"/>
       <c r="H10" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>89</v>
-      </c>
+        <v>206</v>
+      </c>
+      <c r="I10" s="3"/>
       <c r="J10" s="2" t="s">
-        <v>81</v>
+        <v>47</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="L10" s="8" t="s">
-        <v>173</v>
+        <v>182</v>
+      </c>
+      <c r="L10" s="4" t="s">
+        <v>205</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>85</v>
+        <v>202</v>
       </c>
     </row>
     <row r="11" spans="1:13" ht="80">
       <c r="A11">
+        <v>501</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="I11" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="J11" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="K11" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="L11" s="8" t="s">
+        <v>160</v>
+      </c>
+      <c r="M11" s="3" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" ht="208">
+      <c r="A12">
+        <v>502</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="I12" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="J12" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="K12" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="L12" s="8" t="s">
+        <v>159</v>
+      </c>
+      <c r="M12" s="3" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" ht="80">
+      <c r="A13">
         <v>503</v>
       </c>
-      <c r="B11" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="C11" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="H11" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="I11" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="J11" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="K11" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="L11" s="8" t="s">
-        <v>172</v>
-      </c>
-      <c r="M11" s="3" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13" ht="80">
-      <c r="A12">
-        <v>504</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="C12" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="H12" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="I12" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="J12" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="K12" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="L12" s="8" t="s">
-        <v>171</v>
-      </c>
-      <c r="M12" s="3" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13" ht="192">
-      <c r="A13">
-        <v>505</v>
-      </c>
       <c r="B13" s="2" t="s">
-        <v>101</v>
+        <v>87</v>
       </c>
       <c r="C13" s="5" t="s">
         <v>28</v>
       </c>
       <c r="D13" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="I13" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="J13" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="K13" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="L13" s="8" t="s">
+        <v>158</v>
+      </c>
+      <c r="M13" s="3" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" ht="80">
+      <c r="A14">
+        <v>504</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="J14" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="K14" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="L14" s="8" t="s">
+        <v>157</v>
+      </c>
+      <c r="M14" s="3" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" ht="192">
+      <c r="A15">
+        <v>505</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="I15" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="E13" s="1" t="s">
+      <c r="J15" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="K15" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="L15" s="8" t="s">
+        <v>150</v>
+      </c>
+      <c r="M15" s="3" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" ht="192">
+      <c r="A16">
+        <v>506</v>
+      </c>
+      <c r="B16" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="F13" s="2" t="s">
+      <c r="C16" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="I16" t="s">
+        <v>107</v>
+      </c>
+      <c r="J16" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="K16" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="L16" s="8" t="s">
+        <v>151</v>
+      </c>
+      <c r="M16" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="H13" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="I13" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="J13" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="K13" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="L13" s="8" t="s">
-        <v>163</v>
-      </c>
-      <c r="M13" s="3" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13" ht="192">
-      <c r="A14">
-        <v>506</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="C14" s="5" t="s">
+    </row>
+    <row r="17" spans="1:13" ht="144">
+      <c r="A17">
+        <v>507</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="C17" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="I17" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="J17" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="K17" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="L17" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="M17" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" ht="240">
+      <c r="A18">
+        <v>509</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="C18" s="5" t="s">
+        <v>116</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="I18" t="s">
+        <v>123</v>
+      </c>
+      <c r="J18" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="K18" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="L18" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="M18" s="3" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" ht="176">
+      <c r="A19">
+        <v>510</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="C19" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="D14" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="E14" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="F14" s="2" t="s">
+      <c r="D19" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="I19" s="3" t="s">
         <v>129</v>
       </c>
-      <c r="H14" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="I14" t="s">
-        <v>110</v>
-      </c>
-      <c r="J14" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="K14" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="L14" s="8" t="s">
-        <v>164</v>
-      </c>
-      <c r="M14" s="3" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13" ht="144">
-      <c r="A15">
-        <v>507</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="C15" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="E15" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="F15" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="H15" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="I15" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="J15" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="K15" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="L15" s="4" t="s">
-        <v>165</v>
-      </c>
-      <c r="M15" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="16" spans="1:13">
-      <c r="A16">
-        <v>508</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="C16" s="5" t="s">
-        <v>120</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="F16" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="H16" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="I16" s="7" t="s">
-        <v>122</v>
-      </c>
-      <c r="J16" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="K16" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="M16" s="3" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="17" spans="1:13" ht="240">
-      <c r="A17">
-        <v>509</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="C17" s="5" t="s">
+      <c r="J19" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="K19" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="L19" s="9" t="s">
+        <v>154</v>
+      </c>
+      <c r="M19" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="D17" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="E17" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="F17" s="2" t="s">
+    </row>
+    <row r="20" spans="1:13" ht="144">
+      <c r="A20">
+        <v>511</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="C20" s="5" t="s">
         <v>131</v>
       </c>
-      <c r="H17" s="2" t="s">
+      <c r="D20" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="H20" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="I17" t="s">
+      <c r="I20" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="J20" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="K20" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="L20" s="9" t="s">
+        <v>155</v>
+      </c>
+      <c r="M20" s="2" t="s">
         <v>132</v>
       </c>
-      <c r="J17" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="K17" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="L17" s="4" t="s">
-        <v>166</v>
-      </c>
-      <c r="M17" s="3" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="18" spans="1:13" ht="176">
-      <c r="A18">
-        <v>510</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="C18" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="E18" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="F18" s="2" t="s">
+    </row>
+    <row r="21" spans="1:13" ht="304">
+      <c r="A21">
+        <v>512</v>
+      </c>
+      <c r="B21" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="H18" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="I18" s="3" t="s">
+      <c r="C21" s="5" t="s">
         <v>138</v>
       </c>
-      <c r="J18" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="K18" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="L18" s="9" t="s">
-        <v>167</v>
-      </c>
-      <c r="M18" s="3" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="19" spans="1:13" ht="144">
-      <c r="A19">
-        <v>511</v>
-      </c>
-      <c r="B19" s="2" t="s">
+      <c r="D21" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="I21" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="J21" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="K21" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="L21" s="9" t="s">
+        <v>156</v>
+      </c>
+      <c r="M21" s="3" t="s">
         <v>139</v>
-      </c>
-      <c r="C19" s="5" t="s">
-        <v>140</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="E19" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="F19" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="H19" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="I19" s="3" t="s">
-        <v>145</v>
-      </c>
-      <c r="J19" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="K19" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="L19" s="9" t="s">
-        <v>168</v>
-      </c>
-      <c r="M19" s="2" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="20" spans="1:13" ht="304">
-      <c r="A20">
-        <v>512</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="C20" s="5" t="s">
-        <v>147</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>149</v>
-      </c>
-      <c r="E20" s="1" t="s">
-        <v>150</v>
-      </c>
-      <c r="F20" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="H20" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="I20" s="3" t="s">
-        <v>152</v>
-      </c>
-      <c r="J20" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="K20" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="L20" s="9" t="s">
-        <v>169</v>
-      </c>
-      <c r="M20" s="3" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="21" spans="1:13" ht="96">
-      <c r="A21">
-        <v>513</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="C21" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="E21" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="H21" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="J21" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="K21" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="L21" s="9" t="s">
-        <v>170</v>
-      </c>
-      <c r="M21" t="s">
-        <v>153</v>
       </c>
     </row>
     <row r="22" spans="1:13">
@@ -2359,34 +2474,34 @@
         <v>514</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>157</v>
+        <v>144</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>125</v>
+        <v>116</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>159</v>
+        <v>146</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>160</v>
+        <v>147</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>161</v>
+        <v>148</v>
       </c>
       <c r="H22" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="J22" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="I22" s="3" t="s">
-        <v>162</v>
-      </c>
-      <c r="J22" s="2" t="s">
-        <v>81</v>
-      </c>
       <c r="K22" s="2" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="M22" s="3" t="s">
-        <v>158</v>
+        <v>145</v>
       </c>
     </row>
     <row r="23" spans="1:13" ht="96">
@@ -2394,35 +2509,35 @@
         <v>515</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>181</v>
+        <v>167</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>180</v>
+        <v>166</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>182</v>
+        <v>168</v>
       </c>
       <c r="E23" s="1"/>
       <c r="F23" s="2" t="s">
-        <v>183</v>
+        <v>169</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>186</v>
+        <v>172</v>
       </c>
       <c r="I23" s="7" t="s">
-        <v>184</v>
+        <v>170</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="K23" s="2" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="L23" s="8" t="s">
-        <v>188</v>
+        <v>174</v>
       </c>
       <c r="M23" t="s">
-        <v>185</v>
+        <v>171</v>
       </c>
     </row>
     <row r="24" spans="1:13" ht="224">
@@ -2430,313 +2545,423 @@
         <v>307</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>252</v>
+        <v>238</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>257</v>
+        <v>243</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>258</v>
+        <v>244</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>260</v>
+        <v>246</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>254</v>
+        <v>240</v>
       </c>
       <c r="I24" s="7"/>
       <c r="J24" s="2" t="s">
-        <v>256</v>
+        <v>242</v>
       </c>
       <c r="K24" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="L24" s="9" t="s">
+        <v>245</v>
+      </c>
+      <c r="M24" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" ht="192">
+      <c r="A25">
+        <v>310</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="C25" s="5" t="s">
+        <v>239</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="F25" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>272</v>
+      </c>
+      <c r="I25" s="7"/>
+      <c r="J25" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="K25" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="L25" s="9" t="s">
+        <v>282</v>
+      </c>
+      <c r="M25" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" ht="96">
+      <c r="A26">
+        <v>309</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="C26" s="5" t="s">
+        <v>184</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="F26" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>271</v>
+      </c>
+      <c r="I26" s="7" t="s">
+        <v>276</v>
+      </c>
+      <c r="J26" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="K26" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="L26" s="9" t="s">
+        <v>277</v>
+      </c>
+      <c r="M26" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" ht="409.6">
+      <c r="A27">
+        <v>308</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="C27" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="F27" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="I27" s="7"/>
+      <c r="J27" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="K27" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="L27" s="9" t="s">
+        <v>268</v>
+      </c>
+      <c r="M27" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13" ht="335">
+      <c r="A28">
+        <v>301</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="C28" s="5" t="s">
+        <v>184</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="E28" s="10" t="s">
+        <v>186</v>
+      </c>
+      <c r="F28" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="I28" s="7" t="s">
+        <v>188</v>
+      </c>
+      <c r="J28" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="K28" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="L28" s="9" t="s">
+        <v>190</v>
+      </c>
+      <c r="M28" s="3" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13" ht="224">
+      <c r="A29">
+        <v>302</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="C29" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="E29" s="10" t="s">
+        <v>195</v>
+      </c>
+      <c r="F29" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="H29" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="I29" s="7" t="s">
+        <v>197</v>
+      </c>
+      <c r="J29" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="K29" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="L29" s="8" t="s">
+        <v>198</v>
+      </c>
+      <c r="M29" s="7" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13" ht="208">
+      <c r="A30">
+        <v>303</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="E30" s="10" t="s">
+        <v>211</v>
+      </c>
+      <c r="F30" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="H30" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="I30" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="J30" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="K30" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="L30" s="9" t="s">
+        <v>219</v>
+      </c>
+      <c r="M30" s="7" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13" ht="112">
+      <c r="A31">
+        <v>304</v>
+      </c>
+      <c r="B31" s="2" t="s">
         <v>221</v>
       </c>
-      <c r="L24" s="9" t="s">
-        <v>259</v>
-      </c>
-      <c r="M24" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="25" spans="1:13" ht="335">
-      <c r="A25">
-        <v>301</v>
-      </c>
-      <c r="B25" s="2" t="s">
-        <v>197</v>
-      </c>
-      <c r="C25" s="5" t="s">
-        <v>198</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>199</v>
-      </c>
-      <c r="E25" s="10" t="s">
-        <v>200</v>
-      </c>
-      <c r="F25" s="2" t="s">
-        <v>201</v>
-      </c>
-      <c r="H25" s="2" t="s">
-        <v>213</v>
-      </c>
-      <c r="I25" s="7" t="s">
-        <v>202</v>
-      </c>
-      <c r="J25" s="2" t="s">
-        <v>203</v>
-      </c>
-      <c r="K25" s="2" t="s">
-        <v>221</v>
-      </c>
-      <c r="L25" s="9" t="s">
-        <v>204</v>
-      </c>
-      <c r="M25" s="3" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="26" spans="1:13" ht="224">
-      <c r="A26">
-        <v>302</v>
-      </c>
-      <c r="B26" s="2" t="s">
-        <v>206</v>
-      </c>
-      <c r="C26" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>208</v>
-      </c>
-      <c r="E26" s="10" t="s">
-        <v>209</v>
-      </c>
-      <c r="F26" s="2" t="s">
-        <v>210</v>
-      </c>
-      <c r="H26" s="2" t="s">
+      <c r="C31" s="5" t="s">
+        <v>116</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="E31" s="10" t="s">
+        <v>223</v>
+      </c>
+      <c r="F31" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="H31" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="I31" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="J31" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="K31" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="L31" s="9" t="s">
+        <v>225</v>
+      </c>
+      <c r="M31" s="3" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13" ht="112">
+      <c r="A32">
+        <v>305</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="C32" s="5" t="s">
+        <v>116</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="E32" s="10" t="s">
+        <v>228</v>
+      </c>
+      <c r="F32" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="H32" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="I32" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="J32" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="K32" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="L32" s="9" t="s">
+        <v>230</v>
+      </c>
+      <c r="M32" s="3" t="s">
         <v>226</v>
       </c>
-      <c r="I26" s="7" t="s">
-        <v>211</v>
-      </c>
-      <c r="J26" s="2" t="s">
-        <v>203</v>
-      </c>
-      <c r="K26" s="2" t="s">
-        <v>221</v>
-      </c>
-      <c r="L26" s="8" t="s">
-        <v>212</v>
-      </c>
-      <c r="M26" s="7" t="s">
+    </row>
+    <row r="33" spans="1:13" ht="144">
+      <c r="A33">
+        <v>306</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="C33" s="5" t="s">
+        <v>233</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="E33" s="10" t="s">
+        <v>234</v>
+      </c>
+      <c r="F33" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="H33" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="I33" s="3" t="s">
+        <v>235</v>
+      </c>
+      <c r="J33" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="K33" s="2" t="s">
         <v>207</v>
       </c>
-    </row>
-    <row r="27" spans="1:13" ht="208">
-      <c r="A27">
-        <v>303</v>
-      </c>
-      <c r="B27" s="2" t="s">
-        <v>222</v>
-      </c>
-      <c r="C27" s="2" t="s">
+      <c r="L33" s="9" t="s">
+        <v>237</v>
+      </c>
+      <c r="M33" s="3" t="s">
         <v>232</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>224</v>
-      </c>
-      <c r="E27" s="10" t="s">
-        <v>225</v>
-      </c>
-      <c r="F27" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="H27" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="I27" s="3" t="s">
-        <v>231</v>
-      </c>
-      <c r="J27" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="K27" s="2" t="s">
-        <v>221</v>
-      </c>
-      <c r="L27" s="9" t="s">
-        <v>233</v>
-      </c>
-      <c r="M27" s="7" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="28" spans="1:13" ht="112">
-      <c r="A28">
-        <v>304</v>
-      </c>
-      <c r="B28" s="2" t="s">
-        <v>235</v>
-      </c>
-      <c r="C28" s="5" t="s">
-        <v>125</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>236</v>
-      </c>
-      <c r="E28" s="10" t="s">
-        <v>237</v>
-      </c>
-      <c r="F28" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="H28" s="2" t="s">
-        <v>228</v>
-      </c>
-      <c r="I28" s="3" t="s">
-        <v>238</v>
-      </c>
-      <c r="J28" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="K28" s="2" t="s">
-        <v>221</v>
-      </c>
-      <c r="L28" s="9" t="s">
-        <v>239</v>
-      </c>
-      <c r="M28" s="3" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="29" spans="1:13" ht="112">
-      <c r="A29">
-        <v>305</v>
-      </c>
-      <c r="B29" s="2" t="s">
-        <v>241</v>
-      </c>
-      <c r="C29" s="5" t="s">
-        <v>125</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>236</v>
-      </c>
-      <c r="E29" s="10" t="s">
-        <v>242</v>
-      </c>
-      <c r="F29" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="H29" s="2" t="s">
-        <v>229</v>
-      </c>
-      <c r="I29" s="3" t="s">
-        <v>243</v>
-      </c>
-      <c r="J29" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="K29" s="2" t="s">
-        <v>221</v>
-      </c>
-      <c r="L29" s="9" t="s">
-        <v>244</v>
-      </c>
-      <c r="M29" s="3" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="30" spans="1:13" ht="144">
-      <c r="A30">
-        <v>306</v>
-      </c>
-      <c r="B30" s="2" t="s">
-        <v>245</v>
-      </c>
-      <c r="C30" s="5" t="s">
-        <v>247</v>
-      </c>
-      <c r="D30" s="2" t="s">
-        <v>236</v>
-      </c>
-      <c r="E30" s="10" t="s">
-        <v>248</v>
-      </c>
-      <c r="F30" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="H30" s="2" t="s">
-        <v>230</v>
-      </c>
-      <c r="I30" s="3" t="s">
-        <v>249</v>
-      </c>
-      <c r="J30" s="2" t="s">
-        <v>250</v>
-      </c>
-      <c r="K30" s="2" t="s">
-        <v>221</v>
-      </c>
-      <c r="L30" s="9" t="s">
-        <v>251</v>
-      </c>
-      <c r="M30" s="3" t="s">
-        <v>246</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="I4" r:id="rId1" xr:uid="{C4FC3919-D074-B04C-8404-BC6DE733F558}"/>
-    <hyperlink ref="I5" r:id="rId2" xr:uid="{F003A365-8C23-084B-B31A-663E82D27E11}"/>
-    <hyperlink ref="G6" r:id="rId3" xr:uid="{7AEBC60D-47CB-2041-BB0C-5BB638DE9DEC}"/>
-    <hyperlink ref="I6" r:id="rId4" xr:uid="{E2777161-F973-9B42-BC21-88DA80C19FD3}"/>
-    <hyperlink ref="M3" r:id="rId5" xr:uid="{2E20CE02-8C51-1045-B84E-5304199A5CEC}"/>
-    <hyperlink ref="M4" r:id="rId6" xr:uid="{21CC0B31-826D-6549-8434-94B01CACE62D}"/>
-    <hyperlink ref="M6" r:id="rId7" xr:uid="{24019989-F9BD-E143-A40C-50EE4DDF5BD1}"/>
-    <hyperlink ref="M7" r:id="rId8" display="https://www.google.com.tw/maps/place/%E5%8A%89%E5%A6%B9%E9%8D%8B%E7%87%92%E6%84%8F%E9%BA%B5-%E6%A1%83%E5%9C%92%E6%9E%97%E5%8F%A3%E5%BA%97/@25.0548468,121.3827894,19.1z/data=!4m5!3m4!1s0x3442a7b02079176f:0x78906ae51c7f6abc!8m2!3d25.0553573!4d121.3840157?hl=zh-TW&amp;authuser=0" xr:uid="{13C7C2D5-34CD-404D-BEE1-B9C104B3C41D}"/>
-    <hyperlink ref="I9" r:id="rId9" xr:uid="{D22B71CE-BEE8-4D4A-B73B-DF696843091A}"/>
-    <hyperlink ref="M9" r:id="rId10" display="https://www.google.com.tw/maps/place/%E8%83%96%E8%80%81%E7%88%B9%E7%BE%8E%E5%BC%8F%E7%82%B8%E9%9B%9EA7%E6%96%87%E9%9D%92%E5%BA%97/@25.0394257,121.3894157,19.83z/data=!4m5!3m4!1s0x3442a73165d8f2d3:0xce822b237485dc8c!8m2!3d25.0394354!4d121.3903716?hl=zh-TW&amp;authuser=0" xr:uid="{C64399C5-4BBF-C54B-AFFF-C515FF32551F}"/>
-    <hyperlink ref="M10" r:id="rId11" display="https://www.google.com.tw/maps/place/%E8%B6%A3%E5%95%83%E7%82%B8%E7%89%A9-%E6%96%87%E9%9D%92%E5%BA%97/@25.039422,121.389821,19z/data=!4m9!1m2!2m1!1z6Laj5ZWD54K454mpQTfmlofpnZLlupc!3m5!1s0x3442a79257c7d5e1:0x96b9a8c7ea325295!8m2!3d25.0394086!4d121.3903675!15sChfotqPllYPngrjnialBN-aWh-mdkuW6l1ogIh7otqMg5ZWDIOeCuCDniakgYTcg5paHIOmdkiDlupeSAQRkZWxp?hl=zh-TW&amp;authuser=0" xr:uid="{ECDBCB9E-1A0B-2440-BEDC-B3365ABCEB46}"/>
-    <hyperlink ref="I10" r:id="rId12" xr:uid="{C84B02C1-9D57-3449-BF10-8BF8B150E1B0}"/>
-    <hyperlink ref="M11" r:id="rId13" display="https://www.google.com.tw/maps/place/MQ%E5%85%83%E6%B0%A3house/@25.0396043,121.3889924,19z/data=!4m9!1m2!2m1!1z5YWD5rCj5pep5Y2I6aSQQTfmlofpnZLlupc!3m5!1s0x3442a73b0be03237:0xb76fc65b93d291de!8m2!3d25.0395543!4d121.389809!15sChrlhYPmsKPml6nljYjppJBBN-aWh-mdkuW6lyIDiAEBWh4iHOWFg-awoyDml6kg5Y2I6aSQIGE3IOaWhyDpnZKSARRicmVha2Zhc3RfcmVzdGF1cmFudJoBJENoZERTVWhOTUc5blMwVkpRMEZuU1VSTE1tSjJWbWRCUlJBQg?hl=zh-TW&amp;authuser=0" xr:uid="{A608DFF8-5556-A348-BCCF-DF8FED89A676}"/>
-    <hyperlink ref="I11" r:id="rId14" xr:uid="{2AC2704D-3B90-7143-8538-1BCF2601B133}"/>
-    <hyperlink ref="M12" r:id="rId15" xr:uid="{BCFDF63E-46D6-4C46-A895-F2BE3AF3A43C}"/>
-    <hyperlink ref="I12" r:id="rId16" xr:uid="{DA402F63-BBBF-314A-9282-201C2F50A8E9}"/>
-    <hyperlink ref="M13" r:id="rId17" xr:uid="{62B3945D-7D85-6F41-B0AE-685C751A1E0D}"/>
-    <hyperlink ref="I13" r:id="rId18" xr:uid="{CF45B8DE-914A-2B48-BCB7-14602F96BD36}"/>
-    <hyperlink ref="M14" r:id="rId19" display="https://www.google.com.tw/maps/place/W%E3%80%82D%E6%88%91%E7%9A%84%E6%97%A9%E9%A4%90/@25.039828,121.3881883,18z/data=!4m9!1m2!2m1!1zV0TmiJHnmoTml6nppJAgQTfmlofpnZLlupc!3m5!1s0x3442a771fa73353d:0x329428879337e9d8!8m2!3d25.0396834!4d121.38925!15sChpXROaIkeeahOaXqemkkCBBN-aWh-mdkuW6l1oeIhx3ZCDmiJEg55qEIOaXqemkkCBhNyDmlocg6Z2SkgEUYnJlYWtmYXN0X3Jlc3RhdXJhbnSaASNDaFpEU1VoTk1HOW5TMFZKUTBGblNVUk5iMlZYVDFoUkVBRQ?hl=zh-TW&amp;authuser=0" xr:uid="{1A766ADC-BF5A-F54B-8857-2EC343131663}"/>
-    <hyperlink ref="I15" r:id="rId20" xr:uid="{D29C3BC2-9385-1848-8CD3-329B3FEC96D0}"/>
-    <hyperlink ref="M16" r:id="rId21" display="https://www.google.com.tw/maps/place/%E9%BA%B5%E9%A4%93%E5%BF%83%E8%86%B3italiana%E7%BE%A9%E5%BC%8F%E6%96%99%E7%90%86/@25.0399443,121.3879522,18z/data=!3m1!4b1!4m5!3m4!1s0x3442a771fefa1693:0x3751e2ae6c6a4c1b!8m2!3d25.0399443!4d121.3890492?hl=zh-TW&amp;authuser=0" xr:uid="{CFA5CDA3-DFA0-A345-802E-4E27D0DD6388}"/>
-    <hyperlink ref="I16" r:id="rId22" xr:uid="{52227806-B293-3140-BA54-19D8D37B7072}"/>
-    <hyperlink ref="M17" r:id="rId23" display="https://www.google.com.tw/maps/place/%E9%BC%8E%E8%A8%98+%E5%B0%8F%E7%B1%A0%E5%8C%85/@25.0394911,121.3880801,18z/data=!4m9!1m2!2m1!1z6byO6KiY5bCP57Gg5YyFIEE35paH6Z2S5bqX!3m5!1s0x3442a771eb8a1057:0x50474f8ab9f0306d!8m2!3d25.0399461!4d121.3891357!15sChvpvI7oqJjlsI_nsaDljIUgQTfmlofpnZLlupdaJCIi6byOIOiomCDlsI8g57GgIOWMhSBhNyDmlocg6Z2SIOW6l5IBCnJlc3RhdXJhbnSaASRDaGREU1VoTk1HOW5TMFZKUTBGblNVUlZORjlEZFd4blJSQUI?hl=zh-TW&amp;authuser=0" xr:uid="{40D2FFA0-1BA7-7D40-9492-E31751F5971E}"/>
-    <hyperlink ref="M18" r:id="rId24" display="https://www.google.com.tw/maps/place/%E6%B2%88%E5%AE%B6%E8%B1%86%E6%BC%BF/@25.0400428,121.3880621,18z/data=!4m9!1m2!2m1!1z5rKI5a626LGG5ry_IEE35paH6Z2S5bqX!3m5!1s0x3442a7e71b4fdbef:0xa7327c25e217658c!8m2!3d25.0398612!4d121.3890308!15sChjmsojlrrbosYbmvL8gQTfmlofpnZLlupdaGyIZ5rKIIOWutiDosYbmvL8gYTcg5paHIOmdkpIBFGJyZWFrZmFzdF9yZXN0YXVyYW50mgEkQ2hkRFNVaE5NRzluUzBWSlEwRm5TVU5qYWpkRU1HbFJSUkFC?hl=zh-TW&amp;authuser=0" xr:uid="{5BED3BAC-7517-6C44-8DD0-2E9AAD01210B}"/>
-    <hyperlink ref="I18" r:id="rId25" xr:uid="{FA94FB62-C3B4-F440-B546-D5651C4C1EF0}"/>
-    <hyperlink ref="I19" r:id="rId26" xr:uid="{36593C4B-5784-D647-A021-407E9C5E9859}"/>
-    <hyperlink ref="M20" r:id="rId27" xr:uid="{C10E1D29-46CE-4843-8B5F-0C73F3E21715}"/>
-    <hyperlink ref="I20" r:id="rId28" xr:uid="{4108B3FA-F736-964B-AFA8-8EA10E9958B5}"/>
-    <hyperlink ref="M22" r:id="rId29" xr:uid="{98E56C55-CA1A-F648-87ED-05DD4AEF5C71}"/>
-    <hyperlink ref="I22" r:id="rId30" xr:uid="{32037A18-7380-4045-A4B0-FCA8B0774D4F}"/>
-    <hyperlink ref="I23" r:id="rId31" xr:uid="{6F802D23-EF8F-E748-A152-E7AB9EBBC40B}"/>
-    <hyperlink ref="I7" r:id="rId32" xr:uid="{7D690390-5CDC-774F-88F8-D0A10F74092B}"/>
-    <hyperlink ref="I25" r:id="rId33" xr:uid="{3487482B-705B-934F-B345-27830D949CFF}"/>
-    <hyperlink ref="M25" r:id="rId34" xr:uid="{74F32270-5AC7-4741-9928-D33D18CF9FB3}"/>
-    <hyperlink ref="M26" r:id="rId35" xr:uid="{E246A458-07DD-CC4C-99FE-5782C2F2DFA4}"/>
-    <hyperlink ref="I26" r:id="rId36" xr:uid="{5E178450-E303-0D48-8BD2-F7009B785BA5}"/>
-    <hyperlink ref="M8" r:id="rId37" xr:uid="{14DEDDAA-9C5B-4748-8774-11268E961283}"/>
-    <hyperlink ref="M27" r:id="rId38" display="https://www.google.com.tw/maps/place/Joyfull%E5%8F%B0%E7%81%A3%E7%8F%8D%E6%9C%89%E7%A6%8F+%E9%BE%9C%E5%B1%B1%E6%96%87%E9%9D%92%E5%BA%97/@25.0404003,121.3845642,17z/data=!3m1!4b1!4m5!3m4!1s0x3442a7699aa9553d:0xe952e516cf83c284!8m2!3d25.0404003!4d121.3867529?hl=zh-TW&amp;authuser=0" xr:uid="{0F99912D-9206-1341-91D3-A8ABE82B9B7D}"/>
-    <hyperlink ref="I27" r:id="rId39" xr:uid="{B3553713-7114-F644-828F-381533D5B59C}"/>
-    <hyperlink ref="M28" r:id="rId40" xr:uid="{529979E4-4FEA-E947-96A5-E04032E634FE}"/>
-    <hyperlink ref="I28" r:id="rId41" xr:uid="{AE19FED5-B89B-B04A-AF86-C5822C140599}"/>
-    <hyperlink ref="M29" r:id="rId42" display="https://www.google.com.tw/maps/place/Yipin+Pasta+%E7%BE%A9%E5%93%81+%E5%AE%B6%E6%A8%82%E7%A6%8F%E9%BE%9C%E5%B1%B1A7%E6%96%87%E9%9D%92%E5%BA%97/@25.0405787,121.3855057,18z/data=!3m1!4b1!4m5!3m4!1s0x3442a765f994e34f:0x64cc431d298f3874!8m2!3d25.0405787!4d121.3866?hl=zh-TW" xr:uid="{665007E7-4AC9-1B4B-AF8D-A54552764742}"/>
-    <hyperlink ref="I29" r:id="rId43" xr:uid="{1FA1272F-F1EF-ED4B-8F52-3369F01BB595}"/>
-    <hyperlink ref="M30" r:id="rId44" display="https://www.google.com.tw/maps/place/%E8%8D%96%E5%AD%90%E9%8D%8B+%E5%AE%B6%E6%A8%82%E7%A6%8F%E9%BE%9C%E5%B1%B1A7%E6%96%87%E9%9D%92%E5%BA%97/@25.0403589,121.3854987,18z/data=!3m1!4b1!4m5!3m4!1s0x3442a7eeffa65687:0xf193de6d03030a5a!8m2!3d25.0403589!4d121.386593?hl=zh-TW" xr:uid="{493F2D01-2EF4-1544-9625-767871CC044A}"/>
-    <hyperlink ref="I30" r:id="rId45" xr:uid="{0F604AB3-BEFF-2046-B537-A1F987B3C006}"/>
+    <hyperlink ref="I5" r:id="rId1" xr:uid="{C4FC3919-D074-B04C-8404-BC6DE733F558}"/>
+    <hyperlink ref="I6" r:id="rId2" xr:uid="{F003A365-8C23-084B-B31A-663E82D27E11}"/>
+    <hyperlink ref="G7" r:id="rId3" xr:uid="{7AEBC60D-47CB-2041-BB0C-5BB638DE9DEC}"/>
+    <hyperlink ref="I7" r:id="rId4" xr:uid="{E2777161-F973-9B42-BC21-88DA80C19FD3}"/>
+    <hyperlink ref="M4" r:id="rId5" xr:uid="{2E20CE02-8C51-1045-B84E-5304199A5CEC}"/>
+    <hyperlink ref="M5" r:id="rId6" xr:uid="{21CC0B31-826D-6549-8434-94B01CACE62D}"/>
+    <hyperlink ref="M7" r:id="rId7" xr:uid="{24019989-F9BD-E143-A40C-50EE4DDF5BD1}"/>
+    <hyperlink ref="M8" r:id="rId8" display="https://www.google.com.tw/maps/place/%E5%8A%89%E5%A6%B9%E9%8D%8B%E7%87%92%E6%84%8F%E9%BA%B5-%E6%A1%83%E5%9C%92%E6%9E%97%E5%8F%A3%E5%BA%97/@25.0548468,121.3827894,19.1z/data=!4m5!3m4!1s0x3442a7b02079176f:0x78906ae51c7f6abc!8m2!3d25.0553573!4d121.3840157?hl=zh-TW&amp;authuser=0" xr:uid="{13C7C2D5-34CD-404D-BEE1-B9C104B3C41D}"/>
+    <hyperlink ref="I11" r:id="rId9" xr:uid="{D22B71CE-BEE8-4D4A-B73B-DF696843091A}"/>
+    <hyperlink ref="M11" r:id="rId10" display="https://www.google.com.tw/maps/place/%E8%83%96%E8%80%81%E7%88%B9%E7%BE%8E%E5%BC%8F%E7%82%B8%E9%9B%9EA7%E6%96%87%E9%9D%92%E5%BA%97/@25.0394257,121.3894157,19.83z/data=!4m5!3m4!1s0x3442a73165d8f2d3:0xce822b237485dc8c!8m2!3d25.0394354!4d121.3903716?hl=zh-TW&amp;authuser=0" xr:uid="{C64399C5-4BBF-C54B-AFFF-C515FF32551F}"/>
+    <hyperlink ref="M12" r:id="rId11" display="https://www.google.com.tw/maps/place/%E8%B6%A3%E5%95%83%E7%82%B8%E7%89%A9-%E6%96%87%E9%9D%92%E5%BA%97/@25.039422,121.389821,19z/data=!4m9!1m2!2m1!1z6Laj5ZWD54K454mpQTfmlofpnZLlupc!3m5!1s0x3442a79257c7d5e1:0x96b9a8c7ea325295!8m2!3d25.0394086!4d121.3903675!15sChfotqPllYPngrjnialBN-aWh-mdkuW6l1ogIh7otqMg5ZWDIOeCuCDniakgYTcg5paHIOmdkiDlupeSAQRkZWxp?hl=zh-TW&amp;authuser=0" xr:uid="{ECDBCB9E-1A0B-2440-BEDC-B3365ABCEB46}"/>
+    <hyperlink ref="I12" r:id="rId12" xr:uid="{C84B02C1-9D57-3449-BF10-8BF8B150E1B0}"/>
+    <hyperlink ref="M13" r:id="rId13" display="https://www.google.com.tw/maps/place/MQ%E5%85%83%E6%B0%A3house/@25.0396043,121.3889924,19z/data=!4m9!1m2!2m1!1z5YWD5rCj5pep5Y2I6aSQQTfmlofpnZLlupc!3m5!1s0x3442a73b0be03237:0xb76fc65b93d291de!8m2!3d25.0395543!4d121.389809!15sChrlhYPmsKPml6nljYjppJBBN-aWh-mdkuW6lyIDiAEBWh4iHOWFg-awoyDml6kg5Y2I6aSQIGE3IOaWhyDpnZKSARRicmVha2Zhc3RfcmVzdGF1cmFudJoBJENoZERTVWhOTUc5blMwVkpRMEZuU1VSTE1tSjJWbWRCUlJBQg?hl=zh-TW&amp;authuser=0" xr:uid="{A608DFF8-5556-A348-BCCF-DF8FED89A676}"/>
+    <hyperlink ref="I13" r:id="rId14" xr:uid="{2AC2704D-3B90-7143-8538-1BCF2601B133}"/>
+    <hyperlink ref="M14" r:id="rId15" xr:uid="{BCFDF63E-46D6-4C46-A895-F2BE3AF3A43C}"/>
+    <hyperlink ref="I14" r:id="rId16" xr:uid="{DA402F63-BBBF-314A-9282-201C2F50A8E9}"/>
+    <hyperlink ref="M15" r:id="rId17" xr:uid="{62B3945D-7D85-6F41-B0AE-685C751A1E0D}"/>
+    <hyperlink ref="I15" r:id="rId18" xr:uid="{CF45B8DE-914A-2B48-BCB7-14602F96BD36}"/>
+    <hyperlink ref="M16" r:id="rId19" display="https://www.google.com.tw/maps/place/W%E3%80%82D%E6%88%91%E7%9A%84%E6%97%A9%E9%A4%90/@25.039828,121.3881883,18z/data=!4m9!1m2!2m1!1zV0TmiJHnmoTml6nppJAgQTfmlofpnZLlupc!3m5!1s0x3442a771fa73353d:0x329428879337e9d8!8m2!3d25.0396834!4d121.38925!15sChpXROaIkeeahOaXqemkkCBBN-aWh-mdkuW6l1oeIhx3ZCDmiJEg55qEIOaXqemkkCBhNyDmlocg6Z2SkgEUYnJlYWtmYXN0X3Jlc3RhdXJhbnSaASNDaFpEU1VoTk1HOW5TMFZKUTBGblNVUk5iMlZYVDFoUkVBRQ?hl=zh-TW&amp;authuser=0" xr:uid="{1A766ADC-BF5A-F54B-8857-2EC343131663}"/>
+    <hyperlink ref="I17" r:id="rId20" xr:uid="{D29C3BC2-9385-1848-8CD3-329B3FEC96D0}"/>
+    <hyperlink ref="M18" r:id="rId21" display="https://www.google.com.tw/maps/place/%E9%BC%8E%E8%A8%98+%E5%B0%8F%E7%B1%A0%E5%8C%85/@25.0394911,121.3880801,18z/data=!4m9!1m2!2m1!1z6byO6KiY5bCP57Gg5YyFIEE35paH6Z2S5bqX!3m5!1s0x3442a771eb8a1057:0x50474f8ab9f0306d!8m2!3d25.0399461!4d121.3891357!15sChvpvI7oqJjlsI_nsaDljIUgQTfmlofpnZLlupdaJCIi6byOIOiomCDlsI8g57GgIOWMhSBhNyDmlocg6Z2SIOW6l5IBCnJlc3RhdXJhbnSaASRDaGREU1VoTk1HOW5TMFZKUTBGblNVUlZORjlEZFd4blJSQUI?hl=zh-TW&amp;authuser=0" xr:uid="{40D2FFA0-1BA7-7D40-9492-E31751F5971E}"/>
+    <hyperlink ref="M19" r:id="rId22" display="https://www.google.com.tw/maps/place/%E6%B2%88%E5%AE%B6%E8%B1%86%E6%BC%BF/@25.0400428,121.3880621,18z/data=!4m9!1m2!2m1!1z5rKI5a626LGG5ry_IEE35paH6Z2S5bqX!3m5!1s0x3442a7e71b4fdbef:0xa7327c25e217658c!8m2!3d25.0398612!4d121.3890308!15sChjmsojlrrbosYbmvL8gQTfmlofpnZLlupdaGyIZ5rKIIOWutiDosYbmvL8gYTcg5paHIOmdkpIBFGJyZWFrZmFzdF9yZXN0YXVyYW50mgEkQ2hkRFNVaE5NRzluUzBWSlEwRm5TVU5qYWpkRU1HbFJSUkFC?hl=zh-TW&amp;authuser=0" xr:uid="{5BED3BAC-7517-6C44-8DD0-2E9AAD01210B}"/>
+    <hyperlink ref="I19" r:id="rId23" xr:uid="{FA94FB62-C3B4-F440-B546-D5651C4C1EF0}"/>
+    <hyperlink ref="I20" r:id="rId24" xr:uid="{36593C4B-5784-D647-A021-407E9C5E9859}"/>
+    <hyperlink ref="M21" r:id="rId25" xr:uid="{C10E1D29-46CE-4843-8B5F-0C73F3E21715}"/>
+    <hyperlink ref="I21" r:id="rId26" xr:uid="{4108B3FA-F736-964B-AFA8-8EA10E9958B5}"/>
+    <hyperlink ref="M22" r:id="rId27" xr:uid="{98E56C55-CA1A-F648-87ED-05DD4AEF5C71}"/>
+    <hyperlink ref="I22" r:id="rId28" xr:uid="{32037A18-7380-4045-A4B0-FCA8B0774D4F}"/>
+    <hyperlink ref="I23" r:id="rId29" xr:uid="{6F802D23-EF8F-E748-A152-E7AB9EBBC40B}"/>
+    <hyperlink ref="I8" r:id="rId30" xr:uid="{7D690390-5CDC-774F-88F8-D0A10F74092B}"/>
+    <hyperlink ref="I28" r:id="rId31" xr:uid="{3487482B-705B-934F-B345-27830D949CFF}"/>
+    <hyperlink ref="M28" r:id="rId32" xr:uid="{74F32270-5AC7-4741-9928-D33D18CF9FB3}"/>
+    <hyperlink ref="M29" r:id="rId33" xr:uid="{E246A458-07DD-CC4C-99FE-5782C2F2DFA4}"/>
+    <hyperlink ref="I29" r:id="rId34" xr:uid="{5E178450-E303-0D48-8BD2-F7009B785BA5}"/>
+    <hyperlink ref="M10" r:id="rId35" xr:uid="{14DEDDAA-9C5B-4748-8774-11268E961283}"/>
+    <hyperlink ref="M30" r:id="rId36" display="https://www.google.com.tw/maps/place/Joyfull%E5%8F%B0%E7%81%A3%E7%8F%8D%E6%9C%89%E7%A6%8F+%E9%BE%9C%E5%B1%B1%E6%96%87%E9%9D%92%E5%BA%97/@25.0404003,121.3845642,17z/data=!3m1!4b1!4m5!3m4!1s0x3442a7699aa9553d:0xe952e516cf83c284!8m2!3d25.0404003!4d121.3867529?hl=zh-TW&amp;authuser=0" xr:uid="{0F99912D-9206-1341-91D3-A8ABE82B9B7D}"/>
+    <hyperlink ref="I30" r:id="rId37" xr:uid="{B3553713-7114-F644-828F-381533D5B59C}"/>
+    <hyperlink ref="M31" r:id="rId38" xr:uid="{529979E4-4FEA-E947-96A5-E04032E634FE}"/>
+    <hyperlink ref="I31" r:id="rId39" xr:uid="{AE19FED5-B89B-B04A-AF86-C5822C140599}"/>
+    <hyperlink ref="M32" r:id="rId40" display="https://www.google.com.tw/maps/place/Yipin+Pasta+%E7%BE%A9%E5%93%81+%E5%AE%B6%E6%A8%82%E7%A6%8F%E9%BE%9C%E5%B1%B1A7%E6%96%87%E9%9D%92%E5%BA%97/@25.0405787,121.3855057,18z/data=!3m1!4b1!4m5!3m4!1s0x3442a765f994e34f:0x64cc431d298f3874!8m2!3d25.0405787!4d121.3866?hl=zh-TW" xr:uid="{665007E7-4AC9-1B4B-AF8D-A54552764742}"/>
+    <hyperlink ref="I32" r:id="rId41" xr:uid="{1FA1272F-F1EF-ED4B-8F52-3369F01BB595}"/>
+    <hyperlink ref="M33" r:id="rId42" display="https://www.google.com.tw/maps/place/%E8%8D%96%E5%AD%90%E9%8D%8B+%E5%AE%B6%E6%A8%82%E7%A6%8F%E9%BE%9C%E5%B1%B1A7%E6%96%87%E9%9D%92%E5%BA%97/@25.0403589,121.3854987,18z/data=!3m1!4b1!4m5!3m4!1s0x3442a7eeffa65687:0xf193de6d03030a5a!8m2!3d25.0403589!4d121.386593?hl=zh-TW" xr:uid="{493F2D01-2EF4-1544-9625-767871CC044A}"/>
+    <hyperlink ref="I33" r:id="rId43" xr:uid="{0F604AB3-BEFF-2046-B537-A1F987B3C006}"/>
+    <hyperlink ref="M9" r:id="rId44" xr:uid="{F1C6FD45-614D-5E41-A814-2FC046758624}"/>
+    <hyperlink ref="I26" r:id="rId45" xr:uid="{6564EE13-82E2-DB44-8058-211B23573035}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/db/A7XLK-3201-RestaurantA7.xlsx
+++ b/db/A7XLK-3201-RestaurantA7.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wangtaizhong/Documents/92_WebSite/A7Xinlinkou/db/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2E17671-1370-D74D-83BC-EF77899D7F06}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91275660-5B14-7A40-8443-4E158AF394B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="27780" windowHeight="17500" xr2:uid="{EC3C71DD-AB41-7249-985D-4787F3B89605}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="365" uniqueCount="284">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="376" uniqueCount="292">
   <si>
     <t>no</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -1231,6 +1231,41 @@
    資訊: 
 &lt;a style="button" class="btn btn-info"  href="fig/XLK-321-RestaurantA7/A7XLK-3201-RestaurantA7-10 新井茶.jpeg"&gt;菜單&lt;/a&gt;,
 &lt;a style="button" class="btn btn-info"  href="https://www.ubereats.com/tw/store/%E6%96%B0%E4%BA%95%E8%8C%B6-%E9%BE%9C%E5%B1%B1%E9%95%B7%E6%85%B6%E5%BA%97/r4RkIP-bX0yyYwC6zyUpfQ?diningMode=DELIVERY&amp;pl=JTdCJTIyYWRkcmVzcyUyMiUzQSUyMkphZGUlMjBEeW5hc3R5JTIyJTJDJTIycmVmZXJlbmNlJTIyJTNBJTIyZjgyZTA1YTItODE2NS0xMGU4LWQ3M2QtNDMwYzIyOWY5MjA4JTIyJTJDJTIycmVmZXJlbmNlVHlwZSUyMiUzQSUyMnViZXJfcGxhY2VzJTIyJTJDJTIybGF0aXR1ZGUlMjIlM0E0OS4yODAzOSUyQyUyMmxvbmdpdHVkZSUyMiUzQS0xMjMuMTAxMjglN0Q%3D&amp;utm_campaign=place-action-link&amp;utm_medium=organic&amp;utm_source=google"&gt;Uber Eats&lt;/a&gt;
+&lt;/p&gt;</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.google.com.tw/maps/place/%E5%AD%AB%E5%AE%B6%E5%B0%87%E8%87%BA%E5%BC%8F%E7%89%9B%E6%8E%92-%E6%96%87%E9%9D%92%E5%BA%97/@25.0406316,121.3863128,20.59z/data=!4m8!1m2!2m1!1z5YWD5rCj5pep5Y2I6aSQQTfmlofpnZLlupc!3m4!1s0x3442a752cc5f07ff:0x510f93a6d2173af4!8m2!3d25.0407824!4d121.3866426?hl=zh-TW&amp;authuser=0</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>孫家將臺式牛排</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>牛排館</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>桃園市龜山區文青路137號1樓四室</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>03-328-6857</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>fig/XLK-321-RestaurantA7/A7XLK-3203-A7Restaurant-11.jpeg</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.facebook.com/people/%E5%AD%AB%E5%AE%B6%E5%B0%87%E8%87%BA%E5%BC%8F%E7%89%9B%E6%8E%92/100057413380976/</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;p&gt;
+   資訊: &lt;a style="button" class="btn btn-info"  href="https://zaq0930.pixnet.net/blog/post/362621357-%E3%80%90a7%E9%A3%9F%E8%A8%98%E3%80%91%E5%AD%AB%E5%AE%B6%E5%B0%87%E7%89%9B%E6%8E%92"&gt;推薦&lt;/a&gt; &amp;nbsp; 
+&lt;a style="button" class="btn btn-info"  href="https://www.facebook.com/photo/?fbid=270216144443149&amp;set=pb.100057413380976.-2207520000.."&gt;菜單&lt;/a&gt; &amp;nbsp;
 &lt;/p&gt;</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -1652,7 +1687,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D43F91F4-866F-584C-A1A3-A0D1F56F484D}">
-  <dimension ref="A1:M33"/>
+  <dimension ref="A1:M34"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="18.83203125" customWidth="1"/>
@@ -2912,6 +2947,44 @@
       </c>
       <c r="M33" s="3" t="s">
         <v>232</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13" ht="144">
+      <c r="A34">
+        <v>311</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>285</v>
+      </c>
+      <c r="C34" s="5" t="s">
+        <v>286</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="E34" s="10" t="s">
+        <v>288</v>
+      </c>
+      <c r="F34" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="H34" s="2" t="s">
+        <v>289</v>
+      </c>
+      <c r="I34" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="J34" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="K34" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="L34" s="9" t="s">
+        <v>291</v>
+      </c>
+      <c r="M34" s="7" t="s">
+        <v>284</v>
       </c>
     </row>
   </sheetData>
@@ -2962,6 +3035,8 @@
     <hyperlink ref="I33" r:id="rId43" xr:uid="{0F604AB3-BEFF-2046-B537-A1F987B3C006}"/>
     <hyperlink ref="M9" r:id="rId44" xr:uid="{F1C6FD45-614D-5E41-A814-2FC046758624}"/>
     <hyperlink ref="I26" r:id="rId45" xr:uid="{6564EE13-82E2-DB44-8058-211B23573035}"/>
+    <hyperlink ref="M34" r:id="rId46" display="https://www.google.com.tw/maps/place/%E5%AD%AB%E5%AE%B6%E5%B0%87%E8%87%BA%E5%BC%8F%E7%89%9B%E6%8E%92-%E6%96%87%E9%9D%92%E5%BA%97/@25.0406316,121.3863128,20.59z/data=!4m8!1m2!2m1!1z5YWD5rCj5pep5Y2I6aSQQTfmlofpnZLlupc!3m4!1s0x3442a752cc5f07ff:0x510f93a6d2173af4!8m2!3d25.0407824!4d121.3866426?hl=zh-TW&amp;authuser=0" xr:uid="{8587FFCA-4F89-FC42-9B22-1957D3772E96}"/>
+    <hyperlink ref="I34" r:id="rId47" xr:uid="{C0161631-E25F-4747-B8DB-F82DA62B3DBA}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
